--- a/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmeurope-my.sharepoint.com/personal/salman_muhammad_cmeurope_org/Documents/Technical/IF mapping tool/if-map/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1923" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7066EC13-F009-4EF2-9E9E-B9F38DDBF7AD}"/>
+  <xr:revisionPtr revIDLastSave="1961" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D866604E-FE4A-4DBB-A62A-E94333506F5A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Legend" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IF Projects'!$A$1:$AE$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IF Projects'!$A$1:$AD$61</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -59,440 +59,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{ACC6BF44-3BBF-46B5-9709-81A19A5C1C4D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 1.0 Mt/yr × 10 years. Heidelberg Materials Airvault, France. CCS.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T5" authorId="0" shapeId="0" xr:uid="{75DD4FA0-DB5C-4A34-9CBC-05164B750D75}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Estimated: IF24 large-scale grant, not officially published. Heidelberg Materials confirmed 'EU Innovation Fund support' but no amount disclosed. Estimate based on comparable IF23 CCS cement grants.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{CA089D12-DDFF-49A0-AEF6-FE526A130827}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Stated: 7.83 Mt CO₂e removed over first 10 years (Stockholm Exergi docs).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{7944A028-4B18-4734-B27F-183FA1165DB7}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.064 Mt/yr × 10 years. CCS at Ferrara WtE plant.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M15" authorId="0" shapeId="0" xr:uid="{08F7CB66-F756-4ECD-9230-CF123BCF3B07}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.7 Mt/yr × 10 years. Holcim CarboClearTech at Martres-Tolosane, France. CCS – CO₂ stored in Pyrenean subsoil.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N15" authorId="0" shapeId="0" xr:uid="{3F923380-BEAD-40D4-AB5F-4EBF964B8131}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>CCS project – all CO₂ sequestered.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M16" authorId="0" shapeId="0" xr:uid="{5AB2A97B-3027-4973-8EF9-044770BA62BD}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 1.0 Mt/yr × 10 years. Holcim Romania, operational 2032.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U19" authorId="0" shapeId="0" xr:uid="{544CE636-AEB1-4BF8-80AE-DFAB8940E518}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €4.27M (CINEA). Small-scale project. Total investment ~€12M est. Op: 2026.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U21" authorId="0" shapeId="0" xr:uid="{FF161F0B-1FEE-4CC3-B1F9-397FA0DDB245}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF24 large-scale). COnet2 Sea CO₂ shipping Spain. Total investment est. ~€200M+ (maritime CO₂ transport fleet + infrastructure). Op: ~2029.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M24" authorId="0" shapeId="0" xr:uid="{63767E34-FE5E-4869-AEBA-B036799E22FA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.2 Mt/yr × 10 years. DEZiR eSAF CCU France. Note: stated 5 Mt over 25-yr lifespan.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M25" authorId="0" shapeId="0" xr:uid="{C703CE98-6007-453E-B2CC-C4D4D435A26A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 1.0 Mt/yr × 10 years. Heidelberg Materials DREAM CCS, Rezzato-Mazzano Italy.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M26" authorId="0" shapeId="0" xr:uid="{6FFBB4CA-A792-4720-AD6F-E688BB6DAFFB}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>E-fuel Pilot (Norway): Small refinery e-fuel pilot using captured CO₂ + H₂ for Fischer-Tropsch SAF. Pilot/demo scale. No annual CO₂ volume published.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U26" authorId="0" shapeId="0" xr:uid="{34DE0766-8790-4462-B031-CD4D456A9579}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €40M (CINEA 2022). E-fuel Pilot Norway. Total investment ~€120M est. 5yr pilot period.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M27" authorId="0" shapeId="0" xr:uid="{D4783190-AFA7-467D-B716-8B1619CEC1DF}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.195 Mt/yr × 10 years. Elyse Energy eM-Rhône CCU.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U27" authorId="0" shapeId="0" xr:uid="{5A77858C-BE02-4873-8715-7E52EF463E3A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €115.2M (CINEA 2022). eM-Rhône CCU e-methanol France. Total investment ~€700M (Elyse Energy press release: ~€700M total investment). Op: 2028.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T28" authorId="0" shapeId="0" xr:uid="{AD661DD4-D11B-49DD-9155-A291A23619CC}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Estimated: €40M from the €153M awarded to 4 eSAF large-scale projects in IF24 call. DEZiR and ReSTart are the other two French eSAF projects; 4th is likely ENDOR (Denmark). Not officially published; grant agreement preparation underway.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U28" authorId="0" shapeId="0" xr:uid="{13F6BB95-587A-48E4-80EF-14313107396B}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF24 large-scale). Arcadia eFuels ENDOR eSAF plant. Total investment ~€700M est. (FEED completed; commercial-scale SAF plant). Op: 2028 est.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L30" authorId="0" shapeId="0" xr:uid="{B73FB0DC-F8E7-4FFD-A5EB-88339367F3A4}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>KHP: Waste→H₂ via plasma gasification (Plagazi, Sweden). 66,000 t/yr waste processed. CO₂ captured but specific annual volume not confirmed.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{3D3F0413-6B19-454F-B14D-FB49238B9487}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>KHP (Plagazi Sweden, Köping): Plasma gasification of 66,000 t/yr waste → 12,000 t/yr H₂. CO₂ also captured but specific annual volume not confirmed.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{B52CDF60-0E23-45FF-81E3-92C7E692A499}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Stated: 'more than 10 million tonnes CO₂ over 10 years' (Holcim FAQ). 1.0 Mt/yr at Kujawy cement plant, Poland.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U33" authorId="0" shapeId="0" xr:uid="{98CA0721-B4A8-4939-BE8D-A37EFD70754E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €230M (Holcim). Total CAPEX ~€600M est. (Holcim commitment to invest CHF 2B in CCUS projects; GO4ZERO share estimated). Op: 2028-2029.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M34" authorId="0" shapeId="0" xr:uid="{8A91711A-3339-4377-8D63-3736F032CE7C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.29 Mt/yr × 10 years. CCU PtX project, Spain.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{18281F7D-B56F-49B2-A21A-D85A89A15CC5}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.4 Mt/yr × 10 years. Phase 1 operations from mid-2026. Offshore CCS in Nini West field, Danish North Sea.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U35" authorId="0" shapeId="0" xr:uid="{0F9B2B35-D140-4428-8C8E-4156AD8AED67}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €41M (STEP SEAL page). Greensand Future medium-scale offshore CCS storage. Total investment ~€150M+ (INEOS FID Dec 2024: &gt;$150M across value chain). Op: mid-2026.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M36" authorId="0" shapeId="0" xr:uid="{0BDA9F00-BBEB-4F23-B679-D8CA29CB2658}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 1.7 Mt/yr × 10 years. H2BE CCS-H₂ Belgium, CO₂ to Norwegian Continental Shelf storage.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M37" authorId="0" shapeId="0" xr:uid="{7C2398C4-63BC-4C6F-A17F-C94E681ADB60}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>HuCCSar (Heidelberg Materials Poland): Validates CO₂ storage potential in Central Poland. Storage feasibility/infrastructure project. Cement capture component volume not confirmed publicly.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U37" authorId="0" shapeId="0" xr:uid="{A2A01A83-076B-455E-8936-52BB5AEA9558}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF24 pilot, max €40M). HuCCSar CCS storage validation Poland. Total investment est. ~€120M. 5yr pilot.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M39" authorId="0" shapeId="0" xr:uid="{884C49EF-257D-4EE3-B953-FA81175211EF}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.2 Mt/yr × 10 years. Öresundskraft CCS at Filbornaverket WtE, Helsingborg.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U41" authorId="0" shapeId="0" xr:uid="{1C7DC32F-D9CE-4DD9-B4E0-49E6113908C7}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €357M (CINEA confirmed). Total CAPEX ~€900M (Air Liquide/Ineos estimate for Antwerp CCS value chain). Op: 2025, 10yr period ends 2035.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M42" authorId="0" shapeId="0" xr:uid="{D58531C3-20AB-4753-A04F-428EB7DF2D95}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.366 Mt/yr × 10 years. Holcim KOdeCO, Koromačno Croatia.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M44" authorId="0" shapeId="0" xr:uid="{BA07B216-CC56-4852-B214-1BF5C6537329}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.07 Mt/yr × 10 years.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="Q44" authorId="0" shapeId="0" xr:uid="{AB8BFFB0-4F71-49AA-8EFA-DE6C76D21FD7}">
       <text>
         <r>
@@ -507,152 +73,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="L45" authorId="0" shapeId="0" xr:uid="{55133E55-ADEE-4FDE-884C-DA609E81C9D1}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>MetZero: Biocarbon for metallurgy (Norway). Not a CO₂ capture project — reduces emissions through feedstock substitution. No CO₂ capture columns applicable.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M45" authorId="0" shapeId="0" xr:uid="{C9256CAE-BEE0-4701-A624-1A6BA329F6DC}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>MetZero (Norway): Biocarbon (charcoal) for metallurgy as fossil coke replacement. Emissions reduction by feedstock substitution — NOT a CO₂ capture project. No CO₂ columns applicable.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U45" authorId="0" shapeId="0" xr:uid="{D59F164A-F30C-41D6-9177-1D07367BB56D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF23 medium-scale). MetZero biocarbon metallurgy Norway. Total investment est. ~€150M.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U47" authorId="0" shapeId="0" xr:uid="{CB425BF4-A0AF-4B01-9838-407E8FC861B6}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF24 medium-scale). PP2XH e-methanol Estonia. Total investment est. €200M+ (large biomass gasification + methanol plant).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M48" authorId="0" shapeId="0" xr:uid="{5DCE136B-8826-4009-95A6-B87C0E5BCD67}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 0.406 Mt/yr × 10 years. CCU PtX e-fuels, Sweden.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L50" authorId="0" shapeId="0" xr:uid="{018AAA98-C676-4202-A1E4-160EE98E8773}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>RESILIENCE: rSOC biogas-to-power (Germany). CO₂ captured but no volume confirmed.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M50" authorId="0" shapeId="0" xr:uid="{45DCF3AD-855E-4181-93BA-4FAE3E1294FA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>RESILIENCE (Reverion Germany): rSOC converting biogas to electricity at 80% efficiency. CO₂ captured during electrochemical process but no annual volume confirmed.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U50" authorId="0" shapeId="0" xr:uid="{61AE816F-B1DF-4002-8C93-1EB8A4C45A35}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €62M (Bellona article). RESILIENCE rSOC biogas Germany (Reverion). Total investment ~€120M est. Op: ~2028.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M52" authorId="0" shapeId="0" xr:uid="{7578F409-F8B9-4112-97D0-A2541340170D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Stated: 'more than 4 Mt CO₂ in first 10 years' (Neste). CCS at Porvoo refinery, Finland.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M60" authorId="0" shapeId="0" xr:uid="{5CD9E18D-B39E-48CD-AE30-905C53419851}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 1.2 Mt/yr × 10 years. Vicat VAIA CCS at Montalieu-Vercieu.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="491">
   <si>
     <t>Status</t>
   </si>
@@ -803,9 +229,6 @@
     <t>Facility Type</t>
   </si>
   <si>
-    <t>Short Description</t>
-  </si>
-  <si>
     <t>Link</t>
   </si>
   <si>
@@ -845,9 +268,6 @@
     <t>Scheldelaan 600, Haven 725, 2040 Antwerpen, Belgium</t>
   </si>
   <si>
-    <t>Kairos-at-C, Building strong momentum for massive decarbonisation in the EU through a unique end to end CCS project</t>
-  </si>
-  <si>
     <t>small-scale</t>
   </si>
   <si>
@@ -893,9 +313,6 @@
     <t>Rue des Fabriques 2, 7034 Obourg, Belgium</t>
   </si>
   <si>
-    <t>Towards a carbon negative large-scale clinker plant through first-ever demonstration of a groundbreaking flue gas recirculation &amp; concentration-based concept paired with a full CCS solution</t>
-  </si>
-  <si>
     <t>H2BE</t>
   </si>
   <si>
@@ -908,9 +325,6 @@
     <t>IF23</t>
   </si>
   <si>
-    <t>The first 1GW low-carbon H2 production facility to enable and accelerate industrial decarbonisation, critical H2/CO2 infrastructure realisation and H2 market development in Northern Europe.</t>
-  </si>
-  <si>
     <t>Large-scale</t>
   </si>
   <si>
@@ -926,9 +340,6 @@
     <t>Heidelberg Materials Antoing plant, 7640 Antoing, Belgium</t>
   </si>
   <si>
-    <t>Antoing Heidelberg Materials Emissions Integrated System</t>
-  </si>
-  <si>
     <t>ANTHEMIS is a large-scale CCS project at Heidelberg Materials’ Antoing cement plant that will deploy a hybrid oxyfuel and amine carbon capture system to capture over 95% of emissions (~800,000 tCO₂/year). The project includes transport and permanent offshore storage, enabling near net-zero cement production from 2029. Invited to IF24 grant agreement preparation (Nov 2025). Amount not confirmed. Permit application submitted H1 2025 for Antoing clinker plant. FID targeted 2026-2027. Operational: 2029.</t>
   </si>
   <si>
@@ -941,9 +352,6 @@
     <t>Carmeuse</t>
   </si>
   <si>
-    <t>LimE OPeration decARboniseD</t>
-  </si>
-  <si>
     <t>ANRAV</t>
   </si>
   <si>
@@ -953,9 +361,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>ANRAV will establish Eastern Europe’s first full CCS chain, capturing CO₂ from Devnya cement plant and storing it offshore in the Black Sea, achieving ~95% emission reduction.</t>
-  </si>
-  <si>
     <t>KOdeCO net zero</t>
   </si>
   <si>
@@ -974,9 +379,6 @@
     <t>Rørdalsvej 44, 9220 Aalborg Øst, Denmark</t>
   </si>
   <si>
-    <t xml:space="preserve"> Aalborg Portland Carbon Capture and Storage using Infrastructure Onshore in North Jutland</t>
-  </si>
-  <si>
     <t>medium-scale</t>
   </si>
   <si>
@@ -989,18 +391,12 @@
     <t>Port Esbjerg terminal, Esbjerg, Denmark</t>
   </si>
   <si>
-    <t>Contributing to EUs CO2 emissions reduction target by establishing critical EU storage capacity</t>
-  </si>
-  <si>
     <t>ENDOR</t>
   </si>
   <si>
     <t>Arcadia eFuels</t>
   </si>
   <si>
-    <t>Arcadia eFuels,  decarbonizing aviation</t>
-  </si>
-  <si>
     <t>RECLAIM</t>
   </si>
   <si>
@@ -1010,18 +406,12 @@
     <t>Holmevej 100, 9640 Farsø, Denmark</t>
   </si>
   <si>
-    <t>Renewable Energy Cluster for Agro- Industrial Methanol Production</t>
-  </si>
-  <si>
     <t xml:space="preserve">PP2XH </t>
   </si>
   <si>
     <t>Pärnu Airport area, Pärnu County, Estonia</t>
   </si>
   <si>
-    <t>Pärnu P2X Hub</t>
-  </si>
-  <si>
     <t>SHARC</t>
   </si>
   <si>
@@ -1031,9 +421,6 @@
     <t>Kilpilahti, 06850 Porvoo, Finland</t>
   </si>
   <si>
-    <t>Replacing gray hydrogen with green and blue hydrogen</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://climate.ec.europa.eu/document/download/0b0c09d5-4b1d-4ad3-abe7-57e68a53a0c2_en?filename=if_pf_2022_sharc_en.pdf&amp;prefLang=fr </t>
   </si>
   <si>
@@ -1055,9 +442,6 @@
     <t xml:space="preserve"> Lhoist</t>
   </si>
   <si>
-    <t>First industrial scale carbon capture for lime production integrated with transport of CO2 to coastal hub and shipping to geological storage in the North Sea</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://climate.ec.europa.eu/document/download/bd0ab5e5-bc37-4bff-b3b7-1a179c2e2529_en?filename=if_pf_2022_calcc_en.pdf </t>
   </si>
   <si>
@@ -1067,9 +451,6 @@
     <t>Elyse Energy</t>
   </si>
   <si>
-    <t>electroMethanol-Rhône</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101133147.pdf </t>
   </si>
   <si>
@@ -1088,45 +469,30 @@
     <t>Rue de la Cimenterie, 79600 Airvault, France</t>
   </si>
   <si>
-    <t>First large-scale CCUS network for deep inland emitters starting from the Europes first zero water intake cement plant</t>
-  </si>
-  <si>
     <t xml:space="preserve">DEZiR </t>
   </si>
   <si>
     <t>Medium-High</t>
   </si>
   <si>
-    <t>Decarbonation en Seine-Eure et sur la Zone industrielle de Rouen</t>
-  </si>
-  <si>
     <t>ReSTart</t>
   </si>
   <si>
     <t>Not applicable</t>
   </si>
   <si>
-    <t>Renewable e-SAF Tartas</t>
-  </si>
-  <si>
     <t>VAIA</t>
   </si>
   <si>
     <t>Vicat</t>
   </si>
   <si>
-    <t>Vicat Advanced Industrial Alliance</t>
-  </si>
-  <si>
     <t>Post-combustion CO₂ capture (electromechanical activation + electrified amine/post-combustion + heat integration) at Vicat Montalieu-Vercieu cement plant; CO₂ via repurposed SPESE oil pipeline → Lacq/Elengy terminal → geological storage in Italy (depleted gas); 1.2 Mt/yr</t>
   </si>
   <si>
     <t>TAKE KAIR</t>
   </si>
   <si>
-    <t>Take Kair</t>
-  </si>
-  <si>
     <t>Holcim GmbH</t>
   </si>
   <si>
@@ -1142,9 +508,6 @@
     <t>Rheinkalk GMBH</t>
   </si>
   <si>
-    <t>Improved calcination and carbon capture for the largest lime plant in Europe</t>
-  </si>
-  <si>
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101132835.pdf</t>
   </si>
   <si>
@@ -1154,9 +517,6 @@
     <t>Bürener Straße 46, 59590 Geseke, Germany</t>
   </si>
   <si>
-    <t>First German inland cement plant Geseke becomes net carbon negative by implementing a full CCS chain</t>
-  </si>
-  <si>
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101133005.pdf</t>
   </si>
   <si>
@@ -1169,9 +529,6 @@
     <t>Schönerlinderstraße 1, 15562 Rüdersdorf bei Berlin, Germany</t>
   </si>
   <si>
-    <t xml:space="preserve"> Innovation in Carbon Capture and Transport</t>
-  </si>
-  <si>
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101191027.pdf</t>
   </si>
   <si>
@@ -1181,9 +538,6 @@
     <t>REVERION GMBH</t>
   </si>
   <si>
-    <t>Revolutionizing Energy, scaling manufacturing of innovative, reversible, highly efficient, carbon-negative power plants</t>
-  </si>
-  <si>
     <t>OLYMPUS</t>
   </si>
   <si>
@@ -1193,15 +547,9 @@
     <t>Milaki, 344 00 Aliveri, Evia, Greece</t>
   </si>
   <si>
-    <t>Ascending to the top of CO2 avoidance in the EU cement sector through the innovative OxyCalciner technology</t>
-  </si>
-  <si>
     <t>Titan Cement Company S.A.</t>
   </si>
   <si>
-    <t>IFESTOS  one of the largest carbon capture projects in Europe to enable the production of zero carbon cement &amp; concrete and create decarbonization synergies with regional industries</t>
-  </si>
-  <si>
     <t>IRIS</t>
   </si>
   <si>
@@ -1214,9 +562,6 @@
     <t>71st km Athens-Corinth National Road, 20003 Agioi Theodoroi, Greece</t>
   </si>
   <si>
-    <t>Innovative low caRbon hydrogen and methanol productIon by large Scale carbon capture</t>
-  </si>
-  <si>
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101133015.pdf</t>
   </si>
   <si>
@@ -1226,45 +571,30 @@
     <t>Other</t>
   </si>
   <si>
-    <t>Creation of an innovative and cost-efficient CO2 management solution to heavy industrial emitters through a Liquefaction Export Terminal, leveraging on the CCS hub approach.</t>
-  </si>
-  <si>
     <t>Thermolysis</t>
   </si>
   <si>
     <t>Thermo Lysi S.A.</t>
   </si>
   <si>
-    <t>?hermo-lysi SA End-of-Life Tyres (ELTs) recycling facility utilizing innovative made- in-Europe Pyrolysis technology</t>
-  </si>
-  <si>
     <t>Danube Removals</t>
   </si>
   <si>
     <t>Carbon Removal (BioCCS)</t>
   </si>
   <si>
-    <t>Danube Onshore Fermentation Carbon Removals</t>
-  </si>
-  <si>
     <t>Silverstone</t>
   </si>
   <si>
     <t>Carbfix</t>
   </si>
   <si>
-    <t>Silverstone: Full-scale CO2 capture and mineral storage at the Hellisheidi power station</t>
-  </si>
-  <si>
     <t>Coda Terminal</t>
   </si>
   <si>
     <t>Straumsvík, 220 Hafnarfjörður, Iceland</t>
   </si>
   <si>
-    <t>Coda by Carbfix - a highly scalable, cost effective CO2 mineral storage hub</t>
-  </si>
-  <si>
     <t>https://climate.ec.europa.eu/document/download/127cb46b-3974-4145-8960-53031599d4df_en?filename=if_pf_2022_coda_en.pdf</t>
   </si>
   <si>
@@ -1280,9 +610,6 @@
     <t>Low</t>
   </si>
   <si>
-    <t>Carbon Capture and Use at a STeel plant with an Advanced solution to Reach Decarbonisation</t>
-  </si>
-  <si>
     <t>CapturEste</t>
   </si>
   <si>
@@ -1307,9 +634,6 @@
     <t>Esso Nederland BV</t>
   </si>
   <si>
-    <t>CFC Pilot for CCS</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101132998.pdf </t>
   </si>
   <si>
@@ -1325,9 +649,6 @@
     <t>Nordic Electrofuel</t>
   </si>
   <si>
-    <t>Innovative and cost-efficient production process for Power-to-Liquid using industrial off-gases</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101132987.pdf </t>
   </si>
   <si>
@@ -1340,42 +661,27 @@
     <t>MetZero</t>
   </si>
   <si>
-    <t>Biocarbon reductants for decarbonising the metallurgical industry</t>
-  </si>
-  <si>
     <t>BIOVIND</t>
   </si>
   <si>
-    <t>Advancing Sustainable Bio- LNG Production and Waste Valorization</t>
-  </si>
-  <si>
     <t>VIPER</t>
   </si>
   <si>
     <t>Vow Green Metals AS</t>
   </si>
   <si>
-    <t>Viken Industrial Pyrolysis for Emissions Reduction</t>
-  </si>
-  <si>
     <t>Slow pyrolysis biorefinery (Vow Green Metals technology): woody biomass by-products → biocarbon (metallurgical reducing agent replacing fossil coke) + biochar (soil amendment) + bio-oil (bitumen replacement in asphalt); circular bioeconomy; GHG reduction via feedstock substitution</t>
   </si>
   <si>
     <t>SLALOM 2.0</t>
   </si>
   <si>
-    <t>Sustainable, Low- carbon Advancements in LanzaFlex Operations for Manufacturing</t>
-  </si>
-  <si>
     <t>GO4ECOPLANET</t>
   </si>
   <si>
     <t>Holcim</t>
   </si>
   <si>
-    <t>KUJAWY GO4ECOPLANET</t>
-  </si>
-  <si>
     <t>Air Liquide CryocapTM FG (high-pressure cryogenic CO₂ separation from cement flue gas, 99.9% purity) at Holcim Kujawy cement plant; CO₂ liquefied; rail transport to Gdańsk port; ship to North Sea geological storage; 1 Mt/yr</t>
   </si>
   <si>
@@ -1385,9 +691,6 @@
     <t>BZK ENERGY SPOLKA Z OGRANICZONA ODPOWIEDZIALNOSCIA</t>
   </si>
   <si>
-    <t>Closed-loop installation for sustAinable production of bioMethane, BioCO2 And biofertilizerS a new StandArD fOr zeRo waste economy</t>
-  </si>
-  <si>
     <t>HuCCSar</t>
   </si>
   <si>
@@ -1400,9 +703,6 @@
     <t>Cementowa 1, 47-316 Górażdże, Poland</t>
   </si>
   <si>
-    <t>HUb for Carbon Capture and Storage to decarbonise the hard-to Abate Regions in Poland  HuCCSar</t>
-  </si>
-  <si>
     <t>CARBON HUB CPT01</t>
   </si>
   <si>
@@ -1412,18 +712,12 @@
     <t>PETRONOR</t>
   </si>
   <si>
-    <t>Fabrication of CO2 negative AGGREGAtes based on disruptive accelerated carbonation processes fuelled by carbon capture in refineries</t>
-  </si>
-  <si>
     <t>GREEN MEIGA</t>
   </si>
   <si>
     <t xml:space="preserve">IBERDROLA Clientes </t>
   </si>
   <si>
-    <t>Green Methanol in Galicia</t>
-  </si>
-  <si>
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101133150.pdf</t>
   </si>
   <si>
@@ -1433,9 +727,6 @@
     <t xml:space="preserve">Forestal del Atlántico, S.A. </t>
   </si>
   <si>
-    <t>Green Methanol manufacturing from CO2</t>
-  </si>
-  <si>
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101133213.pdf</t>
   </si>
   <si>
@@ -1445,18 +736,12 @@
     <t>TarraCO2</t>
   </si>
   <si>
-    <t>The reduction of CO2 emissions through geological storage, a catalyst of the CO2 market</t>
-  </si>
-  <si>
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101191313.pdf</t>
   </si>
   <si>
     <t>COnet2 Sea</t>
   </si>
   <si>
-    <t>Pioneering CO? Maritime Transport for CCS Across the Mediterranean</t>
-  </si>
-  <si>
     <t>Maritime CO₂ transport service: medium-pressure liquid CO₂ (LCO₂) vessel with zeolite-based onboard CO₂ capture unit + bioLNG propulsion + innovative boil-off gas management using LNG cold; CO₂ shipped from cement plant to Mediterranean/North Sea geological storage</t>
   </si>
   <si>
@@ -1466,27 +751,15 @@
     <t>Lidingövägen 115, 115 77 Stockholm, Sweden</t>
   </si>
   <si>
-    <t>Bio-Energy Carbon Capture and Storage (BECCS) at the existing Combined Heat and Power-plant KVV8 at Värtaverket, Stockholm, Sweden</t>
-  </si>
-  <si>
-    <t>Production of sustainable methanol as raw material for chemical products by first-of-a-kind Carbon Capture and Utilization process integrated with world scale electrolysis unit</t>
-  </si>
-  <si>
     <t>INNOZHERO</t>
   </si>
   <si>
     <t>Öresundskraft Kraft &amp; Värme AB</t>
   </si>
   <si>
-    <t xml:space="preserve"> Innovation for Zero Emissions in Helsingborg</t>
-  </si>
-  <si>
     <t>Köping Hydrogen Park AB</t>
   </si>
   <si>
-    <t>The Plagazi Process, A Patented Plasma Gasification System to Turn Hard-to-Recycle Waste into Clean Hydrogen</t>
-  </si>
-  <si>
     <t>IFESTOS</t>
   </si>
   <si>
@@ -1703,9 +976,6 @@
     <t>https://ha.gruppohera.it/captureste-project</t>
   </si>
   <si>
-    <t>Carbon Capture to Decarbonize Herambiente Ferrara Waste-to-Energy Plant</t>
-  </si>
-  <si>
     <t>CarboClearTech is a large-scale CCS project at Holcim’s Martres-Tolosane cement plant in France, designed to significantly reduce CO₂ emissions from clinker production through an integrated carbon capture, transport, and storage chain. Developed in collaboration with Air Liquide and regional infrastructure partners, the project will capture approximately 0.7 MtCO₂ per year and permanently store it in geological formations in southwestern France. In addition to decarbonising the plant, CarboClearTech serves as an industrial-scale demonstration platform for modular and replicable CCS solutions in the cement sector. The project aims to support Holcim’s net-zero strategy while enabling standardised, scalable CCS deployment across European heavy industry.</t>
   </si>
   <si>
@@ -2232,9 +1502,6 @@
   </si>
   <si>
     <t>Via Gardesana, 84, 25086 Rezzato BS, Italy</t>
-  </si>
-  <si>
-    <t>Decarbonisation of the Rezzato and Mazzano cement plant in taly</t>
   </si>
   <si>
     <t>CO₂ transport and storage</t>
@@ -3194,7 +2461,7 @@
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
-  <dimension ref="A1:AE61"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr defaultColWidth="30" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="10" customWidth="1"/>
@@ -3213,15 +2480,14 @@
     <col min="24" max="24" width="10" style="10" customWidth="1"/>
     <col min="25" max="25" width="28" style="10" customWidth="1"/>
     <col min="26" max="26" width="18" style="10" customWidth="1"/>
-    <col min="27" max="27" width="40" style="10" customWidth="1"/>
-    <col min="28" max="28" width="14" style="10" customWidth="1"/>
-    <col min="29" max="29" width="50" style="10" customWidth="1"/>
-    <col min="30" max="30" width="55" style="10" customWidth="1"/>
-    <col min="31" max="31" width="30" style="10" customWidth="1"/>
-    <col min="32" max="16384" width="30" style="10"/>
+    <col min="27" max="27" width="14" style="10" customWidth="1"/>
+    <col min="28" max="28" width="50" style="10" customWidth="1"/>
+    <col min="29" max="29" width="55" style="10" customWidth="1"/>
+    <col min="30" max="30" width="30" style="10" customWidth="1"/>
+    <col min="31" max="16384" width="30" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="24" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" s="24" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>23</v>
       </c>
@@ -3271,10 +2537,10 @@
         <v>37</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="S1" s="9" t="s">
         <v>38</v>
@@ -3310,33 +2576,30 @@
         <v>48</v>
       </c>
       <c r="AD1" s="9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="148.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AE1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" ht="148.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="B2" s="41" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H2" s="20">
         <v>1.5</v>
@@ -3348,7 +2611,7 @@
         <v>1.4</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" s="20">
         <v>15.077949</v>
@@ -3360,7 +2623,7 @@
         <v>14</v>
       </c>
       <c r="O2" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P2" s="13">
         <v>2024</v>
@@ -3372,13 +2635,13 @@
         <v>2040</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T2" s="14">
         <v>220123498</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V2" s="5">
         <v>57.062100000000001</v>
@@ -3387,51 +2650,48 @@
         <v>9.9770000000000003</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB2" s="25" t="s">
-        <v>288</v>
+        <v>461</v>
+      </c>
+      <c r="AA2" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>472</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>525</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="AE2" s="51" t="s">
-        <v>496</v>
+        <v>473</v>
+      </c>
+      <c r="AD2" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="H3" s="12">
         <v>0.12330000000000001</v>
@@ -3443,7 +2703,7 @@
         <v>0.112</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" s="21">
         <v>1.2330000000000001</v>
@@ -3455,7 +2715,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P3" s="13">
         <v>2025</v>
@@ -3467,13 +2727,13 @@
         <v>2037</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T3" s="14">
         <v>31238542</v>
       </c>
       <c r="U3" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V3" s="5">
         <v>44.464755134852901</v>
@@ -3482,60 +2742,57 @@
         <v>12.2450955929227</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA3" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB3" s="25" t="s">
-        <v>210</v>
+        <v>461</v>
+      </c>
+      <c r="AA3" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>477</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="AE3" s="71" t="s">
-        <v>497</v>
+        <v>476</v>
+      </c>
+      <c r="AD3" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="125.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K4" s="22">
         <v>2.2000000000000001E-3</v>
@@ -3544,7 +2801,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" s="22">
         <v>2.1999999999999999E-2</v>
@@ -3562,13 +2819,13 @@
         <v>2036</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T4" s="18">
         <v>3168000</v>
       </c>
       <c r="U4" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V4" s="7">
         <v>43.327720234653299</v>
@@ -3577,51 +2834,48 @@
         <v>-3.1153158320413699</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y4" s="15" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="Z4" s="15" t="s">
-        <v>514</v>
-      </c>
-      <c r="AA4" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="AB4" s="25" t="s">
-        <v>287</v>
+        <v>462</v>
+      </c>
+      <c r="AA4" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>228</v>
       </c>
       <c r="AC4" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="AD4" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="AE4" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD4" s="45" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H5" s="12">
         <v>1</v>
@@ -3633,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" s="21">
         <v>10</v>
@@ -3645,10 +2899,10 @@
         <v>10</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="Q5" s="13">
         <v>2030</v>
@@ -3657,13 +2911,13 @@
         <v>2040</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T5" s="14">
-        <v>170000000</v>
+        <v>145000000</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V5" s="5">
         <v>46.809800000000003</v>
@@ -3672,75 +2926,72 @@
         <v>-0.13900000000000001</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA5" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB5" s="25" t="s">
-        <v>292</v>
+        <v>461</v>
+      </c>
+      <c r="AA5" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>242</v>
       </c>
       <c r="AC5" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="AD5" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="AE5" s="47" t="s">
-        <v>499</v>
+        <v>243</v>
+      </c>
+      <c r="AD5" s="47" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="125.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="H6" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" s="21">
         <v>0.128</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P6" s="13">
         <v>2025</v>
@@ -3752,66 +3003,63 @@
         <v>2038</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T6" s="14">
         <v>7958244</v>
       </c>
       <c r="U6" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z6" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA6" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="AB6" s="25" t="s">
-        <v>298</v>
+        <v>461</v>
+      </c>
+      <c r="AA6" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>246</v>
       </c>
       <c r="AC6" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="AD6" s="11" t="s">
-        <v>503</v>
-      </c>
-      <c r="AE6" s="70" t="s">
-        <v>498</v>
+        <v>451</v>
+      </c>
+      <c r="AD6" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H7" s="12">
         <v>0.8</v>
@@ -3823,7 +3071,7 @@
         <v>0.8</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" s="21">
         <v>7.8</v>
@@ -3835,7 +3083,7 @@
         <v>8</v>
       </c>
       <c r="O7" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7" s="13">
         <v>2023</v>
@@ -3847,13 +3095,13 @@
         <v>2038</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T7" s="14">
         <v>189694949</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V7" s="5">
         <v>43.232830995956597</v>
@@ -3862,51 +3110,48 @@
         <v>27.594387234972402</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>275</v>
+        <v>224</v>
       </c>
       <c r="Z7" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA7" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB7" s="25" t="s">
-        <v>300</v>
+        <v>461</v>
+      </c>
+      <c r="AA7" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>248</v>
       </c>
       <c r="AC7" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="AD7" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="AE7" s="49" t="s">
-        <v>500</v>
+        <v>250</v>
+      </c>
+      <c r="AD7" s="49" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H8" s="12">
         <v>0.8</v>
@@ -3918,7 +3163,7 @@
         <v>0.8</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L8" s="21">
         <v>8</v>
@@ -3930,10 +3175,10 @@
         <v>8</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="Q8" s="13">
         <v>2029</v>
@@ -3942,13 +3187,13 @@
         <v>2039</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T8" s="14">
         <v>115000000</v>
       </c>
       <c r="U8" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V8" s="5">
         <v>50.575420999999999</v>
@@ -3957,75 +3202,72 @@
         <v>3.4423240000000002</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA8" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB8" s="25" t="s">
-        <v>302</v>
+        <v>461</v>
+      </c>
+      <c r="AA8" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD8" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="AE8" s="47" t="s">
-        <v>499</v>
+        <v>252</v>
+      </c>
+      <c r="AD8" s="47" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="H9" s="16">
         <v>2.5819174</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="16">
         <v>3</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L9" s="28">
         <v>25.819174</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P9" s="17">
         <v>2025</v>
@@ -4037,13 +3279,13 @@
         <v>2039</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T9" s="18">
         <v>169300000</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V9" s="7">
         <v>37.960247145532399</v>
@@ -4052,75 +3294,72 @@
         <v>23.401746903124501</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y9" s="15" t="s">
-        <v>504</v>
+        <v>452</v>
       </c>
       <c r="Z9" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="AA9" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="AB9" s="25" t="s">
-        <v>305</v>
+        <v>463</v>
+      </c>
+      <c r="AA9" s="25" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB9" s="15" t="s">
+        <v>453</v>
       </c>
       <c r="AC9" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="AD9" s="15" t="s">
-        <v>531</v>
-      </c>
-      <c r="AE9" s="71" t="s">
-        <v>497</v>
+        <v>478</v>
+      </c>
+      <c r="AD9" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>307</v>
+        <v>256</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>508</v>
+        <v>456</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I10" s="21">
-        <v>0.78300000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="J10" s="21">
-        <v>0.78300000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L10" s="21">
         <v>7.83</v>
       </c>
       <c r="M10" s="21">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="N10" s="21">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P10" s="13">
         <v>2021</v>
@@ -4132,7 +3371,7 @@
         <v>2038</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T10" s="14">
         <v>180000000</v>
@@ -4147,75 +3386,72 @@
         <v>18.1028633833951</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB10" s="25" t="s">
-        <v>308</v>
+        <v>461</v>
+      </c>
+      <c r="AA10" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>480</v>
       </c>
       <c r="AC10" s="11" t="s">
-        <v>533</v>
-      </c>
-      <c r="AD10" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="AE10" s="45" t="s">
+        <v>479</v>
+      </c>
+      <c r="AD10" s="45" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>351</v>
+        <v>299</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" s="31">
         <v>7.6649999999999999E-3</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M11" s="21">
         <v>0.08</v>
       </c>
       <c r="N11" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P11" s="13">
         <v>2025</v>
@@ -4227,13 +3463,13 @@
         <v>2037</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T11" s="14">
         <v>10206000</v>
       </c>
       <c r="U11" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V11" s="5">
         <v>59.592303479664103</v>
@@ -4242,51 +3478,48 @@
         <v>5.8029778441568904</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y11" s="11" t="s">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="Z11" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA11" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB11" s="25" t="s">
-        <v>349</v>
+        <v>461</v>
+      </c>
+      <c r="AA11" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>301</v>
       </c>
       <c r="AC11" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="AD11" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="AE11" s="47" t="s">
-        <v>499</v>
+        <v>302</v>
+      </c>
+      <c r="AD11" s="47" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="H12" s="16">
         <v>1.3</v>
@@ -4295,7 +3528,7 @@
         <v>1.2</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K12" s="22">
         <v>1.2</v>
@@ -4307,7 +3540,7 @@
         <v>12</v>
       </c>
       <c r="N12" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O12" s="22">
         <v>12</v>
@@ -4322,7 +3555,7 @@
         <v>2038</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T12" s="18">
         <v>109816528</v>
@@ -4337,51 +3570,48 @@
         <v>9.5841999999999992</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y12" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="Z12" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA12" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB12" s="25" t="s">
-        <v>356</v>
+        <v>461</v>
+      </c>
+      <c r="AA12" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB12" s="15" t="s">
+        <v>303</v>
       </c>
       <c r="AC12" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="AD12" s="15" t="s">
-        <v>543</v>
-      </c>
-      <c r="AE12" s="70" t="s">
-        <v>498</v>
+        <v>490</v>
+      </c>
+      <c r="AD12" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H13" s="22">
         <v>0.57999999999999996</v>
@@ -4393,7 +3623,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L13" s="22">
         <v>5.8</v>
@@ -4405,7 +3635,7 @@
         <v>5.8</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P13" s="17">
         <v>2023</v>
@@ -4417,7 +3647,7 @@
         <v>2038</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T13" s="18">
         <v>125198197</v>
@@ -4432,51 +3662,48 @@
         <v>1.78234746701462</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y13" s="15" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="Z13" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA13" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB13" s="8" t="s">
-        <v>131</v>
+        <v>461</v>
+      </c>
+      <c r="AA13" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB13" s="15" t="s">
+        <v>268</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="AD13" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="AE13" s="51" t="s">
-        <v>496</v>
+        <v>269</v>
+      </c>
+      <c r="AD13" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="H14" s="16">
         <v>6.4000000000000001E-2</v>
@@ -4488,7 +3715,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L14" s="22">
         <v>0.64</v>
@@ -4500,7 +3727,7 @@
         <v>0.64</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P14" s="17">
         <v>2025</v>
@@ -4512,13 +3739,13 @@
         <v>2038</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T14" s="18">
         <v>23635998</v>
       </c>
       <c r="U14" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V14" s="7">
         <v>44.826999999999998</v>
@@ -4527,51 +3754,48 @@
         <v>11.614000000000001</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="Y14" s="15" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="Z14" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA14" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="AB14" s="25" t="s">
-        <v>345</v>
+        <v>461</v>
+      </c>
+      <c r="AA14" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="AB14" s="15" t="s">
+        <v>292</v>
       </c>
       <c r="AC14" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="AD14" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE14" s="70" t="s">
-        <v>498</v>
+        <v>293</v>
+      </c>
+      <c r="AD14" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="148.19999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" ht="148.19999999999999" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="H15" s="16">
         <v>0.7</v>
@@ -4583,7 +3807,7 @@
         <v>0.7</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L15" s="22">
         <v>7</v>
@@ -4595,7 +3819,7 @@
         <v>7</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P15" s="17">
         <v>2024</v>
@@ -4607,13 +3831,13 @@
         <v>2041</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T15" s="18">
         <v>119682059</v>
       </c>
       <c r="U15" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V15" s="7">
         <v>43.186100000000003</v>
@@ -4622,52 +3846,51 @@
         <v>0.99039999999999995</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y15" s="15" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="Z15" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA15" s="15"/>
-      <c r="AB15" s="25" t="s">
-        <v>348</v>
+        <v>461</v>
+      </c>
+      <c r="AA15" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="AB15" s="15" t="s">
+        <v>295</v>
       </c>
       <c r="AC15" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="AD15" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="AE15" s="70" t="s">
-        <v>498</v>
+        <v>481</v>
+      </c>
+      <c r="AD15" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>358</v>
+        <v>306</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I16" s="21">
         <v>1.2</v>
@@ -4676,10 +3899,10 @@
         <v>1.2</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M16" s="21">
         <v>12</v>
@@ -4688,7 +3911,7 @@
         <v>12</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P16" s="13">
         <v>2025</v>
@@ -4700,13 +3923,13 @@
         <v>2042</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T16" s="14">
         <v>146415990</v>
       </c>
       <c r="U16" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V16" s="5">
         <v>45.290985428950698</v>
@@ -4715,51 +3938,48 @@
         <v>25.1109549184484</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>361</v>
+        <v>309</v>
       </c>
       <c r="Z16" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA16" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="AB16" s="25" t="s">
-        <v>357</v>
+        <v>461</v>
+      </c>
+      <c r="AA16" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>307</v>
       </c>
       <c r="AC16" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="AD16" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="AE16" s="48" t="s">
-        <v>499</v>
+        <v>308</v>
+      </c>
+      <c r="AD16" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="H17" s="30">
         <v>4.5999999999999999E-3</v>
@@ -4771,7 +3991,7 @@
         <v>4.5999999999999999E-3</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L17" s="31">
         <v>4.5689E-2</v>
@@ -4783,7 +4003,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P17" s="13">
         <v>2024</v>
@@ -4795,13 +4015,13 @@
         <v>2031</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T17" s="14">
         <v>30497000</v>
       </c>
       <c r="U17" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V17" s="4">
         <v>51.870851200822599</v>
@@ -4810,51 +4030,48 @@
         <v>4.30094696894741</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>365</v>
+        <v>313</v>
       </c>
       <c r="Z17" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA17" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB17" s="6" t="s">
-        <v>215</v>
+        <v>461</v>
+      </c>
+      <c r="AA17" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB17" s="11" t="s">
+        <v>311</v>
       </c>
       <c r="AC17" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="AD17" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="AE17" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD17" s="45" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="H18" s="21">
         <v>1.3</v>
@@ -4866,7 +4083,7 @@
         <v>1.3</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L18" s="21">
         <v>12.56</v>
@@ -4878,7 +4095,7 @@
         <v>13</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P18" s="13">
         <v>2025</v>
@@ -4890,13 +4107,13 @@
         <v>2040</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T18" s="14">
         <v>157000000</v>
       </c>
       <c r="U18" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V18" s="5">
         <v>52.489100000000001</v>
@@ -4905,51 +4122,48 @@
         <v>13.836399999999999</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA18" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB18" s="6" t="s">
-        <v>169</v>
+        <v>461</v>
+      </c>
+      <c r="AA18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="AC18" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="AD18" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="AE18" s="48" t="s">
-        <v>499</v>
+        <v>274</v>
+      </c>
+      <c r="AD18" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="57" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="D19" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H19" s="16">
         <v>0.02</v>
@@ -4958,7 +4172,7 @@
         <v>0.02</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K19" s="22">
         <v>0.02</v>
@@ -4970,7 +4184,7 @@
         <v>0.2</v>
       </c>
       <c r="N19" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O19" s="22">
         <v>0.2</v>
@@ -4985,13 +4199,13 @@
         <v>2036</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T19" s="18">
         <v>4265136</v>
       </c>
       <c r="U19" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V19" s="7">
         <v>50.569000000000003</v>
@@ -5000,75 +4214,72 @@
         <v>5.359</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y19" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z19" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="AA19" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB19" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC19" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="Z19" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA19" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB19" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="AC19" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD19" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE19" s="45" t="s">
+      <c r="AD19" s="45" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>507</v>
+        <v>455</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>312</v>
+        <v>261</v>
       </c>
       <c r="H20" s="16">
         <v>2.11</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J20" s="22">
         <v>2.11</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L20" s="22">
         <v>21.1</v>
       </c>
       <c r="M20" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N20" s="22">
         <v>21.1</v>
       </c>
       <c r="O20" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P20" s="17">
         <v>2023</v>
@@ -5080,7 +4291,7 @@
         <v>2037</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T20" s="18">
         <v>115000000</v>
@@ -5095,93 +4306,90 @@
         <v>-22.0167</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y20" s="15" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="Z20" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="AA20" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="AB20" s="8" t="s">
-        <v>200</v>
+        <v>463</v>
+      </c>
+      <c r="AA20" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB20" s="15" t="s">
+        <v>315</v>
       </c>
       <c r="AC20" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="AD20" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="AE20" s="50" t="s">
-        <v>500</v>
+        <v>316</v>
+      </c>
+      <c r="AD20" s="50" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="H21" s="32">
         <v>0.63600000000000001</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L21" s="27">
         <v>6.3620479999999997</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N21" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O21" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P21" s="17">
         <v>2025</v>
       </c>
       <c r="Q21" s="17" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="R21" s="17" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T21" s="18">
         <v>25400000</v>
       </c>
       <c r="U21" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V21" s="7">
         <v>41.352637812781921</v>
@@ -5190,51 +4398,48 @@
         <v>2.1794021596499702</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="Z21" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="AA21" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB21" s="25" t="s">
-        <v>371</v>
+        <v>463</v>
+      </c>
+      <c r="AA21" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB21" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="AC21" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="AD21" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="AE21" s="48" t="s">
-        <v>499</v>
+        <v>217</v>
+      </c>
+      <c r="AD21" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="H22" s="31">
         <v>1.7904E-2</v>
@@ -5243,7 +4448,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K22" s="21">
         <v>1.2999999999999999E-2</v>
@@ -5255,7 +4460,7 @@
         <v>0.13</v>
       </c>
       <c r="N22" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O22" s="21">
         <v>0.13</v>
@@ -5270,7 +4475,7 @@
         <v>2039</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T22" s="14">
         <v>4150000</v>
@@ -5285,51 +4490,48 @@
         <v>13.253440646806</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA22" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB22" s="25" t="s">
-        <v>372</v>
+        <v>461</v>
+      </c>
+      <c r="AA22" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>321</v>
       </c>
       <c r="AC22" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="AD22" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="AE22" s="70" t="s">
-        <v>498</v>
+        <v>322</v>
+      </c>
+      <c r="AD22" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="136.80000000000001" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" ht="136.80000000000001" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="H23" s="16">
         <v>0.56499999999999995</v>
@@ -5341,7 +4543,7 @@
         <v>0.5</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L23" s="22">
         <v>5.65</v>
@@ -5353,7 +4555,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P23" s="17">
         <v>2025</v>
@@ -5365,7 +4567,7 @@
         <v>2037</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T23" s="18">
         <v>48445901</v>
@@ -5380,51 +4582,48 @@
         <v>18.9154603437044</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y23" s="15" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
       <c r="Z23" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA23" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="AB23" s="25" t="s">
-        <v>377</v>
+        <v>461</v>
+      </c>
+      <c r="AA23" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB23" s="15" t="s">
+        <v>326</v>
       </c>
       <c r="AC23" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="AD23" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="AE23" s="48" t="s">
-        <v>499</v>
+        <v>327</v>
+      </c>
+      <c r="AD23" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="G24" s="40" t="s">
-        <v>387</v>
+        <v>335</v>
       </c>
       <c r="H24" s="16">
         <v>0.2</v>
@@ -5433,7 +4632,7 @@
         <v>0.35</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K24" s="22">
         <v>0.35</v>
@@ -5445,7 +4644,7 @@
         <v>3.5</v>
       </c>
       <c r="N24" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O24" s="22">
         <v>3.5</v>
@@ -5460,7 +4659,7 @@
         <v>2040</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T24" s="18">
         <v>40000000</v>
@@ -5475,51 +4674,48 @@
         <v>1.1835034670687401</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="Y24" s="15" t="s">
-        <v>390</v>
+        <v>338</v>
       </c>
       <c r="Z24" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA24" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB24" s="25" t="s">
-        <v>391</v>
+        <v>461</v>
+      </c>
+      <c r="AA24" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AB24" s="15" t="s">
+        <v>336</v>
       </c>
       <c r="AC24" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="AD24" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="AE24" s="71" t="s">
-        <v>497</v>
+        <v>337</v>
+      </c>
+      <c r="AD24" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
       <c r="H25" s="16">
         <v>1</v>
@@ -5531,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L25" s="22">
         <v>10</v>
@@ -5543,7 +4739,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P25" s="17">
         <v>2024</v>
@@ -5555,13 +4751,13 @@
         <v>2040</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T25" s="18">
         <v>216000000</v>
       </c>
       <c r="U25" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V25" s="7">
         <v>45.515127894849797</v>
@@ -5570,75 +4766,72 @@
         <v>10.343124922954001</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y25" s="15" t="s">
-        <v>522</v>
+        <v>470</v>
       </c>
       <c r="Z25" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA25" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="AB25" s="25" t="s">
-        <v>382</v>
+        <v>461</v>
+      </c>
+      <c r="AA25" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB25" s="15" t="s">
+        <v>331</v>
       </c>
       <c r="AC25" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="AD25" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="AE25" s="48" t="s">
-        <v>499</v>
+        <v>332</v>
+      </c>
+      <c r="AD25" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>520</v>
+        <v>468</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H26" s="32">
         <v>2.2800000000000001E-2</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L26" s="22">
         <v>0.228163</v>
       </c>
       <c r="M26" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O26" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P26" s="17">
         <v>2024</v>
@@ -5650,13 +4843,13 @@
         <v>2040</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T26" s="18">
         <v>40000000</v>
       </c>
       <c r="U26" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V26" s="3">
         <v>59.121267699503399</v>
@@ -5665,51 +4858,48 @@
         <v>9.6300609243118291</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y26" s="15" t="s">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="Z26" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA26" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="AB26" s="8" t="s">
-        <v>221</v>
+        <v>464</v>
+      </c>
+      <c r="AA26" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB26" s="15" t="s">
+        <v>466</v>
       </c>
       <c r="AC26" s="15" t="s">
-        <v>518</v>
-      </c>
-      <c r="AD26" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="AE26" s="51" t="s">
-        <v>496</v>
+        <v>467</v>
+      </c>
+      <c r="AD26" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="125.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>392</v>
+        <v>340</v>
       </c>
       <c r="H27" s="12">
         <v>0.23252429999999999</v>
@@ -5718,7 +4908,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K27" s="21">
         <v>0.19500000000000001</v>
@@ -5730,7 +4920,7 @@
         <v>1.95</v>
       </c>
       <c r="N27" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O27" s="21">
         <v>1.95</v>
@@ -5745,7 +4935,7 @@
         <v>2038</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T27" s="14">
         <v>115190750</v>
@@ -5760,51 +4950,48 @@
         <v>4.6899272399638701</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>395</v>
+        <v>343</v>
       </c>
       <c r="Z27" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA27" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB27" s="6" t="s">
-        <v>135</v>
+        <v>464</v>
+      </c>
+      <c r="AA27" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="AC27" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="AD27" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="AE27" s="71" t="s">
-        <v>497</v>
+        <v>342</v>
+      </c>
+      <c r="AD27" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H28" s="12">
         <v>0.26</v>
@@ -5813,7 +5000,7 @@
         <v>0.25</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K28" s="21">
         <v>0.25</v>
@@ -5825,7 +5012,7 @@
         <v>2.5</v>
       </c>
       <c r="N28" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O28" s="21">
         <v>2.5</v>
@@ -5840,13 +5027,13 @@
         <v>2038</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T28" s="14">
-        <v>40000000</v>
-      </c>
-      <c r="U28" s="14">
-        <v>700000000</v>
+        <v>54000000</v>
+      </c>
+      <c r="U28" s="18" t="s">
+        <v>244</v>
       </c>
       <c r="V28" s="5">
         <v>54.992185868676003</v>
@@ -5855,51 +5042,48 @@
         <v>11.8749856575691</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="Z28" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA28" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB28" s="25" t="s">
-        <v>397</v>
+        <v>464</v>
+      </c>
+      <c r="AA28" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>346</v>
       </c>
       <c r="AC28" s="11" t="s">
-        <v>398</v>
-      </c>
-      <c r="AD28" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="AE28" s="51" t="s">
-        <v>496</v>
+        <v>347</v>
+      </c>
+      <c r="AD28" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="H29" s="21">
         <v>1.5</v>
@@ -5911,7 +5095,7 @@
         <v>1.5</v>
       </c>
       <c r="K29" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L29" s="21">
         <v>15</v>
@@ -5923,7 +5107,7 @@
         <v>15</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P29" s="13">
         <v>2024</v>
@@ -5935,13 +5119,13 @@
         <v>2041</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T29" s="14">
         <v>228721666</v>
       </c>
       <c r="U29" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V29" s="5">
         <v>51.297800000000002</v>
@@ -5950,51 +5134,48 @@
         <v>7.0148000000000001</v>
       </c>
       <c r="X29" s="4" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>400</v>
+        <v>348</v>
       </c>
       <c r="Z29" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA29" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB29" s="6" t="s">
-        <v>160</v>
+        <v>461</v>
+      </c>
+      <c r="AA29" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB29" s="11" t="s">
+        <v>349</v>
       </c>
       <c r="AC29" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="AD29" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="AE29" s="51" t="s">
-        <v>496</v>
+        <v>350</v>
+      </c>
+      <c r="AD29" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>427</v>
+        <v>375</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="H30" s="32">
         <v>4.5999999999999999E-2</v>
@@ -6006,7 +5187,7 @@
         <v>0.16</v>
       </c>
       <c r="K30" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L30" s="16">
         <v>0.46373999999999999</v>
@@ -6018,7 +5199,7 @@
         <v>1.6</v>
       </c>
       <c r="O30" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P30" s="17">
         <v>2024</v>
@@ -6030,13 +5211,13 @@
         <v>2038</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T30" s="18">
         <v>29500000</v>
       </c>
       <c r="U30" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V30" s="3">
         <v>60.618241659279597</v>
@@ -6045,51 +5226,48 @@
         <v>16.891107915855802</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y30" s="15" t="s">
-        <v>426</v>
+        <v>374</v>
       </c>
       <c r="Z30" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA30" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="AB30" s="26" t="s">
-        <v>428</v>
+        <v>461</v>
+      </c>
+      <c r="AA30" s="26" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB30" s="15" t="s">
+        <v>377</v>
       </c>
       <c r="AC30" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="AD30" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="AE30" s="71" t="s">
-        <v>497</v>
+        <v>378</v>
+      </c>
+      <c r="AD30" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H31" s="16">
         <v>0.7</v>
@@ -6101,7 +5279,7 @@
         <v>0.7</v>
       </c>
       <c r="K31" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L31" s="22">
         <v>7.27</v>
@@ -6113,7 +5291,7 @@
         <v>7</v>
       </c>
       <c r="O31" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P31" s="17">
         <v>2024</v>
@@ -6125,13 +5303,13 @@
         <v>2040</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T31" s="18">
         <v>191000000</v>
       </c>
       <c r="U31" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V31" s="7">
         <v>51.618000000000002</v>
@@ -6140,51 +5318,48 @@
         <v>8.5100999999999996</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y31" s="15" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="Z31" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA31" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB31" s="38" t="s">
-        <v>164</v>
+        <v>461</v>
+      </c>
+      <c r="AA31" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB31" s="15" t="s">
+        <v>290</v>
       </c>
       <c r="AC31" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="AD31" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="AE31" s="51" t="s">
-        <v>496</v>
+        <v>291</v>
+      </c>
+      <c r="AD31" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="H32" s="16">
         <v>1</v>
@@ -6196,7 +5371,7 @@
         <v>1.2</v>
       </c>
       <c r="K32" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L32" s="22">
         <v>10</v>
@@ -6208,7 +5383,7 @@
         <v>12</v>
       </c>
       <c r="O32" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P32" s="17">
         <v>2022</v>
@@ -6220,7 +5395,7 @@
         <v>2037</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T32" s="18">
         <v>228210004</v>
@@ -6235,51 +5410,48 @@
         <v>17.989599999999999</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y32" s="15" t="s">
-        <v>403</v>
+        <v>351</v>
       </c>
       <c r="Z32" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA32" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB32" s="25" t="s">
-        <v>404</v>
+        <v>461</v>
+      </c>
+      <c r="AA32" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="AB32" s="15" t="s">
+        <v>276</v>
       </c>
       <c r="AC32" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="AD32" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="AE32" s="51" t="s">
-        <v>496</v>
+        <v>197</v>
+      </c>
+      <c r="AD32" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H33" s="20">
         <v>1.0045932</v>
@@ -6291,7 +5463,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="K33" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L33" s="12">
         <v>10.045932000000001</v>
@@ -6303,7 +5475,7 @@
         <v>11</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P33" s="13">
         <v>2023</v>
@@ -6315,7 +5487,7 @@
         <v>2038</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T33" s="14">
         <v>230000000</v>
@@ -6330,48 +5502,45 @@
         <v>3.9928129999999999</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Z33" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA33" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB33" s="25" t="s">
-        <v>407</v>
+        <v>461</v>
+      </c>
+      <c r="AA33" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB33" s="11" t="s">
+        <v>353</v>
       </c>
       <c r="AC33" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="AD33" s="11" t="s">
-        <v>406</v>
-      </c>
-      <c r="AE33" s="50" t="s">
-        <v>500</v>
+        <v>354</v>
+      </c>
+      <c r="AD33" s="50" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="12">
@@ -6381,7 +5550,7 @@
         <v>0.15</v>
       </c>
       <c r="J34" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K34" s="21">
         <v>0.15</v>
@@ -6393,7 +5562,7 @@
         <v>1.5</v>
       </c>
       <c r="N34" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O34" s="21">
         <v>1.5</v>
@@ -6408,13 +5577,13 @@
         <v>2038</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T34" s="14">
         <v>122900000</v>
       </c>
       <c r="U34" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V34" s="4">
         <v>43.151000000000003</v>
@@ -6423,63 +5592,60 @@
         <v>-7.6859999999999999</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>408</v>
+        <v>356</v>
       </c>
       <c r="Z34" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA34" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="AB34" s="25" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA34" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB34" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="AC34" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="AD34" s="70" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" ht="114" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="AC34" s="11" t="s">
-        <v>409</v>
-      </c>
-      <c r="AD34" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="AE34" s="70" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" ht="114" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>309</v>
+        <v>258</v>
       </c>
       <c r="H35" s="16">
         <v>0.28144999999999998</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J35" s="22">
         <v>0.4</v>
       </c>
       <c r="K35" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L35" s="27">
         <v>2.8</v>
@@ -6491,7 +5657,7 @@
         <v>4</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P35" s="17">
         <v>2024</v>
@@ -6503,7 +5669,7 @@
         <v>2034</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T35" s="18">
         <v>41041661</v>
@@ -6518,75 +5684,72 @@
         <v>8.4393999999999991</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y35" s="15" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="Z35" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="AA35" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB35" s="25" t="s">
-        <v>411</v>
+        <v>463</v>
+      </c>
+      <c r="AA35" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB35" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="AC35" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="AD35" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="AE35" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="AD35" s="45" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" s="42" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>511</v>
+        <v>459</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H36" s="16">
         <v>1.28</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J36" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K36" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L36" s="22">
         <v>12.8</v>
       </c>
       <c r="M36" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N36" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O36" s="37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P36" s="17">
         <v>2025</v>
@@ -6598,13 +5761,13 @@
         <v>2039</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T36" s="18">
         <v>159000000</v>
       </c>
       <c r="U36" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V36" s="7">
         <v>51.1339349</v>
@@ -6613,75 +5776,72 @@
         <v>3.7766611000000001</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y36" s="15" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="Z36" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA36" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB36" s="25" t="s">
-        <v>418</v>
+        <v>461</v>
+      </c>
+      <c r="AA36" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="AB36" s="15" t="s">
+        <v>361</v>
       </c>
       <c r="AC36" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="AD36" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="AE36" s="51" t="s">
-        <v>496</v>
+        <v>362</v>
+      </c>
+      <c r="AD36" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B37" s="42" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="H37" s="32">
         <v>5.0046999999999999E-3</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J37" s="22">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="K37" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L37" s="27">
         <v>5.0047000000000001E-2</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N37" s="32">
         <v>5.1711E-2</v>
       </c>
       <c r="O37" s="36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P37" s="17">
         <v>2026</v>
@@ -6693,13 +5853,13 @@
         <v>2038</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T37" s="18">
         <v>26498650</v>
       </c>
       <c r="U37" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V37" s="7">
         <v>50.529000000000003</v>
@@ -6708,51 +5868,48 @@
         <v>18.047000000000001</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y37" s="15" t="s">
-        <v>244</v>
+        <v>203</v>
       </c>
       <c r="Z37" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="AA37" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB37" s="25" t="s">
-        <v>417</v>
+        <v>463</v>
+      </c>
+      <c r="AA37" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="AB37" s="15" t="s">
+        <v>363</v>
       </c>
       <c r="AC37" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="AD37" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="AE37" s="51" t="s">
-        <v>496</v>
+        <v>364</v>
+      </c>
+      <c r="AD37" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" s="42" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="H38" s="16">
         <v>0.68</v>
@@ -6764,7 +5921,7 @@
         <v>1.9</v>
       </c>
       <c r="K38" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L38" s="22">
         <v>6.8</v>
@@ -6776,7 +5933,7 @@
         <v>19</v>
       </c>
       <c r="O38" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P38" s="17">
         <v>2025</v>
@@ -6788,13 +5945,13 @@
         <v>2039</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T38" s="18">
         <v>234000000</v>
       </c>
       <c r="U38" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V38" s="7">
         <v>38.129899999999999</v>
@@ -6803,48 +5960,45 @@
         <v>23.527000000000001</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y38" s="15" t="s">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="Z38" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA38" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB38" s="25" t="s">
-        <v>340</v>
+        <v>461</v>
+      </c>
+      <c r="AA38" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB38" s="15" t="s">
+        <v>286</v>
       </c>
       <c r="AC38" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="AD38" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="AE38" s="71" t="s">
-        <v>497</v>
+        <v>287</v>
+      </c>
+      <c r="AD38" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="12">
@@ -6857,7 +6011,7 @@
         <v>0.2</v>
       </c>
       <c r="K39" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L39" s="21">
         <v>2</v>
@@ -6869,7 +6023,7 @@
         <v>2</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P39" s="13">
         <v>2025</v>
@@ -6881,7 +6035,7 @@
         <v>2038</v>
       </c>
       <c r="S39" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T39" s="14">
         <v>54000000</v>
@@ -6896,51 +6050,48 @@
         <v>12.7671053619066</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="Y39" s="11" t="s">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="Z39" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA39" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="AB39" s="25" t="s">
-        <v>419</v>
+        <v>461</v>
+      </c>
+      <c r="AA39" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB39" s="11" t="s">
+        <v>475</v>
       </c>
       <c r="AC39" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="AD39" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="AE39" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD39" s="46" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" s="41" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="H40" s="12">
         <v>0.85799999999999998</v>
@@ -6976,13 +6127,13 @@
         <v>2039</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T40" s="14">
         <v>127000000</v>
       </c>
       <c r="U40" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V40" s="5">
         <v>37.916800000000002</v>
@@ -6991,51 +6142,48 @@
         <v>23.069400000000002</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y40" s="11" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="Z40" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA40" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB40" s="25" t="s">
-        <v>184</v>
+        <v>461</v>
+      </c>
+      <c r="AA40" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB40" s="11" t="s">
+        <v>368</v>
       </c>
       <c r="AC40" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="AD40" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="AE40" s="70" t="s">
-        <v>498</v>
+        <v>369</v>
+      </c>
+      <c r="AD40" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="C41" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="D41" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="H41" s="12">
         <v>1.4</v>
@@ -7047,7 +6195,7 @@
         <v>1.4</v>
       </c>
       <c r="K41" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L41" s="21">
         <v>14</v>
@@ -7059,7 +6207,7 @@
         <v>14</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P41" s="13">
         <v>2020</v>
@@ -7071,13 +6219,13 @@
         <v>2039</v>
       </c>
       <c r="S41" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T41" s="14">
         <v>356900000</v>
       </c>
-      <c r="U41" s="14">
-        <v>900000000</v>
+      <c r="U41" s="18" t="s">
+        <v>244</v>
       </c>
       <c r="V41" s="5">
         <v>51.368588000000003</v>
@@ -7086,51 +6234,48 @@
         <v>4.2713660000000004</v>
       </c>
       <c r="X41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y41" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="Y41" s="11" t="s">
-        <v>59</v>
-      </c>
       <c r="Z41" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA41" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB41" s="25" t="s">
-        <v>424</v>
+        <v>461</v>
+      </c>
+      <c r="AA41" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB41" s="11" t="s">
+        <v>370</v>
       </c>
       <c r="AC41" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="AD41" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="AE41" s="50" t="s">
-        <v>500</v>
+        <v>371</v>
+      </c>
+      <c r="AD41" s="50" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="42" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H42" s="16">
         <v>0.36599999999999999</v>
@@ -7142,7 +6287,7 @@
         <v>0.36599999999999999</v>
       </c>
       <c r="K42" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L42" s="22">
         <v>3.7</v>
@@ -7154,7 +6299,7 @@
         <v>3.66</v>
       </c>
       <c r="O42" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P42" s="17">
         <v>2023</v>
@@ -7166,13 +6311,13 @@
         <v>2038</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T42" s="18">
         <v>117000000</v>
       </c>
       <c r="U42" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V42" s="7">
         <v>44.968299999999999</v>
@@ -7181,75 +6326,72 @@
         <v>14.1221</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y42" s="15" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Z42" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA42" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB42" s="25" t="s">
-        <v>332</v>
+        <v>461</v>
+      </c>
+      <c r="AA42" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="AB42" s="15" t="s">
+        <v>449</v>
       </c>
       <c r="AC42" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="AD42" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="AE42" s="51" t="s">
-        <v>496</v>
+        <v>280</v>
+      </c>
+      <c r="AD42" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>313</v>
+        <v>262</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>314</v>
+        <v>263</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>509</v>
+        <v>457</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J43" s="22">
         <v>5</v>
       </c>
       <c r="K43" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L43" s="28">
         <v>31.381101000000001</v>
       </c>
       <c r="M43" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N43" s="22">
         <v>50</v>
       </c>
       <c r="O43" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P43" s="17">
         <v>2025</v>
@@ -7261,13 +6403,13 @@
         <v>2039</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T43" s="18">
         <v>118000000</v>
       </c>
       <c r="U43" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V43" s="7">
         <v>51.976999999999997</v>
@@ -7276,51 +6418,48 @@
         <v>4.05</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y43" s="15" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="Z43" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="AA43" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB43" s="26" t="s">
-        <v>315</v>
+        <v>465</v>
+      </c>
+      <c r="AA43" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB43" s="15" t="s">
+        <v>265</v>
       </c>
       <c r="AC43" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="AD43" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="AE43" s="51" t="s">
-        <v>496</v>
+        <v>266</v>
+      </c>
+      <c r="AD43" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="68.400000000000006" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B44" s="42" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H44" s="16">
         <v>7.0000000000000007E-2</v>
@@ -7332,7 +6471,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K44" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L44" s="22">
         <v>0.7</v>
@@ -7344,7 +6483,7 @@
         <v>0.7</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P44" s="17">
         <v>2026</v>
@@ -7356,13 +6495,13 @@
         <v>2041</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T44" s="18">
         <v>36000000</v>
       </c>
       <c r="U44" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V44" s="7">
         <v>50.406342306737002</v>
@@ -7371,75 +6510,72 @@
         <v>4.6321740189769196</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y44" s="15" t="s">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="Z44" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA44" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB44" s="25" t="s">
-        <v>432</v>
+        <v>461</v>
+      </c>
+      <c r="AA44" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="AB44" s="15" t="s">
+        <v>381</v>
       </c>
       <c r="AC44" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="AD44" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="AE44" s="51" t="s">
-        <v>496</v>
+        <v>382</v>
+      </c>
+      <c r="AD44" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B45" s="42" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>512</v>
+        <v>460</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>436</v>
+        <v>384</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H45" s="16">
         <v>0.04</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L45" s="16">
         <v>0.41452</v>
       </c>
       <c r="M45" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N45" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O45" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P45" s="17">
         <v>2025</v>
@@ -7451,13 +6587,13 @@
         <v>2038</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T45" s="18">
         <v>13000000</v>
       </c>
       <c r="U45" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V45" s="3">
         <v>59.2181</v>
@@ -7466,54 +6602,51 @@
         <v>10.9298</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y45" s="15" t="s">
-        <v>437</v>
+        <v>385</v>
       </c>
       <c r="Z45" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA45" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="AB45" s="25" t="s">
-        <v>435</v>
+        <v>159</v>
+      </c>
+      <c r="AA45" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="AB45" s="15" t="s">
+        <v>386</v>
       </c>
       <c r="AC45" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="AD45" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="AE45" s="70" t="s">
-        <v>498</v>
+        <v>387</v>
+      </c>
+      <c r="AD45" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I46" s="21">
         <v>1</v>
@@ -7522,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L46" s="29">
         <v>6.8833489999999999</v>
@@ -7534,7 +6667,7 @@
         <v>10</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P46" s="13">
         <v>2024</v>
@@ -7546,7 +6679,7 @@
         <v>2039</v>
       </c>
       <c r="S46" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T46" s="14">
         <v>124268490</v>
@@ -7561,75 +6694,72 @@
         <v>24.060400000000001</v>
       </c>
       <c r="X46" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y46" s="11" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="Z46" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA46" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB46" s="25" t="s">
-        <v>336</v>
+        <v>461</v>
+      </c>
+      <c r="AA46" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB46" s="11" t="s">
+        <v>283</v>
       </c>
       <c r="AC46" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="AD46" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="AE46" s="70" t="s">
-        <v>498</v>
+        <v>284</v>
+      </c>
+      <c r="AD46" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B47" s="41" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>440</v>
+        <v>388</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
       <c r="H47" s="31">
         <v>1.55E-2</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="J47" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K47" s="21" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="L47" s="21">
         <v>0.155</v>
       </c>
       <c r="M47" s="21" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="N47" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="P47" s="13">
         <v>2026</v>
@@ -7641,13 +6771,13 @@
         <v>2038</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T47" s="14">
         <v>8600000</v>
       </c>
-      <c r="U47" s="14">
-        <v>72000000</v>
+      <c r="U47" s="18" t="s">
+        <v>244</v>
       </c>
       <c r="V47" s="5">
         <v>58.418889999999998</v>
@@ -7656,75 +6786,72 @@
         <v>24.47278</v>
       </c>
       <c r="X47" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y47" s="11" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="Z47" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA47" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB47" s="25" t="s">
-        <v>444</v>
+        <v>464</v>
+      </c>
+      <c r="AA47" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="AB47" s="11" t="s">
+        <v>390</v>
       </c>
       <c r="AC47" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="AD47" s="11" t="s">
-        <v>443</v>
-      </c>
-      <c r="AE47" s="48" t="s">
-        <v>499</v>
+        <v>391</v>
+      </c>
+      <c r="AD47" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" s="42" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>445</v>
+        <v>393</v>
       </c>
       <c r="H48" s="16">
         <v>0.40600000000000003</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K48" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L48" s="22">
         <v>4.0599999999999996</v>
       </c>
       <c r="M48" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N48" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O48" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P48" s="17">
         <v>2023</v>
@@ -7736,13 +6863,13 @@
         <v>2037</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T48" s="18">
         <v>97000000</v>
       </c>
       <c r="U48" s="18" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="V48" s="3">
         <v>58.099057767351503</v>
@@ -7751,75 +6878,72 @@
         <v>11.861499508001399</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y48" s="15" t="s">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="Z48" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA48" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="AB48" s="26" t="s">
-        <v>286</v>
+        <v>461</v>
+      </c>
+      <c r="AA48" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB48" s="15" t="s">
+        <v>394</v>
       </c>
       <c r="AC48" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="AD48" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="AE48" s="71" t="s">
-        <v>497</v>
+        <v>234</v>
+      </c>
+      <c r="AD48" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B49" s="42" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="H49" s="32">
         <v>6.7077999999999999E-2</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K49" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L49" s="27">
         <v>0.67078000000000004</v>
       </c>
       <c r="M49" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N49" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O49" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P49" s="17">
         <v>2026</v>
@@ -7831,13 +6955,13 @@
         <v>2040</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T49" s="18">
         <v>40000000</v>
       </c>
       <c r="U49" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V49" s="7">
         <v>56.787056035485499</v>
@@ -7846,51 +6970,48 @@
         <v>9.3873420638001708</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y49" s="15" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="Z49" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA49" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB49" s="25" t="s">
-        <v>448</v>
+        <v>461</v>
+      </c>
+      <c r="AA49" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="AB49" s="15" t="s">
+        <v>397</v>
       </c>
       <c r="AC49" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="AD49" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="AE49" s="70" t="s">
-        <v>498</v>
+        <v>398</v>
+      </c>
+      <c r="AD49" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B50" s="42" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="H50" s="16">
         <v>0.24099999999999999</v>
@@ -7914,13 +7035,13 @@
         <v>2036</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T50" s="18">
         <v>19458418</v>
       </c>
       <c r="U50" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V50" s="7">
         <v>48.096166502584701</v>
@@ -7929,51 +7050,48 @@
         <v>11.0247947737657</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y50" s="15" t="s">
-        <v>451</v>
+        <v>399</v>
       </c>
       <c r="Z50" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA50" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB50" s="25" t="s">
-        <v>452</v>
+        <v>159</v>
+      </c>
+      <c r="AA50" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="AB50" s="15" t="s">
+        <v>401</v>
       </c>
       <c r="AC50" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="AD50" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="AE50" s="48" t="s">
-        <v>499</v>
+        <v>402</v>
+      </c>
+      <c r="AD50" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B51" s="41" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>455</v>
+        <v>403</v>
       </c>
       <c r="H51" s="12">
         <v>0.27411429999999998</v>
@@ -7982,7 +7100,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K51" s="33">
         <v>0.33400000000000002</v>
@@ -7994,7 +7112,7 @@
         <v>3.34</v>
       </c>
       <c r="N51" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O51" s="21">
         <v>3.34</v>
@@ -8009,7 +7127,7 @@
         <v>2041</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T51" s="14">
         <v>31982730</v>
@@ -8024,51 +7142,48 @@
         <v>-0.82662848923265397</v>
       </c>
       <c r="X51" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y51" s="11" t="s">
-        <v>459</v>
+        <v>407</v>
       </c>
       <c r="Z51" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA51" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB51" s="25" t="s">
-        <v>456</v>
+        <v>461</v>
+      </c>
+      <c r="AA51" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="AB51" s="11" t="s">
+        <v>405</v>
       </c>
       <c r="AC51" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="AD51" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="AE51" s="48" t="s">
-        <v>499</v>
+        <v>406</v>
+      </c>
+      <c r="AD51" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="42" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H52" s="16">
         <v>0.4</v>
@@ -8080,7 +7195,7 @@
         <v>0.4</v>
       </c>
       <c r="K52" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L52" s="22">
         <v>4</v>
@@ -8092,25 +7207,25 @@
         <v>4</v>
       </c>
       <c r="O52" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P52" s="17">
         <v>2022</v>
       </c>
       <c r="Q52" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="R52" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="S52" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="R52" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="T52" s="18">
         <v>88286266</v>
       </c>
       <c r="U52" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V52" s="7">
         <v>60.306100000000001</v>
@@ -8119,51 +7234,48 @@
         <v>25.498100000000001</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y52" s="15" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="Z52" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA52" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB52" s="25" t="s">
-        <v>123</v>
+        <v>461</v>
+      </c>
+      <c r="AA52" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB52" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="AC52" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD52" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="AE52" s="50" t="s">
-        <v>500</v>
+        <v>112</v>
+      </c>
+      <c r="AD52" s="50" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="114" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" ht="114" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>461</v>
+        <v>409</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>464</v>
+        <v>412</v>
       </c>
       <c r="H53" s="12">
         <v>1.72E-2</v>
@@ -8175,7 +7287,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="K53" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L53" s="21">
         <v>0.17199999999999999</v>
@@ -8187,7 +7299,7 @@
         <v>0.15</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P53" s="13">
         <v>2021</v>
@@ -8199,13 +7311,13 @@
         <v>2035</v>
       </c>
       <c r="S53" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T53" s="14">
         <v>3867988</v>
       </c>
       <c r="U53" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V53" s="5">
         <v>64.037112316635401</v>
@@ -8214,51 +7326,48 @@
         <v>-21.4004875161618</v>
       </c>
       <c r="X53" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y53" s="11" t="s">
-        <v>462</v>
+        <v>410</v>
       </c>
       <c r="Z53" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA53" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB53" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
+      </c>
+      <c r="AA53" s="25" t="s">
+        <v>411</v>
+      </c>
+      <c r="AB53" s="11" t="s">
+        <v>413</v>
       </c>
       <c r="AC53" s="11" t="s">
-        <v>465</v>
-      </c>
-      <c r="AD53" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="AE53" s="44" t="s">
+        <v>414</v>
+      </c>
+      <c r="AD53" s="44" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>521</v>
+        <v>469</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>467</v>
+        <v>415</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="H54" s="12">
         <v>0.16981750000000001</v>
@@ -8294,13 +7403,13 @@
         <v>2041</v>
       </c>
       <c r="S54" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T54" s="14">
         <v>40000000</v>
       </c>
       <c r="U54" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V54" s="5">
         <v>59.127044152710397</v>
@@ -8309,75 +7418,72 @@
         <v>9.6218923201747906</v>
       </c>
       <c r="X54" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y54" s="11" t="s">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="Z54" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA54" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="AB54" s="25" t="s">
-        <v>469</v>
+        <v>461</v>
+      </c>
+      <c r="AA54" s="25" t="s">
+        <v>417</v>
+      </c>
+      <c r="AB54" s="11" t="s">
+        <v>418</v>
       </c>
       <c r="AC54" s="11" t="s">
-        <v>470</v>
-      </c>
-      <c r="AD54" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="AE54" s="48" t="s">
-        <v>499</v>
+        <v>419</v>
+      </c>
+      <c r="AD54" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="125.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55" s="41" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>314</v>
+        <v>263</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>509</v>
+        <v>457</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H55" s="12">
         <v>4.2</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J55" s="21">
         <v>4.2750000000000004</v>
       </c>
       <c r="K55" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L55" s="21">
         <v>42.05</v>
       </c>
       <c r="M55" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N55" s="21">
         <v>42.75</v>
       </c>
       <c r="O55" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P55" s="13">
         <v>2025</v>
@@ -8389,13 +7495,13 @@
         <v>2039</v>
       </c>
       <c r="S55" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T55" s="14">
         <v>225000000</v>
       </c>
       <c r="U55" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V55" s="4">
         <v>57.788622470324199</v>
@@ -8404,49 +7510,48 @@
         <v>4.4366416948962097</v>
       </c>
       <c r="X55" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y55" s="11" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
       <c r="Z55" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="AA55" s="11"/>
-      <c r="AB55" s="25" t="s">
-        <v>223</v>
+        <v>465</v>
+      </c>
+      <c r="AA55" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB55" s="11" t="s">
+        <v>271</v>
       </c>
       <c r="AC55" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="AD55" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="AE55" s="51" t="s">
-        <v>496</v>
+        <v>272</v>
+      </c>
+      <c r="AD55" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B56" s="41" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>475</v>
+        <v>423</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>476</v>
+        <v>424</v>
       </c>
       <c r="H56" s="12">
         <v>0.17</v>
@@ -8455,7 +7560,7 @@
         <v>0.16</v>
       </c>
       <c r="J56" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K56" s="21">
         <v>0.16</v>
@@ -8467,7 +7572,7 @@
         <v>1.6</v>
       </c>
       <c r="N56" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O56" s="21">
         <v>1.6</v>
@@ -8482,7 +7587,7 @@
         <v>2042</v>
       </c>
       <c r="S56" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T56" s="14">
         <v>40000000</v>
@@ -8497,75 +7602,72 @@
         <v>-2.1625372580756901</v>
       </c>
       <c r="X56" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y56" s="11" t="s">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="Z56" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="AA56" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB56" s="25" t="s">
-        <v>478</v>
+        <v>462</v>
+      </c>
+      <c r="AA56" s="25" t="s">
+        <v>426</v>
+      </c>
+      <c r="AB56" s="11" t="s">
+        <v>427</v>
       </c>
       <c r="AC56" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="AD56" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="AE56" s="70" t="s">
-        <v>498</v>
+        <v>428</v>
+      </c>
+      <c r="AD56" s="70" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>259</v>
+        <v>214</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>314</v>
+        <v>263</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>509</v>
+        <v>457</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>481</v>
+        <v>429</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>481</v>
+        <v>429</v>
       </c>
       <c r="H57" s="12">
         <v>2</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J57" s="21">
         <v>2</v>
       </c>
       <c r="K57" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L57" s="21">
         <v>20</v>
       </c>
       <c r="M57" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N57" s="21">
         <v>54</v>
       </c>
       <c r="O57" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P57" s="13">
         <v>2025</v>
@@ -8577,13 +7679,13 @@
         <v>2041</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T57" s="14">
         <v>205061582</v>
       </c>
       <c r="U57" s="14" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V57" s="5">
         <v>40.8482802817337</v>
@@ -8592,75 +7694,72 @@
         <v>1.6966936283218199</v>
       </c>
       <c r="X57" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y57" s="11" t="s">
-        <v>482</v>
+        <v>430</v>
       </c>
       <c r="Z57" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="AA57" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB57" s="6" t="s">
-        <v>261</v>
+        <v>465</v>
+      </c>
+      <c r="AA57" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB57" s="11" t="s">
+        <v>431</v>
       </c>
       <c r="AC57" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="AD57" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="AE57" s="51" t="s">
-        <v>496</v>
+        <v>432</v>
+      </c>
+      <c r="AD57" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B58" s="41" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>512</v>
+        <v>460</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="H58" s="31">
         <v>7.8E-2</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J58" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K58" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L58" s="35">
         <v>0.784304</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N58" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O58" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P58" s="13">
         <v>2025</v>
@@ -8672,7 +7771,7 @@
         <v>2040</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T58" s="14">
         <v>29401945</v>
@@ -8687,51 +7786,48 @@
         <v>23.058033778902399</v>
       </c>
       <c r="X58" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Y58" s="11" t="s">
-        <v>495</v>
+        <v>443</v>
       </c>
       <c r="Z58" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA58" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="AB58" s="25" t="s">
-        <v>492</v>
+        <v>159</v>
+      </c>
+      <c r="AA58" s="25" t="s">
+        <v>440</v>
+      </c>
+      <c r="AB58" s="11" t="s">
+        <v>441</v>
       </c>
       <c r="AC58" s="11" t="s">
-        <v>493</v>
-      </c>
-      <c r="AD58" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="AE58" s="51" t="s">
-        <v>496</v>
+        <v>442</v>
+      </c>
+      <c r="AD58" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="68.400000000000006" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" s="42" t="s">
-        <v>254</v>
+        <v>210</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="H59" s="32">
         <v>8.5999999999999993E-2</v>
@@ -8740,7 +7836,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="J59" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K59" s="22">
         <v>5.6000000000000001E-2</v>
@@ -8752,7 +7848,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="N59" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O59" s="22">
         <v>0.56000000000000005</v>
@@ -8767,7 +7863,7 @@
         <v>2038</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T59" s="18">
         <v>48846672</v>
@@ -8782,51 +7878,48 @@
         <v>-8.2351799999999997</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y59" s="15" t="s">
-        <v>485</v>
+        <v>433</v>
       </c>
       <c r="Z59" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA59" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB59" s="8" t="s">
-        <v>257</v>
+        <v>464</v>
+      </c>
+      <c r="AA59" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB59" s="15" t="s">
+        <v>434</v>
       </c>
       <c r="AC59" s="15" t="s">
-        <v>486</v>
-      </c>
-      <c r="AD59" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="AE59" s="71" t="s">
-        <v>497</v>
+        <v>213</v>
+      </c>
+      <c r="AD59" s="71" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B60" s="42" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="H60" s="16">
         <v>1.2</v>
@@ -8838,7 +7931,7 @@
         <v>1.2</v>
       </c>
       <c r="K60" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L60" s="22">
         <v>12</v>
@@ -8850,7 +7943,7 @@
         <v>12</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P60" s="17">
         <v>2026</v>
@@ -8862,7 +7955,7 @@
         <v>2040</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T60" s="18">
         <v>149998000</v>
@@ -8877,75 +7970,72 @@
         <v>5.4216006729600599</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y60" s="15" t="s">
-        <v>527</v>
+        <v>474</v>
       </c>
       <c r="Z60" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="AA60" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="AB60" s="25" t="s">
-        <v>487</v>
+        <v>461</v>
+      </c>
+      <c r="AA60" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="AB60" s="15" t="s">
+        <v>436</v>
       </c>
       <c r="AC60" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="AD60" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE60" s="51" t="s">
-        <v>496</v>
+        <v>132</v>
+      </c>
+      <c r="AD60" s="51" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B61" s="42" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="H61" s="16">
         <v>0.1</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J61" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L61" s="22">
         <v>1</v>
       </c>
       <c r="M61" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N61" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O61" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P61" s="17">
         <v>2026</v>
@@ -8957,13 +8047,13 @@
         <v>2040</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T61" s="18">
         <v>26200000</v>
       </c>
       <c r="U61" s="18" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="V61" s="7">
         <v>59.242157075260003</v>
@@ -8972,93 +8062,90 @@
         <v>11.046906259539099</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="Y61" s="15" t="s">
-        <v>489</v>
+        <v>437</v>
       </c>
       <c r="Z61" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA61" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB61" s="25" t="s">
-        <v>490</v>
+        <v>159</v>
+      </c>
+      <c r="AA61" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="AB61" s="15" t="s">
+        <v>439</v>
       </c>
       <c r="AC61" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="AD61" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="AE61" s="48" t="s">
-        <v>499</v>
+        <v>193</v>
+      </c>
+      <c r="AD61" s="48" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE61" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AD61" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <hyperlinks>
-    <hyperlink ref="AB2" r:id="rId1" xr:uid="{732997D1-2192-49C8-AD3C-37FF6D9C50FB}"/>
-    <hyperlink ref="AB3" r:id="rId2" xr:uid="{6D3D26FD-6440-42D0-915E-7DC5B096846A}"/>
-    <hyperlink ref="AB4" r:id="rId3" xr:uid="{F06EF75F-03E5-4FF4-94E9-B13CD521BCC4}"/>
-    <hyperlink ref="AB5" r:id="rId4" xr:uid="{10E71439-6E78-4DC8-94BA-708278AA49E1}"/>
-    <hyperlink ref="AB6" r:id="rId5" xr:uid="{AD5083CF-D35A-4E44-ACD1-0096D32B2035}"/>
-    <hyperlink ref="AB7" r:id="rId6" xr:uid="{EF1C82B1-E495-49BC-9C7C-5A819C6B4157}"/>
-    <hyperlink ref="AB8" r:id="rId7" xr:uid="{1500CDB3-2564-419A-83A6-D6A2AD106DFA}"/>
-    <hyperlink ref="AB9" r:id="rId8" xr:uid="{AD24B4CC-D138-4A10-8B1B-9F104C1F0E04}"/>
-    <hyperlink ref="AB10" r:id="rId9" xr:uid="{E24D7C14-029E-4A47-A026-A1CABC412744}"/>
-    <hyperlink ref="AB11" r:id="rId10" xr:uid="{431278EF-EBDB-42AE-9F9B-9121762AB4BD}"/>
-    <hyperlink ref="AB12" r:id="rId11" xr:uid="{D47AED6B-D37D-4CE8-8AC3-869FE4E73A4C}"/>
-    <hyperlink ref="AB13" r:id="rId12" xr:uid="{0B57C4D9-36D2-465E-AB07-1DEFA76CB325}"/>
-    <hyperlink ref="AB14" r:id="rId13" xr:uid="{422B11F8-5AAA-46B3-A9F4-8400C1BA175D}"/>
-    <hyperlink ref="AB15" r:id="rId14" xr:uid="{9F8FD200-53B5-427A-AAC6-66661E99DD06}"/>
-    <hyperlink ref="AB16" r:id="rId15" xr:uid="{27AE20A9-9999-4A9F-BF34-A0F451238BA4}"/>
-    <hyperlink ref="AB17" r:id="rId16" xr:uid="{21A72ADE-0573-4B53-8DDD-458141853D21}"/>
-    <hyperlink ref="AB18" r:id="rId17" xr:uid="{2BF32E9F-6E2B-41AA-B458-BC18EEEBE8EE}"/>
-    <hyperlink ref="AB19" r:id="rId18" xr:uid="{ABBFF699-C458-4BB8-B468-ED1B6F009F84}"/>
-    <hyperlink ref="AB20" r:id="rId19" xr:uid="{AEDFB273-5228-48A3-BB78-4CBF04C03206}"/>
-    <hyperlink ref="AB21" r:id="rId20" xr:uid="{76CBB5AF-C783-4C7E-BA94-D9457FBA37E0}"/>
-    <hyperlink ref="AB22" r:id="rId21" xr:uid="{C799105C-AEBB-4D14-93E9-22873AEDF926}"/>
-    <hyperlink ref="AB23" r:id="rId22" xr:uid="{3CA1EB14-2983-484B-9094-16A511911CBB}"/>
-    <hyperlink ref="AB24" r:id="rId23" xr:uid="{960B7DAB-8A2D-4205-AFED-BC6933B991C8}"/>
-    <hyperlink ref="AB25" r:id="rId24" xr:uid="{892979DC-66E7-4087-897B-DECDCABD9F49}"/>
-    <hyperlink ref="AB26" r:id="rId25" xr:uid="{16614237-1C39-4C4D-94D4-D0E7FFF979B1}"/>
-    <hyperlink ref="AB27" r:id="rId26" xr:uid="{0C749F65-298D-4EAC-8F1B-5ECBB05989E3}"/>
-    <hyperlink ref="AB28" r:id="rId27" xr:uid="{00E269EE-4B9F-48BB-834E-82E86CDA7518}"/>
-    <hyperlink ref="AB29" r:id="rId28" xr:uid="{E6F96F29-F14A-42B1-99E7-92248173F8F3}"/>
-    <hyperlink ref="AB31" r:id="rId29" xr:uid="{6F4A86C7-B0ED-4D27-8127-770150578009}"/>
-    <hyperlink ref="AB32" r:id="rId30" xr:uid="{9AF1CD1A-84CA-434F-9956-E9701891D767}"/>
-    <hyperlink ref="AB33" r:id="rId31" xr:uid="{3337C136-70E6-437A-9276-1A3E9EF077B8}"/>
-    <hyperlink ref="AB34" r:id="rId32" xr:uid="{39F83F25-34FE-464D-B841-CE1468C3692B}"/>
-    <hyperlink ref="AB35" r:id="rId33" xr:uid="{CEEC9363-357E-47E3-A9CD-AB84597FA50F}"/>
-    <hyperlink ref="AB36" r:id="rId34" xr:uid="{6B9F7810-5E7E-4182-9F13-D9B429A1586B}"/>
-    <hyperlink ref="AB37" r:id="rId35" xr:uid="{D7B07B19-77B0-478F-BED2-C3A73B87F0EA}"/>
-    <hyperlink ref="AB38" r:id="rId36" xr:uid="{0D89940F-5CA6-4697-9E73-6FB8ACC874E5}"/>
-    <hyperlink ref="AB39" r:id="rId37" xr:uid="{3CBA5543-2BDF-4515-A5C8-6167176A7CDA}"/>
-    <hyperlink ref="AB40" r:id="rId38" xr:uid="{AD4CA7D9-992A-4D00-B696-E4AB01398F61}"/>
-    <hyperlink ref="AB41" r:id="rId39" xr:uid="{2DB2FCAF-A130-455A-BD19-74DFF72F886B}"/>
-    <hyperlink ref="AB30" r:id="rId40" xr:uid="{BCE2581F-C8D1-4DB6-8DAC-61F82459B2FA}"/>
-    <hyperlink ref="AB42" r:id="rId41" xr:uid="{582B0362-6797-4BFB-9F49-97FC41D5970B}"/>
-    <hyperlink ref="AB43" r:id="rId42" xr:uid="{CDFA3F36-4E5D-4793-AB3B-A1F260B64C05}"/>
-    <hyperlink ref="AB44" r:id="rId43" xr:uid="{E3BF613E-2716-494D-B929-DA2DCE9B87E1}"/>
-    <hyperlink ref="AB45" r:id="rId44" xr:uid="{C1FE33F7-6A8E-49FF-8344-4767C3C382B8}"/>
-    <hyperlink ref="AB46" r:id="rId45" xr:uid="{025F1806-644A-4BC1-9BA2-82B18CDC3CFC}"/>
-    <hyperlink ref="AB47" r:id="rId46" xr:uid="{579A5B14-B1D1-43BC-A563-9B1A5D70009B}"/>
-    <hyperlink ref="AB48" r:id="rId47" xr:uid="{0104AAFA-1F51-49CF-A6FF-6E45EA22388C}"/>
-    <hyperlink ref="AB49" r:id="rId48" xr:uid="{CD0E4F2B-8E5A-4191-A572-068C9C343160}"/>
-    <hyperlink ref="AB50" r:id="rId49" xr:uid="{A0BFEC34-7172-4002-B36B-FF35A09A595C}"/>
-    <hyperlink ref="AB51" r:id="rId50" xr:uid="{214FA9BE-0BED-446A-AE77-9A4E64B7893B}"/>
-    <hyperlink ref="AB52" r:id="rId51" xr:uid="{67C30C5A-52CF-45CF-AE23-980CF97F709E}"/>
-    <hyperlink ref="AB53" r:id="rId52" xr:uid="{D35F4C83-C11D-4569-B4B1-8A91B6D9731C}"/>
-    <hyperlink ref="AB54" r:id="rId53" xr:uid="{626F1EB7-3239-4D2B-9E95-E6D3A4506136}"/>
-    <hyperlink ref="AB55" r:id="rId54" xr:uid="{C61E2950-F84F-4E21-810D-E45C1BC1D9C5}"/>
-    <hyperlink ref="AB56" r:id="rId55" xr:uid="{43D95FB8-5223-4294-A0A4-9C0D0ADFD69F}"/>
-    <hyperlink ref="AB57" r:id="rId56" xr:uid="{8DC4FCE2-C1BE-429F-9775-BE707502FFEF}"/>
-    <hyperlink ref="AB58" r:id="rId57" xr:uid="{E6AED6C5-A803-4A2A-A29F-9CE5A39EE263}"/>
-    <hyperlink ref="AB59" r:id="rId58" xr:uid="{3A6317A2-7755-4240-91C6-924A11DF2798}"/>
-    <hyperlink ref="AB60" r:id="rId59" xr:uid="{0083C2A7-2776-4276-A0FA-7FA71E181C28}"/>
-    <hyperlink ref="AB61" r:id="rId60" xr:uid="{92A35B3A-2924-4588-B23F-EFD1A1E345F1}"/>
+    <hyperlink ref="AA2" r:id="rId1" xr:uid="{732997D1-2192-49C8-AD3C-37FF6D9C50FB}"/>
+    <hyperlink ref="AA3" r:id="rId2" xr:uid="{6D3D26FD-6440-42D0-915E-7DC5B096846A}"/>
+    <hyperlink ref="AA4" r:id="rId3" xr:uid="{F06EF75F-03E5-4FF4-94E9-B13CD521BCC4}"/>
+    <hyperlink ref="AA5" r:id="rId4" xr:uid="{10E71439-6E78-4DC8-94BA-708278AA49E1}"/>
+    <hyperlink ref="AA6" r:id="rId5" xr:uid="{AD5083CF-D35A-4E44-ACD1-0096D32B2035}"/>
+    <hyperlink ref="AA7" r:id="rId6" xr:uid="{EF1C82B1-E495-49BC-9C7C-5A819C6B4157}"/>
+    <hyperlink ref="AA8" r:id="rId7" xr:uid="{1500CDB3-2564-419A-83A6-D6A2AD106DFA}"/>
+    <hyperlink ref="AA9" r:id="rId8" xr:uid="{AD24B4CC-D138-4A10-8B1B-9F104C1F0E04}"/>
+    <hyperlink ref="AA10" r:id="rId9" xr:uid="{E24D7C14-029E-4A47-A026-A1CABC412744}"/>
+    <hyperlink ref="AA11" r:id="rId10" xr:uid="{431278EF-EBDB-42AE-9F9B-9121762AB4BD}"/>
+    <hyperlink ref="AA12" r:id="rId11" xr:uid="{D47AED6B-D37D-4CE8-8AC3-869FE4E73A4C}"/>
+    <hyperlink ref="AA13" r:id="rId12" xr:uid="{0B57C4D9-36D2-465E-AB07-1DEFA76CB325}"/>
+    <hyperlink ref="AA14" r:id="rId13" xr:uid="{422B11F8-5AAA-46B3-A9F4-8400C1BA175D}"/>
+    <hyperlink ref="AA15" r:id="rId14" xr:uid="{9F8FD200-53B5-427A-AAC6-66661E99DD06}"/>
+    <hyperlink ref="AA16" r:id="rId15" xr:uid="{27AE20A9-9999-4A9F-BF34-A0F451238BA4}"/>
+    <hyperlink ref="AA17" r:id="rId16" xr:uid="{21A72ADE-0573-4B53-8DDD-458141853D21}"/>
+    <hyperlink ref="AA18" r:id="rId17" xr:uid="{2BF32E9F-6E2B-41AA-B458-BC18EEEBE8EE}"/>
+    <hyperlink ref="AA19" r:id="rId18" xr:uid="{ABBFF699-C458-4BB8-B468-ED1B6F009F84}"/>
+    <hyperlink ref="AA20" r:id="rId19" xr:uid="{AEDFB273-5228-48A3-BB78-4CBF04C03206}"/>
+    <hyperlink ref="AA21" r:id="rId20" xr:uid="{76CBB5AF-C783-4C7E-BA94-D9457FBA37E0}"/>
+    <hyperlink ref="AA22" r:id="rId21" xr:uid="{C799105C-AEBB-4D14-93E9-22873AEDF926}"/>
+    <hyperlink ref="AA23" r:id="rId22" xr:uid="{3CA1EB14-2983-484B-9094-16A511911CBB}"/>
+    <hyperlink ref="AA24" r:id="rId23" xr:uid="{960B7DAB-8A2D-4205-AFED-BC6933B991C8}"/>
+    <hyperlink ref="AA25" r:id="rId24" xr:uid="{892979DC-66E7-4087-897B-DECDCABD9F49}"/>
+    <hyperlink ref="AA26" r:id="rId25" xr:uid="{16614237-1C39-4C4D-94D4-D0E7FFF979B1}"/>
+    <hyperlink ref="AA27" r:id="rId26" xr:uid="{0C749F65-298D-4EAC-8F1B-5ECBB05989E3}"/>
+    <hyperlink ref="AA28" r:id="rId27" xr:uid="{00E269EE-4B9F-48BB-834E-82E86CDA7518}"/>
+    <hyperlink ref="AA29" r:id="rId28" xr:uid="{E6F96F29-F14A-42B1-99E7-92248173F8F3}"/>
+    <hyperlink ref="AA31" r:id="rId29" xr:uid="{6F4A86C7-B0ED-4D27-8127-770150578009}"/>
+    <hyperlink ref="AA32" r:id="rId30" xr:uid="{9AF1CD1A-84CA-434F-9956-E9701891D767}"/>
+    <hyperlink ref="AA33" r:id="rId31" xr:uid="{3337C136-70E6-437A-9276-1A3E9EF077B8}"/>
+    <hyperlink ref="AA34" r:id="rId32" xr:uid="{39F83F25-34FE-464D-B841-CE1468C3692B}"/>
+    <hyperlink ref="AA35" r:id="rId33" xr:uid="{CEEC9363-357E-47E3-A9CD-AB84597FA50F}"/>
+    <hyperlink ref="AA36" r:id="rId34" xr:uid="{6B9F7810-5E7E-4182-9F13-D9B429A1586B}"/>
+    <hyperlink ref="AA37" r:id="rId35" xr:uid="{D7B07B19-77B0-478F-BED2-C3A73B87F0EA}"/>
+    <hyperlink ref="AA38" r:id="rId36" xr:uid="{0D89940F-5CA6-4697-9E73-6FB8ACC874E5}"/>
+    <hyperlink ref="AA39" r:id="rId37" xr:uid="{3CBA5543-2BDF-4515-A5C8-6167176A7CDA}"/>
+    <hyperlink ref="AA40" r:id="rId38" xr:uid="{AD4CA7D9-992A-4D00-B696-E4AB01398F61}"/>
+    <hyperlink ref="AA41" r:id="rId39" xr:uid="{2DB2FCAF-A130-455A-BD19-74DFF72F886B}"/>
+    <hyperlink ref="AA30" r:id="rId40" xr:uid="{BCE2581F-C8D1-4DB6-8DAC-61F82459B2FA}"/>
+    <hyperlink ref="AA42" r:id="rId41" xr:uid="{582B0362-6797-4BFB-9F49-97FC41D5970B}"/>
+    <hyperlink ref="AA43" r:id="rId42" xr:uid="{CDFA3F36-4E5D-4793-AB3B-A1F260B64C05}"/>
+    <hyperlink ref="AA44" r:id="rId43" xr:uid="{E3BF613E-2716-494D-B929-DA2DCE9B87E1}"/>
+    <hyperlink ref="AA45" r:id="rId44" xr:uid="{C1FE33F7-6A8E-49FF-8344-4767C3C382B8}"/>
+    <hyperlink ref="AA46" r:id="rId45" xr:uid="{025F1806-644A-4BC1-9BA2-82B18CDC3CFC}"/>
+    <hyperlink ref="AA47" r:id="rId46" xr:uid="{579A5B14-B1D1-43BC-A563-9B1A5D70009B}"/>
+    <hyperlink ref="AA48" r:id="rId47" xr:uid="{0104AAFA-1F51-49CF-A6FF-6E45EA22388C}"/>
+    <hyperlink ref="AA49" r:id="rId48" xr:uid="{CD0E4F2B-8E5A-4191-A572-068C9C343160}"/>
+    <hyperlink ref="AA50" r:id="rId49" xr:uid="{A0BFEC34-7172-4002-B36B-FF35A09A595C}"/>
+    <hyperlink ref="AA51" r:id="rId50" xr:uid="{214FA9BE-0BED-446A-AE77-9A4E64B7893B}"/>
+    <hyperlink ref="AA52" r:id="rId51" xr:uid="{67C30C5A-52CF-45CF-AE23-980CF97F709E}"/>
+    <hyperlink ref="AA53" r:id="rId52" xr:uid="{D35F4C83-C11D-4569-B4B1-8A91B6D9731C}"/>
+    <hyperlink ref="AA54" r:id="rId53" xr:uid="{626F1EB7-3239-4D2B-9E95-E6D3A4506136}"/>
+    <hyperlink ref="AA55" r:id="rId54" xr:uid="{C61E2950-F84F-4E21-810D-E45C1BC1D9C5}"/>
+    <hyperlink ref="AA56" r:id="rId55" xr:uid="{43D95FB8-5223-4294-A0A4-9C0D0ADFD69F}"/>
+    <hyperlink ref="AA57" r:id="rId56" xr:uid="{8DC4FCE2-C1BE-429F-9775-BE707502FFEF}"/>
+    <hyperlink ref="AA58" r:id="rId57" xr:uid="{E6AED6C5-A803-4A2A-A29F-9CE5A39EE263}"/>
+    <hyperlink ref="AA59" r:id="rId58" xr:uid="{3A6317A2-7755-4240-91C6-924A11DF2798}"/>
+    <hyperlink ref="AA60" r:id="rId59" xr:uid="{0083C2A7-2776-4276-A0FA-7FA71E181C28}"/>
+    <hyperlink ref="AA61" r:id="rId60" xr:uid="{92A35B3A-2924-4588-B23F-EFD1A1E345F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId61"/>
@@ -9083,7 +8170,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="72" t="s">
-        <v>542</v>
+        <v>489</v>
       </c>
       <c r="B1" s="72"/>
     </row>
@@ -9109,10 +8196,10 @@
     </row>
     <row r="3" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
-        <v>499</v>
+        <v>447</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>535</v>
+        <v>482</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="53"/>
@@ -9129,10 +8216,10 @@
     </row>
     <row r="4" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="68" t="s">
-        <v>498</v>
+        <v>446</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>536</v>
+        <v>483</v>
       </c>
       <c r="C4" s="55"/>
       <c r="D4" s="53"/>
@@ -9149,10 +8236,10 @@
     </row>
     <row r="5" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
-        <v>497</v>
+        <v>445</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>537</v>
+        <v>484</v>
       </c>
       <c r="C5" s="55"/>
       <c r="D5" s="53"/>
@@ -9169,10 +8256,10 @@
     </row>
     <row r="6" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="69" t="s">
-        <v>496</v>
+        <v>444</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>538</v>
+        <v>485</v>
       </c>
       <c r="C6" s="55"/>
       <c r="D6" s="53"/>
@@ -9192,7 +8279,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>539</v>
+        <v>486</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="53"/>
@@ -9212,7 +8299,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>540</v>
+        <v>487</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="53"/>
@@ -9229,10 +8316,10 @@
     </row>
     <row r="9" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="66" t="s">
-        <v>500</v>
+        <v>448</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>541</v>
+        <v>488</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="58"/>
@@ -9273,26 +8360,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100052CBA820BEBCD468114CF62615C95D9" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41d93ad2b4fecab14cfdaed9255371f8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ba695df1-2cef-45b3-b38e-525c8136ab22" xmlns:ns3="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a815193907c452009623866744c535" ns2:_="" ns3:_="">
     <xsd:import namespace="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
@@ -9533,32 +8600,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39E8DA8-D782-4F69-B46B-77021BF1B166}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82507086-9DCD-4197-A4F6-ECCED658E0D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9575,4 +8637,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39E8DA8-D782-4F69-B46B-77021BF1B166}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmeurope-my.sharepoint.com/personal/salman_muhammad_cmeurope_org/Documents/Technical/IF mapping tool/if-map/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1961" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D866604E-FE4A-4DBB-A62A-E94333506F5A}"/>
+  <xr:revisionPtr revIDLastSave="1965" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EB866FB-CDF0-4B08-886C-B125D881B4FA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,44 +37,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Research</author>
-  </authors>
-  <commentList>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{F2A869B0-CEE1-4593-820B-8308CD9E197E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Calculated: 1.4 Mt/yr × 10 years (captured); avoided is 1.5 × 10 = 15 Mt. ACCSION CCS cement plant, Denmark.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q44" authorId="0" shapeId="0" xr:uid="{AB8BFFB0-4F71-49AA-8EFA-DE6C76D21FD7}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Estimated operational year for Leopard (Carmeuse, Belgium) lime CCS pilot. IF24 project; grant agreement in H1 2026, operations likely ~2029.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1669,7 +1631,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1680,18 +1642,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
-        <bgColor rgb="FFF7F9FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1770,6 +1720,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1924,73 +1880,16 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1998,64 +1897,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2066,19 +1927,13 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2112,34 +1967,132 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2457,5629 +2410,5629 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
   <dimension ref="A1:AD61"/>
   <sheetFormatPr defaultColWidth="30" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="22" style="10" customWidth="1"/>
-    <col min="3" max="3" width="24" style="10" customWidth="1"/>
-    <col min="4" max="4" width="22" style="10" customWidth="1"/>
-    <col min="5" max="5" width="12" style="10" customWidth="1"/>
-    <col min="6" max="7" width="22" style="10" customWidth="1"/>
-    <col min="8" max="8" width="11" style="19" customWidth="1"/>
-    <col min="9" max="11" width="11" style="10" customWidth="1"/>
-    <col min="12" max="15" width="13" style="10" customWidth="1"/>
-    <col min="16" max="18" width="9" style="10" customWidth="1"/>
-    <col min="19" max="19" width="7" style="10" customWidth="1"/>
-    <col min="20" max="21" width="14" style="10" customWidth="1"/>
-    <col min="22" max="23" width="11" style="10" customWidth="1"/>
-    <col min="24" max="24" width="10" style="10" customWidth="1"/>
-    <col min="25" max="25" width="28" style="10" customWidth="1"/>
-    <col min="26" max="26" width="18" style="10" customWidth="1"/>
-    <col min="27" max="27" width="14" style="10" customWidth="1"/>
-    <col min="28" max="28" width="50" style="10" customWidth="1"/>
-    <col min="29" max="29" width="55" style="10" customWidth="1"/>
-    <col min="30" max="30" width="30" style="10" customWidth="1"/>
-    <col min="31" max="16384" width="30" style="10"/>
+    <col min="1" max="1" width="13.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12" style="2" customWidth="1"/>
+    <col min="6" max="7" width="22" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11" style="3" customWidth="1"/>
+    <col min="9" max="11" width="11" style="2" customWidth="1"/>
+    <col min="12" max="15" width="13" style="2" customWidth="1"/>
+    <col min="16" max="18" width="9" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7" style="2" customWidth="1"/>
+    <col min="20" max="21" width="14" style="2" customWidth="1"/>
+    <col min="22" max="23" width="11" style="2" customWidth="1"/>
+    <col min="24" max="24" width="10" style="2" customWidth="1"/>
+    <col min="25" max="25" width="28" style="2" customWidth="1"/>
+    <col min="26" max="26" width="18" style="2" customWidth="1"/>
+    <col min="27" max="27" width="14" style="2" customWidth="1"/>
+    <col min="28" max="28" width="50" style="2" customWidth="1"/>
+    <col min="29" max="29" width="55" style="2" customWidth="1"/>
+    <col min="30" max="30" width="30" style="2" customWidth="1"/>
+    <col min="31" max="16384" width="30" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="24" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:30" s="5" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="X1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AA1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AB1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="148.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="42">
         <v>1.5</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="43">
         <v>1.4</v>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="43">
         <v>1.4</v>
       </c>
-      <c r="K2" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="20">
+      <c r="K2" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="42">
         <v>15.077949</v>
       </c>
-      <c r="M2" s="21">
+      <c r="M2" s="43">
         <v>14</v>
       </c>
-      <c r="N2" s="21">
+      <c r="N2" s="43">
         <v>14</v>
       </c>
-      <c r="O2" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P2" s="13">
+      <c r="O2" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="44">
         <v>2024</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="44">
         <v>2030</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="44">
         <v>2040</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T2" s="14">
+      <c r="T2" s="45">
         <v>220123498</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="46">
         <v>57.062100000000001</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="46">
         <v>9.9770000000000003</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="Z2" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA2" s="25" t="s">
+      <c r="AA2" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AB2" s="41" t="s">
         <v>472</v>
       </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AC2" s="41" t="s">
         <v>473</v>
       </c>
-      <c r="AD2" s="51" t="s">
+      <c r="AD2" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="48">
         <v>0.12330000000000001</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="48">
         <v>0.112</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="48">
         <v>0.112</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="21">
+      <c r="K3" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="43">
         <v>1.2330000000000001</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="43">
         <v>1.1200000000000001</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="43">
         <v>1.1200000000000001</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" s="13">
+      <c r="O3" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" s="44">
         <v>2025</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="44">
         <v>2028</v>
       </c>
-      <c r="R3" s="13">
+      <c r="R3" s="44">
         <v>2037</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="45">
         <v>31238542</v>
       </c>
-      <c r="U3" s="14" t="s">
+      <c r="U3" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V3" s="46">
         <v>44.464755134852901</v>
       </c>
-      <c r="W3" s="5">
+      <c r="W3" s="46">
         <v>12.2450955929227</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y3" s="11" t="s">
+      <c r="Y3" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="Z3" s="11" t="s">
+      <c r="Z3" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA3" s="25" t="s">
+      <c r="AA3" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="AB3" s="11" t="s">
+      <c r="AB3" s="41" t="s">
         <v>477</v>
       </c>
-      <c r="AC3" s="11" t="s">
+      <c r="AC3" s="41" t="s">
         <v>476</v>
       </c>
-      <c r="AD3" s="71" t="s">
+      <c r="AD3" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="22">
+      <c r="H4" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="51">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="51">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="M4" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" s="22">
+      <c r="M4" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="51">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="O4" s="22">
+      <c r="O4" s="51">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="P4" s="17">
+      <c r="P4" s="52">
         <v>2021</v>
       </c>
-      <c r="Q4" s="17">
+      <c r="Q4" s="52">
         <v>2026</v>
       </c>
-      <c r="R4" s="17">
+      <c r="R4" s="52">
         <v>2036</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="T4" s="18">
+      <c r="T4" s="53">
         <v>3168000</v>
       </c>
-      <c r="U4" s="14" t="s">
+      <c r="U4" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V4" s="7">
+      <c r="V4" s="54">
         <v>43.327720234653299</v>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="54">
         <v>-3.1153158320413699</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y4" s="15" t="s">
+      <c r="Y4" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="Z4" s="15" t="s">
+      <c r="Z4" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="AA4" s="25" t="s">
+      <c r="AA4" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="AB4" s="15" t="s">
+      <c r="AB4" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="15" t="s">
+      <c r="AC4" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="45" t="s">
+      <c r="AD4" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="48">
         <v>1</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="43">
         <v>1</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="43">
         <v>1</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L5" s="21">
+      <c r="K5" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="43">
         <v>10</v>
       </c>
-      <c r="M5" s="21">
+      <c r="M5" s="43">
         <v>10</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="43">
         <v>10</v>
       </c>
-      <c r="O5" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P5" s="13" t="s">
+      <c r="O5" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="44">
         <v>2030</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="44">
         <v>2040</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="45">
         <v>145000000</v>
       </c>
-      <c r="U5" s="14" t="s">
+      <c r="U5" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V5" s="5">
+      <c r="V5" s="46">
         <v>46.809800000000003</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W5" s="46">
         <v>-0.13900000000000001</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y5" s="11" t="s">
+      <c r="Y5" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="Z5" s="11" t="s">
+      <c r="Z5" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA5" s="25" t="s">
+      <c r="AA5" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="AB5" s="11" t="s">
+      <c r="AB5" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="AC5" s="11" t="s">
+      <c r="AC5" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="AD5" s="47" t="s">
+      <c r="AD5" s="14" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="48">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="I6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="21">
+      <c r="I6" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="43">
         <v>0.128</v>
       </c>
-      <c r="M6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="P6" s="13">
+      <c r="M6" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="44">
         <v>2025</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="44">
         <v>2028</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="44">
         <v>2038</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="S6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T6" s="14">
+      <c r="T6" s="45">
         <v>7958244</v>
       </c>
-      <c r="U6" s="14" t="s">
+      <c r="U6" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="X6" s="4" t="s">
+      <c r="V6" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="X6" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="Y6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z6" s="11" t="s">
+      <c r="Y6" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z6" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA6" s="25" t="s">
+      <c r="AA6" s="47" t="s">
         <v>247</v>
       </c>
-      <c r="AB6" s="11" t="s">
+      <c r="AB6" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="AC6" s="11" t="s">
+      <c r="AC6" s="41" t="s">
         <v>451</v>
       </c>
-      <c r="AD6" s="70" t="s">
+      <c r="AD6" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="48">
         <v>0.8</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="48">
         <v>0.8</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="48">
         <v>0.8</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" s="21">
+      <c r="K7" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="43">
         <v>7.8</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="43">
         <v>8</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="43">
         <v>8</v>
       </c>
-      <c r="O7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7" s="13">
+      <c r="O7" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" s="44">
         <v>2023</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="Q7" s="44">
         <v>2028</v>
       </c>
-      <c r="R7" s="13">
+      <c r="R7" s="44">
         <v>2038</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="S7" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="T7" s="14">
+      <c r="T7" s="45">
         <v>189694949</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="U7" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V7" s="5">
+      <c r="V7" s="46">
         <v>43.232830995956597</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="46">
         <v>27.594387234972402</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="Y7" s="11" t="s">
+      <c r="Y7" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="Z7" s="11" t="s">
+      <c r="Z7" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA7" s="25" t="s">
+      <c r="AA7" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="AB7" s="11" t="s">
+      <c r="AB7" s="41" t="s">
         <v>248</v>
       </c>
-      <c r="AC7" s="11" t="s">
+      <c r="AC7" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="AD7" s="49" t="s">
+      <c r="AD7" s="16" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="48">
         <v>0.8</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="43">
         <v>0.8</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="43">
         <v>0.8</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" s="21">
+      <c r="K8" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="43">
         <v>8</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="43">
         <v>8</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="43">
         <v>8</v>
       </c>
-      <c r="O8" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P8" s="13" t="s">
+      <c r="O8" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="44">
         <v>2029</v>
       </c>
-      <c r="R8" s="13">
+      <c r="R8" s="44">
         <v>2039</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="S8" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T8" s="14">
+      <c r="T8" s="45">
         <v>115000000</v>
       </c>
-      <c r="U8" s="14" t="s">
+      <c r="U8" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V8" s="5">
+      <c r="V8" s="46">
         <v>50.575420999999999</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="46">
         <v>3.4423240000000002</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y8" s="11" t="s">
+      <c r="Y8" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="Z8" s="11" t="s">
+      <c r="Z8" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA8" s="25" t="s">
+      <c r="AA8" s="47" t="s">
         <v>251</v>
       </c>
-      <c r="AB8" s="11" t="s">
+      <c r="AB8" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="AC8" s="11" t="s">
+      <c r="AC8" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="AD8" s="47" t="s">
+      <c r="AD8" s="14" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="50">
         <v>2.5819174</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="16">
+      <c r="I9" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="50">
         <v>3</v>
       </c>
-      <c r="K9" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="28">
+      <c r="K9" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="55">
         <v>25.819174</v>
       </c>
-      <c r="M9" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="O9" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P9" s="17">
+      <c r="M9" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" s="52">
         <v>2025</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="52">
         <v>2029</v>
       </c>
-      <c r="R9" s="17">
+      <c r="R9" s="52">
         <v>2039</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T9" s="18">
+      <c r="T9" s="53">
         <v>169300000</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="U9" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V9" s="7">
+      <c r="V9" s="54">
         <v>37.960247145532399</v>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="54">
         <v>23.401746903124501</v>
       </c>
-      <c r="X9" s="3" t="s">
+      <c r="X9" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y9" s="15" t="s">
+      <c r="Y9" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="Z9" s="15" t="s">
+      <c r="Z9" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="AA9" s="25" t="s">
+      <c r="AA9" s="47" t="s">
         <v>254</v>
       </c>
-      <c r="AB9" s="15" t="s">
+      <c r="AB9" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="AC9" s="15" t="s">
+      <c r="AC9" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="AD9" s="71" t="s">
+      <c r="AD9" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="41" t="s">
         <v>456</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="21">
+      <c r="H10" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="43">
         <v>0.8</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="43">
         <v>0.8</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="21">
+      <c r="K10" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="43">
         <v>7.83</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="43">
         <v>8</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="43">
         <v>8</v>
       </c>
-      <c r="O10" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P10" s="13">
+      <c r="O10" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P10" s="44">
         <v>2021</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="44">
         <v>2028</v>
       </c>
-      <c r="R10" s="13">
+      <c r="R10" s="44">
         <v>2038</v>
       </c>
-      <c r="S10" s="4" t="s">
+      <c r="S10" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="T10" s="14">
+      <c r="T10" s="45">
         <v>180000000</v>
       </c>
-      <c r="U10" s="14">
+      <c r="U10" s="45">
         <v>1130000000</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V10" s="46">
         <v>59.352399526270403</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W10" s="46">
         <v>18.1028633833951</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="X10" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y10" s="11" t="s">
+      <c r="Y10" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="Z10" s="11" t="s">
+      <c r="Z10" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA10" s="25" t="s">
+      <c r="AA10" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="AB10" s="11" t="s">
+      <c r="AB10" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="AC10" s="11" t="s">
+      <c r="AC10" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="AD10" s="45" t="s">
+      <c r="AD10" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="31">
+      <c r="H11" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="56">
         <v>7.6649999999999999E-3</v>
       </c>
-      <c r="J11" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" s="21">
+      <c r="J11" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="43">
         <v>0.08</v>
       </c>
-      <c r="N11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P11" s="13">
+      <c r="N11" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="44">
         <v>2025</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="44">
         <v>2027</v>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="44">
         <v>2037</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="S11" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T11" s="14">
+      <c r="T11" s="45">
         <v>10206000</v>
       </c>
-      <c r="U11" s="14" t="s">
+      <c r="U11" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V11" s="5">
+      <c r="V11" s="46">
         <v>59.592303479664103</v>
       </c>
-      <c r="W11" s="5">
+      <c r="W11" s="46">
         <v>5.8029778441568904</v>
       </c>
-      <c r="X11" s="4" t="s">
+      <c r="X11" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="Y11" s="11" t="s">
+      <c r="Y11" s="41" t="s">
         <v>300</v>
       </c>
-      <c r="Z11" s="11" t="s">
+      <c r="Z11" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA11" s="25" t="s">
+      <c r="AA11" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="AB11" s="11" t="s">
+      <c r="AB11" s="41" t="s">
         <v>301</v>
       </c>
-      <c r="AC11" s="11" t="s">
+      <c r="AC11" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="AD11" s="47" t="s">
+      <c r="AD11" s="14" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="50">
         <v>1.3</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="51">
         <v>1.2</v>
       </c>
-      <c r="J12" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K12" s="22">
+      <c r="J12" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="51">
         <v>1.2</v>
       </c>
-      <c r="L12" s="22">
+      <c r="L12" s="51">
         <v>13</v>
       </c>
-      <c r="M12" s="22">
+      <c r="M12" s="51">
         <v>12</v>
       </c>
-      <c r="N12" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O12" s="22">
+      <c r="N12" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="51">
         <v>12</v>
       </c>
-      <c r="P12" s="17">
+      <c r="P12" s="52">
         <v>2023</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="Q12" s="52">
         <v>2028</v>
       </c>
-      <c r="R12" s="17">
+      <c r="R12" s="52">
         <v>2038</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="S12" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="T12" s="18">
+      <c r="T12" s="53">
         <v>109816528</v>
       </c>
-      <c r="U12" s="18">
+      <c r="U12" s="53">
         <v>410000000</v>
       </c>
-      <c r="V12" s="7">
+      <c r="V12" s="54">
         <v>53.875399999999999</v>
       </c>
-      <c r="W12" s="7">
+      <c r="W12" s="54">
         <v>9.5841999999999992</v>
       </c>
-      <c r="X12" s="3" t="s">
+      <c r="X12" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y12" s="15" t="s">
+      <c r="Y12" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="Z12" s="15" t="s">
+      <c r="Z12" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA12" s="25" t="s">
+      <c r="AA12" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="AB12" s="15" t="s">
+      <c r="AB12" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="AC12" s="15" t="s">
+      <c r="AC12" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="AD12" s="70" t="s">
+      <c r="AD12" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="51">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="51">
         <v>0.57999999999999996</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="51">
         <v>0.57999999999999996</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="22">
+      <c r="K13" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="51">
         <v>5.8</v>
       </c>
-      <c r="M13" s="22">
+      <c r="M13" s="51">
         <v>5.8</v>
       </c>
-      <c r="N13" s="22">
+      <c r="N13" s="51">
         <v>5.8</v>
       </c>
-      <c r="O13" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P13" s="17">
+      <c r="O13" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P13" s="52">
         <v>2023</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="52">
         <v>2028</v>
       </c>
-      <c r="R13" s="17">
+      <c r="R13" s="52">
         <v>2038</v>
       </c>
-      <c r="S13" s="3" t="s">
+      <c r="S13" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="T13" s="18">
+      <c r="T13" s="53">
         <v>125198197</v>
       </c>
-      <c r="U13" s="18">
+      <c r="U13" s="53">
         <v>198444191</v>
       </c>
-      <c r="V13" s="7">
+      <c r="V13" s="54">
         <v>50.813014492756999</v>
       </c>
-      <c r="W13" s="7">
+      <c r="W13" s="54">
         <v>1.78234746701462</v>
       </c>
-      <c r="X13" s="3" t="s">
+      <c r="X13" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y13" s="15" t="s">
+      <c r="Y13" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="Z13" s="15" t="s">
+      <c r="Z13" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA13" s="8" t="s">
+      <c r="AA13" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="AB13" s="15" t="s">
+      <c r="AB13" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="AC13" s="15" t="s">
+      <c r="AC13" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="AD13" s="51" t="s">
+      <c r="AD13" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="50">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="51">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="51">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L14" s="22">
+      <c r="K14" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="51">
         <v>0.64</v>
       </c>
-      <c r="M14" s="22">
+      <c r="M14" s="51">
         <v>0.64</v>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="51">
         <v>0.64</v>
       </c>
-      <c r="O14" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P14" s="17">
+      <c r="O14" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P14" s="52">
         <v>2025</v>
       </c>
-      <c r="Q14" s="17">
+      <c r="Q14" s="52">
         <v>2028</v>
       </c>
-      <c r="R14" s="17">
+      <c r="R14" s="52">
         <v>2038</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T14" s="18">
+      <c r="T14" s="53">
         <v>23635998</v>
       </c>
-      <c r="U14" s="18" t="s">
+      <c r="U14" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V14" s="7">
+      <c r="V14" s="54">
         <v>44.826999999999998</v>
       </c>
-      <c r="W14" s="7">
+      <c r="W14" s="54">
         <v>11.614000000000001</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="Y14" s="15" t="s">
+      <c r="Y14" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="Z14" s="15" t="s">
+      <c r="Z14" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA14" s="25" t="s">
+      <c r="AA14" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="AB14" s="15" t="s">
+      <c r="AB14" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="AC14" s="15" t="s">
+      <c r="AC14" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="AD14" s="70" t="s">
+      <c r="AD14" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="148.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="50">
         <v>0.7</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="51">
         <v>0.7</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="51">
         <v>0.7</v>
       </c>
-      <c r="K15" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L15" s="22">
+      <c r="K15" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="51">
         <v>7</v>
       </c>
-      <c r="M15" s="22">
+      <c r="M15" s="51">
         <v>7</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="51">
         <v>7</v>
       </c>
-      <c r="O15" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P15" s="17">
+      <c r="O15" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P15" s="52">
         <v>2024</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="52">
         <v>2031</v>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="52">
         <v>2041</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T15" s="18">
+      <c r="T15" s="53">
         <v>119682059</v>
       </c>
-      <c r="U15" s="18" t="s">
+      <c r="U15" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V15" s="7">
+      <c r="V15" s="54">
         <v>43.186100000000003</v>
       </c>
-      <c r="W15" s="7">
+      <c r="W15" s="54">
         <v>0.99039999999999995</v>
       </c>
-      <c r="X15" s="3" t="s">
+      <c r="X15" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y15" s="15" t="s">
+      <c r="Y15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="Z15" s="15" t="s">
+      <c r="Z15" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA15" s="25" t="s">
+      <c r="AA15" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="AB15" s="15" t="s">
+      <c r="AB15" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="AC15" s="15" t="s">
+      <c r="AC15" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="AD15" s="70" t="s">
+      <c r="AD15" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="H16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="21">
+      <c r="H16" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="43">
         <v>1.2</v>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="43">
         <v>1.2</v>
       </c>
-      <c r="K16" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="M16" s="21">
+      <c r="K16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="43">
         <v>12</v>
       </c>
-      <c r="N16" s="21">
+      <c r="N16" s="43">
         <v>12</v>
       </c>
-      <c r="O16" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P16" s="13">
+      <c r="O16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P16" s="44">
         <v>2025</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="Q16" s="44">
         <v>2032</v>
       </c>
-      <c r="R16" s="13">
+      <c r="R16" s="44">
         <v>2042</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="S16" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T16" s="14">
+      <c r="T16" s="45">
         <v>146415990</v>
       </c>
-      <c r="U16" s="14" t="s">
+      <c r="U16" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V16" s="5">
+      <c r="V16" s="46">
         <v>45.290985428950698</v>
       </c>
-      <c r="W16" s="5">
+      <c r="W16" s="46">
         <v>25.1109549184484</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="X16" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="Y16" s="11" t="s">
+      <c r="Y16" s="41" t="s">
         <v>309</v>
       </c>
-      <c r="Z16" s="11" t="s">
+      <c r="Z16" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA16" s="25" t="s">
+      <c r="AA16" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="AB16" s="11" t="s">
+      <c r="AB16" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="AC16" s="11" t="s">
+      <c r="AC16" s="41" t="s">
         <v>308</v>
       </c>
-      <c r="AD16" s="48" t="s">
+      <c r="AD16" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="40" t="s">
         <v>310</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="58">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="58">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="58">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="K17" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L17" s="31">
+      <c r="K17" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" s="56">
         <v>4.5689E-2</v>
       </c>
-      <c r="M17" s="21">
+      <c r="M17" s="43">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="N17" s="21">
+      <c r="N17" s="43">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="O17" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="O17" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P17" s="44">
         <v>2024</v>
       </c>
-      <c r="Q17" s="13">
+      <c r="Q17" s="44">
         <v>2026</v>
       </c>
-      <c r="R17" s="13">
+      <c r="R17" s="44">
         <v>2031</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="S17" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="T17" s="14">
+      <c r="T17" s="45">
         <v>30497000</v>
       </c>
-      <c r="U17" s="14" t="s">
+      <c r="U17" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V17" s="4">
+      <c r="V17" s="39">
         <v>51.870851200822599</v>
       </c>
-      <c r="W17" s="4">
+      <c r="W17" s="39">
         <v>4.30094696894741</v>
       </c>
-      <c r="X17" s="4" t="s">
+      <c r="X17" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="Y17" s="11" t="s">
+      <c r="Y17" s="41" t="s">
         <v>313</v>
       </c>
-      <c r="Z17" s="11" t="s">
+      <c r="Z17" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA17" s="6" t="s">
+      <c r="AA17" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="AB17" s="11" t="s">
+      <c r="AB17" s="41" t="s">
         <v>311</v>
       </c>
-      <c r="AC17" s="11" t="s">
+      <c r="AC17" s="41" t="s">
         <v>312</v>
       </c>
-      <c r="AD17" s="45" t="s">
+      <c r="AD17" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="43">
         <v>1.3</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="43">
         <v>1.3</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="43">
         <v>1.3</v>
       </c>
-      <c r="K18" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L18" s="21">
+      <c r="K18" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="43">
         <v>12.56</v>
       </c>
-      <c r="M18" s="21">
+      <c r="M18" s="43">
         <v>13</v>
       </c>
-      <c r="N18" s="21">
+      <c r="N18" s="43">
         <v>13</v>
       </c>
-      <c r="O18" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P18" s="13">
+      <c r="O18" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P18" s="44">
         <v>2025</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="Q18" s="44">
         <v>2030</v>
       </c>
-      <c r="R18" s="13">
+      <c r="R18" s="44">
         <v>2040</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="S18" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T18" s="14">
+      <c r="T18" s="45">
         <v>157000000</v>
       </c>
-      <c r="U18" s="14" t="s">
+      <c r="U18" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V18" s="5">
+      <c r="V18" s="46">
         <v>52.489100000000001</v>
       </c>
-      <c r="W18" s="5">
+      <c r="W18" s="46">
         <v>13.836399999999999</v>
       </c>
-      <c r="X18" s="4" t="s">
+      <c r="X18" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y18" s="11" t="s">
+      <c r="Y18" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="Z18" s="11" t="s">
+      <c r="Z18" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA18" s="6" t="s">
+      <c r="AA18" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="AB18" s="11" t="s">
+      <c r="AB18" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="AC18" s="11" t="s">
+      <c r="AC18" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="AD18" s="48" t="s">
+      <c r="AD18" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="50">
         <v>0.02</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="51">
         <v>0.02</v>
       </c>
-      <c r="J19" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K19" s="22">
+      <c r="J19" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="51">
         <v>0.02</v>
       </c>
-      <c r="L19" s="22">
+      <c r="L19" s="51">
         <v>0.2</v>
       </c>
-      <c r="M19" s="22">
+      <c r="M19" s="51">
         <v>0.2</v>
       </c>
-      <c r="N19" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O19" s="22">
+      <c r="N19" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" s="51">
         <v>0.2</v>
       </c>
-      <c r="P19" s="17">
+      <c r="P19" s="52">
         <v>2023</v>
       </c>
-      <c r="Q19" s="17">
+      <c r="Q19" s="52">
         <v>2026</v>
       </c>
-      <c r="R19" s="17">
+      <c r="R19" s="52">
         <v>2036</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="S19" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="T19" s="18">
+      <c r="T19" s="53">
         <v>4265136</v>
       </c>
-      <c r="U19" s="14" t="s">
+      <c r="U19" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V19" s="7">
+      <c r="V19" s="54">
         <v>50.569000000000003</v>
       </c>
-      <c r="W19" s="7">
+      <c r="W19" s="54">
         <v>5.359</v>
       </c>
-      <c r="X19" s="3" t="s">
+      <c r="X19" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y19" s="15" t="s">
+      <c r="Y19" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="Z19" s="15" t="s">
+      <c r="Z19" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA19" s="25" t="s">
+      <c r="AA19" s="47" t="s">
         <v>314</v>
       </c>
-      <c r="AB19" s="15" t="s">
+      <c r="AB19" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="AC19" s="15" t="s">
+      <c r="AC19" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="AD19" s="45" t="s">
+      <c r="AD19" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="41" t="s">
         <v>455</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="50">
         <v>2.11</v>
       </c>
-      <c r="I20" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="22">
+      <c r="I20" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="51">
         <v>2.11</v>
       </c>
-      <c r="K20" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L20" s="22">
+      <c r="K20" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" s="51">
         <v>21.1</v>
       </c>
-      <c r="M20" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N20" s="22">
+      <c r="M20" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="51">
         <v>21.1</v>
       </c>
-      <c r="O20" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P20" s="17">
+      <c r="O20" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P20" s="52">
         <v>2023</v>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="52">
         <v>2027</v>
       </c>
-      <c r="R20" s="17">
+      <c r="R20" s="52">
         <v>2037</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="S20" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="T20" s="18">
+      <c r="T20" s="53">
         <v>115000000</v>
       </c>
-      <c r="U20" s="18">
+      <c r="U20" s="53">
         <v>400157000</v>
       </c>
-      <c r="V20" s="7">
+      <c r="V20" s="54">
         <v>64.055300000000003</v>
       </c>
-      <c r="W20" s="7">
+      <c r="W20" s="54">
         <v>-22.0167</v>
       </c>
-      <c r="X20" s="3" t="s">
+      <c r="X20" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y20" s="15" t="s">
+      <c r="Y20" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="Z20" s="15" t="s">
+      <c r="Z20" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="AA20" s="8" t="s">
+      <c r="AA20" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="AB20" s="15" t="s">
+      <c r="AB20" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="AC20" s="15" t="s">
+      <c r="AC20" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="AD20" s="50" t="s">
+      <c r="AD20" s="17" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="60">
         <v>0.63600000000000001</v>
       </c>
-      <c r="I21" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K21" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L21" s="27">
+      <c r="I21" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" s="61">
         <v>6.3620479999999997</v>
       </c>
-      <c r="M21" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N21" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O21" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P21" s="17">
+      <c r="M21" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O21" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P21" s="52">
         <v>2025</v>
       </c>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="R21" s="17" t="s">
+      <c r="R21" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="S21" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T21" s="18">
+      <c r="T21" s="53">
         <v>25400000</v>
       </c>
-      <c r="U21" s="18" t="s">
+      <c r="U21" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V21" s="7">
+      <c r="V21" s="54">
         <v>41.352637812781921</v>
       </c>
-      <c r="W21" s="7">
+      <c r="W21" s="54">
         <v>2.1794021596499702</v>
       </c>
-      <c r="X21" s="3" t="s">
+      <c r="X21" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="Y21" s="11" t="s">
+      <c r="Y21" s="41" t="s">
         <v>317</v>
       </c>
-      <c r="Z21" s="15" t="s">
+      <c r="Z21" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="AA21" s="25" t="s">
+      <c r="AA21" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="AB21" s="15" t="s">
+      <c r="AB21" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="AC21" s="15" t="s">
+      <c r="AC21" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="AD21" s="48" t="s">
+      <c r="AD21" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="56">
         <v>1.7904E-2</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="43">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="J22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K22" s="21">
+      <c r="J22" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="43">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="L22" s="21">
+      <c r="L22" s="43">
         <v>0.17904</v>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="43">
         <v>0.13</v>
       </c>
-      <c r="N22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O22" s="21">
+      <c r="N22" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" s="43">
         <v>0.13</v>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="44">
         <v>2024</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="44">
         <v>2029</v>
       </c>
-      <c r="R22" s="13">
+      <c r="R22" s="44">
         <v>2039</v>
       </c>
-      <c r="S22" s="4" t="s">
+      <c r="S22" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="T22" s="14">
+      <c r="T22" s="45">
         <v>4150000</v>
       </c>
-      <c r="U22" s="14">
+      <c r="U22" s="45">
         <v>7337000</v>
       </c>
-      <c r="V22" s="4">
+      <c r="V22" s="39">
         <v>46.007872968721003</v>
       </c>
-      <c r="W22" s="4">
+      <c r="W22" s="39">
         <v>13.253440646806</v>
       </c>
-      <c r="X22" s="4" t="s">
+      <c r="X22" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="Y22" s="10" t="s">
+      <c r="Y22" s="62" t="s">
         <v>323</v>
       </c>
-      <c r="Z22" s="11" t="s">
+      <c r="Z22" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA22" s="25" t="s">
+      <c r="AA22" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="AB22" s="11" t="s">
+      <c r="AB22" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="AC22" s="11" t="s">
+      <c r="AC22" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="AD22" s="70" t="s">
+      <c r="AD22" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="136.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="50">
         <v>0.56499999999999995</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="51">
         <v>0.5</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23" s="51">
         <v>0.5</v>
       </c>
-      <c r="K23" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L23" s="22">
+      <c r="K23" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" s="51">
         <v>5.65</v>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="51">
         <v>5</v>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="51">
         <v>5</v>
       </c>
-      <c r="O23" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P23" s="17">
+      <c r="O23" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P23" s="52">
         <v>2025</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="52">
         <v>2027</v>
       </c>
-      <c r="R23" s="17">
+      <c r="R23" s="52">
         <v>2037</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="S23" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T23" s="18">
+      <c r="T23" s="53">
         <v>48445901</v>
       </c>
-      <c r="U23" s="18">
+      <c r="U23" s="53">
         <v>80000000</v>
       </c>
-      <c r="V23" s="7">
+      <c r="V23" s="54">
         <v>46.833519292993699</v>
       </c>
-      <c r="W23" s="7">
+      <c r="W23" s="54">
         <v>18.9154603437044</v>
       </c>
-      <c r="X23" s="3" t="s">
+      <c r="X23" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y23" s="15" t="s">
+      <c r="Y23" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="Z23" s="15" t="s">
+      <c r="Z23" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA23" s="25" t="s">
+      <c r="AA23" s="47" t="s">
         <v>325</v>
       </c>
-      <c r="AB23" s="15" t="s">
+      <c r="AB23" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="AC23" s="15" t="s">
+      <c r="AC23" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="AD23" s="48" t="s">
+      <c r="AD23" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="39" t="s">
+      <c r="F24" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="50">
         <v>0.2</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="51">
         <v>0.35</v>
       </c>
-      <c r="J24" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K24" s="22">
+      <c r="J24" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="51">
         <v>0.35</v>
       </c>
-      <c r="L24" s="22">
+      <c r="L24" s="51">
         <v>2</v>
       </c>
-      <c r="M24" s="22">
+      <c r="M24" s="51">
         <v>3.5</v>
       </c>
-      <c r="N24" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O24" s="22">
+      <c r="N24" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O24" s="51">
         <v>3.5</v>
       </c>
-      <c r="P24" s="17">
+      <c r="P24" s="52">
         <v>2025</v>
       </c>
-      <c r="Q24" s="17">
+      <c r="Q24" s="52">
         <v>2030</v>
       </c>
-      <c r="R24" s="17">
+      <c r="R24" s="52">
         <v>2040</v>
       </c>
-      <c r="S24" s="3" t="s">
+      <c r="S24" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T24" s="18">
+      <c r="T24" s="53">
         <v>40000000</v>
       </c>
-      <c r="U24" s="18">
+      <c r="U24" s="53">
         <v>1300000000</v>
       </c>
-      <c r="V24" s="7">
+      <c r="V24" s="54">
         <v>49.3107441033359</v>
       </c>
-      <c r="W24" s="7">
+      <c r="W24" s="54">
         <v>1.1835034670687401</v>
       </c>
-      <c r="X24" s="3" t="s">
+      <c r="X24" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="Y24" s="15" t="s">
+      <c r="Y24" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="Z24" s="15" t="s">
+      <c r="Z24" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA24" s="25" t="s">
+      <c r="AA24" s="47" t="s">
         <v>339</v>
       </c>
-      <c r="AB24" s="15" t="s">
+      <c r="AB24" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="AC24" s="15" t="s">
+      <c r="AC24" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="AD24" s="71" t="s">
+      <c r="AD24" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="50">
         <v>1</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="51">
         <v>1</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="51">
         <v>1</v>
       </c>
-      <c r="K25" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L25" s="22">
+      <c r="K25" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" s="51">
         <v>10</v>
       </c>
-      <c r="M25" s="22">
+      <c r="M25" s="51">
         <v>10</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="51">
         <v>10</v>
       </c>
-      <c r="O25" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P25" s="17">
+      <c r="O25" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P25" s="52">
         <v>2024</v>
       </c>
-      <c r="Q25" s="17">
+      <c r="Q25" s="52">
         <v>2030</v>
       </c>
-      <c r="R25" s="17">
+      <c r="R25" s="52">
         <v>2040</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="S25" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T25" s="18">
+      <c r="T25" s="53">
         <v>216000000</v>
       </c>
-      <c r="U25" s="18" t="s">
+      <c r="U25" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V25" s="7">
+      <c r="V25" s="54">
         <v>45.515127894849797</v>
       </c>
-      <c r="W25" s="7">
+      <c r="W25" s="54">
         <v>10.343124922954001</v>
       </c>
-      <c r="X25" s="3" t="s">
+      <c r="X25" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="Y25" s="15" t="s">
+      <c r="Y25" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="Z25" s="15" t="s">
+      <c r="Z25" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA25" s="25" t="s">
+      <c r="AA25" s="47" t="s">
         <v>330</v>
       </c>
-      <c r="AB25" s="15" t="s">
+      <c r="AB25" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="AC25" s="15" t="s">
+      <c r="AC25" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="AD25" s="48" t="s">
+      <c r="AD25" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="60">
         <v>2.2800000000000001E-2</v>
       </c>
-      <c r="I26" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L26" s="22">
+      <c r="I26" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="51">
         <v>0.228163</v>
       </c>
-      <c r="M26" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N26" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O26" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P26" s="17">
+      <c r="M26" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O26" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P26" s="52">
         <v>2024</v>
       </c>
-      <c r="Q26" s="17">
+      <c r="Q26" s="52">
         <v>2030</v>
       </c>
-      <c r="R26" s="17">
+      <c r="R26" s="52">
         <v>2040</v>
       </c>
-      <c r="S26" s="3" t="s">
+      <c r="S26" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="T26" s="18">
+      <c r="T26" s="53">
         <v>40000000</v>
       </c>
-      <c r="U26" s="18" t="s">
+      <c r="U26" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V26" s="3">
+      <c r="V26" s="49">
         <v>59.121267699503399</v>
       </c>
-      <c r="W26" s="3">
+      <c r="W26" s="49">
         <v>9.6300609243118291</v>
       </c>
-      <c r="X26" s="3" t="s">
+      <c r="X26" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="Y26" s="15" t="s">
+      <c r="Y26" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="Z26" s="15" t="s">
+      <c r="Z26" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="AA26" s="8" t="s">
+      <c r="AA26" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="AB26" s="15" t="s">
+      <c r="AB26" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="AC26" s="15" t="s">
+      <c r="AC26" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="AD26" s="51" t="s">
+      <c r="AD26" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="48">
         <v>0.23252429999999999</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="43">
         <v>0.19500000000000001</v>
       </c>
-      <c r="J27" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K27" s="21">
+      <c r="J27" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K27" s="43">
         <v>0.19500000000000001</v>
       </c>
-      <c r="L27" s="21">
+      <c r="L27" s="43">
         <v>2.3252429999999999</v>
       </c>
-      <c r="M27" s="21">
+      <c r="M27" s="43">
         <v>1.95</v>
       </c>
-      <c r="N27" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O27" s="21">
+      <c r="N27" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O27" s="43">
         <v>1.95</v>
       </c>
-      <c r="P27" s="13">
+      <c r="P27" s="44">
         <v>2024</v>
       </c>
-      <c r="Q27" s="13">
+      <c r="Q27" s="44">
         <v>2028</v>
       </c>
-      <c r="R27" s="13">
+      <c r="R27" s="44">
         <v>2038</v>
       </c>
-      <c r="S27" s="4" t="s">
+      <c r="S27" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="T27" s="14">
+      <c r="T27" s="45">
         <v>115190750</v>
       </c>
-      <c r="U27" s="14">
+      <c r="U27" s="45">
         <v>700000000</v>
       </c>
-      <c r="V27" s="5">
+      <c r="V27" s="46">
         <v>44.521196111732202</v>
       </c>
-      <c r="W27" s="5">
+      <c r="W27" s="46">
         <v>4.6899272399638701</v>
       </c>
-      <c r="X27" s="4" t="s">
+      <c r="X27" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y27" s="11" t="s">
+      <c r="Y27" s="41" t="s">
         <v>343</v>
       </c>
-      <c r="Z27" s="11" t="s">
+      <c r="Z27" s="41" t="s">
         <v>464</v>
       </c>
-      <c r="AA27" s="6" t="s">
+      <c r="AA27" s="59" t="s">
         <v>120</v>
       </c>
-      <c r="AB27" s="11" t="s">
+      <c r="AB27" s="41" t="s">
         <v>341</v>
       </c>
-      <c r="AC27" s="11" t="s">
+      <c r="AC27" s="41" t="s">
         <v>342</v>
       </c>
-      <c r="AD27" s="71" t="s">
+      <c r="AD27" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="48">
         <v>0.26</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="43">
         <v>0.25</v>
       </c>
-      <c r="J28" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K28" s="21">
+      <c r="J28" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" s="43">
         <v>0.25</v>
       </c>
-      <c r="L28" s="21">
+      <c r="L28" s="43">
         <v>2.6</v>
       </c>
-      <c r="M28" s="21">
+      <c r="M28" s="43">
         <v>2.5</v>
       </c>
-      <c r="N28" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O28" s="21">
+      <c r="N28" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O28" s="43">
         <v>2.5</v>
       </c>
-      <c r="P28" s="13">
+      <c r="P28" s="44">
         <v>2025</v>
       </c>
-      <c r="Q28" s="13">
+      <c r="Q28" s="44">
         <v>2028</v>
       </c>
-      <c r="R28" s="13">
+      <c r="R28" s="44">
         <v>2038</v>
       </c>
-      <c r="S28" s="4" t="s">
+      <c r="S28" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T28" s="14">
+      <c r="T28" s="45">
         <v>54000000</v>
       </c>
-      <c r="U28" s="18" t="s">
+      <c r="U28" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V28" s="5">
+      <c r="V28" s="46">
         <v>54.992185868676003</v>
       </c>
-      <c r="W28" s="5">
+      <c r="W28" s="46">
         <v>11.8749856575691</v>
       </c>
-      <c r="X28" s="4" t="s">
+      <c r="X28" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="Y28" s="11" t="s">
+      <c r="Y28" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="Z28" s="11" t="s">
+      <c r="Z28" s="41" t="s">
         <v>464</v>
       </c>
-      <c r="AA28" s="25" t="s">
+      <c r="AA28" s="47" t="s">
         <v>345</v>
       </c>
-      <c r="AB28" s="11" t="s">
+      <c r="AB28" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="AC28" s="11" t="s">
+      <c r="AC28" s="41" t="s">
         <v>347</v>
       </c>
-      <c r="AD28" s="51" t="s">
+      <c r="AD28" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="43">
         <v>1.5</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="43">
         <v>1.5</v>
       </c>
-      <c r="J29" s="21">
+      <c r="J29" s="43">
         <v>1.5</v>
       </c>
-      <c r="K29" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L29" s="21">
+      <c r="K29" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" s="43">
         <v>15</v>
       </c>
-      <c r="M29" s="21">
+      <c r="M29" s="43">
         <v>15</v>
       </c>
-      <c r="N29" s="21">
+      <c r="N29" s="43">
         <v>15</v>
       </c>
-      <c r="O29" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P29" s="13">
+      <c r="O29" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P29" s="44">
         <v>2024</v>
       </c>
-      <c r="Q29" s="13">
+      <c r="Q29" s="44">
         <v>2031</v>
       </c>
-      <c r="R29" s="13">
+      <c r="R29" s="44">
         <v>2041</v>
       </c>
-      <c r="S29" s="4" t="s">
+      <c r="S29" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="T29" s="14">
+      <c r="T29" s="45">
         <v>228721666</v>
       </c>
-      <c r="U29" s="14" t="s">
+      <c r="U29" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V29" s="5">
+      <c r="V29" s="46">
         <v>51.297800000000002</v>
       </c>
-      <c r="W29" s="5">
+      <c r="W29" s="46">
         <v>7.0148000000000001</v>
       </c>
-      <c r="X29" s="4" t="s">
+      <c r="X29" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="Y29" s="11" t="s">
+      <c r="Y29" s="41" t="s">
         <v>348</v>
       </c>
-      <c r="Z29" s="11" t="s">
+      <c r="Z29" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA29" s="6" t="s">
+      <c r="AA29" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="AB29" s="11" t="s">
+      <c r="AB29" s="41" t="s">
         <v>349</v>
       </c>
-      <c r="AC29" s="11" t="s">
+      <c r="AC29" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="AD29" s="51" t="s">
+      <c r="AD29" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="60">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="51">
         <v>0.16</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="51">
         <v>0.16</v>
       </c>
-      <c r="K30" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L30" s="16">
+      <c r="K30" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="50">
         <v>0.46373999999999999</v>
       </c>
-      <c r="M30" s="22">
+      <c r="M30" s="51">
         <v>1.6</v>
       </c>
-      <c r="N30" s="22">
+      <c r="N30" s="51">
         <v>1.6</v>
       </c>
-      <c r="O30" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P30" s="17">
+      <c r="O30" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P30" s="52">
         <v>2024</v>
       </c>
-      <c r="Q30" s="17">
+      <c r="Q30" s="52">
         <v>2028</v>
       </c>
-      <c r="R30" s="17">
+      <c r="R30" s="52">
         <v>2038</v>
       </c>
-      <c r="S30" s="3" t="s">
+      <c r="S30" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T30" s="18">
+      <c r="T30" s="53">
         <v>29500000</v>
       </c>
-      <c r="U30" s="18" t="s">
+      <c r="U30" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V30" s="3">
+      <c r="V30" s="49">
         <v>60.618241659279597</v>
       </c>
-      <c r="W30" s="3">
+      <c r="W30" s="49">
         <v>16.891107915855802</v>
       </c>
-      <c r="X30" s="3" t="s">
+      <c r="X30" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="Y30" s="15" t="s">
+      <c r="Y30" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="Z30" s="15" t="s">
+      <c r="Z30" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA30" s="26" t="s">
+      <c r="AA30" s="63" t="s">
         <v>376</v>
       </c>
-      <c r="AB30" s="15" t="s">
+      <c r="AB30" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="AC30" s="15" t="s">
+      <c r="AC30" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="AD30" s="71" t="s">
+      <c r="AD30" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="50">
         <v>0.7</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="51">
         <v>0.7</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="51">
         <v>0.7</v>
       </c>
-      <c r="K31" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L31" s="22">
+      <c r="K31" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="51">
         <v>7.27</v>
       </c>
-      <c r="M31" s="22">
+      <c r="M31" s="51">
         <v>7</v>
       </c>
-      <c r="N31" s="22">
+      <c r="N31" s="51">
         <v>7</v>
       </c>
-      <c r="O31" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P31" s="17">
+      <c r="O31" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P31" s="52">
         <v>2024</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="Q31" s="52">
         <v>2030</v>
       </c>
-      <c r="R31" s="17">
+      <c r="R31" s="52">
         <v>2040</v>
       </c>
-      <c r="S31" s="3" t="s">
+      <c r="S31" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="T31" s="18">
+      <c r="T31" s="53">
         <v>191000000</v>
       </c>
-      <c r="U31" s="14" t="s">
+      <c r="U31" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V31" s="7">
+      <c r="V31" s="54">
         <v>51.618000000000002</v>
       </c>
-      <c r="W31" s="7">
+      <c r="W31" s="54">
         <v>8.5100999999999996</v>
       </c>
-      <c r="X31" s="3" t="s">
+      <c r="X31" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y31" s="15" t="s">
+      <c r="Y31" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z31" s="15" t="s">
+      <c r="Z31" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA31" s="38" t="s">
+      <c r="AA31" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="AB31" s="15" t="s">
+      <c r="AB31" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="AC31" s="15" t="s">
+      <c r="AC31" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="AD31" s="51" t="s">
+      <c r="AD31" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="50">
         <v>1</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="51">
         <v>1.2</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="51">
         <v>1.2</v>
       </c>
-      <c r="K32" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L32" s="22">
+      <c r="K32" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" s="51">
         <v>10</v>
       </c>
-      <c r="M32" s="22">
+      <c r="M32" s="51">
         <v>12</v>
       </c>
-      <c r="N32" s="22">
+      <c r="N32" s="51">
         <v>12</v>
       </c>
-      <c r="O32" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P32" s="17">
+      <c r="O32" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P32" s="52">
         <v>2022</v>
       </c>
-      <c r="Q32" s="17">
+      <c r="Q32" s="52">
         <v>2027</v>
       </c>
-      <c r="R32" s="17">
+      <c r="R32" s="52">
         <v>2037</v>
       </c>
-      <c r="S32" s="3" t="s">
+      <c r="S32" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="18">
+      <c r="T32" s="53">
         <v>228210004</v>
       </c>
-      <c r="U32" s="18">
+      <c r="U32" s="53">
         <v>380350000</v>
       </c>
-      <c r="V32" s="7">
+      <c r="V32" s="54">
         <v>52.837400000000002</v>
       </c>
-      <c r="W32" s="7">
+      <c r="W32" s="54">
         <v>17.989599999999999</v>
       </c>
-      <c r="X32" s="3" t="s">
+      <c r="X32" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y32" s="15" t="s">
+      <c r="Y32" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="Z32" s="15" t="s">
+      <c r="Z32" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA32" s="25" t="s">
+      <c r="AA32" s="47" t="s">
         <v>352</v>
       </c>
-      <c r="AB32" s="15" t="s">
+      <c r="AB32" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="AC32" s="15" t="s">
+      <c r="AC32" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="AD32" s="51" t="s">
+      <c r="AD32" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="42">
         <v>1.0045932</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="43">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J33" s="21">
+      <c r="J33" s="43">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K33" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L33" s="12">
+      <c r="K33" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" s="48">
         <v>10.045932000000001</v>
       </c>
-      <c r="M33" s="21">
+      <c r="M33" s="43">
         <v>11</v>
       </c>
-      <c r="N33" s="21">
+      <c r="N33" s="43">
         <v>11</v>
       </c>
-      <c r="O33" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P33" s="13">
+      <c r="O33" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P33" s="44">
         <v>2023</v>
       </c>
-      <c r="Q33" s="13">
+      <c r="Q33" s="44">
         <v>2028</v>
       </c>
-      <c r="R33" s="13">
+      <c r="R33" s="44">
         <v>2038</v>
       </c>
-      <c r="S33" s="4" t="s">
+      <c r="S33" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="T33" s="14">
+      <c r="T33" s="45">
         <v>230000000</v>
       </c>
-      <c r="U33" s="14">
+      <c r="U33" s="45">
         <v>500000000</v>
       </c>
-      <c r="V33" s="5">
+      <c r="V33" s="46">
         <v>50.472380999999999</v>
       </c>
-      <c r="W33" s="5">
+      <c r="W33" s="46">
         <v>3.9928129999999999</v>
       </c>
-      <c r="X33" s="4" t="s">
+      <c r="X33" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y33" s="11" t="s">
+      <c r="Y33" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="Z33" s="11" t="s">
+      <c r="Z33" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA33" s="25" t="s">
+      <c r="AA33" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="AB33" s="11" t="s">
+      <c r="AB33" s="41" t="s">
         <v>353</v>
       </c>
-      <c r="AC33" s="11" t="s">
+      <c r="AC33" s="41" t="s">
         <v>354</v>
       </c>
-      <c r="AD33" s="50" t="s">
+      <c r="AD33" s="17" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="12">
+      <c r="G34" s="40"/>
+      <c r="H34" s="48">
         <v>0.29010780000000003</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="43">
         <v>0.15</v>
       </c>
-      <c r="J34" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K34" s="21">
+      <c r="J34" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" s="43">
         <v>0.15</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="48">
         <v>2.901078</v>
       </c>
-      <c r="M34" s="21">
+      <c r="M34" s="43">
         <v>1.5</v>
       </c>
-      <c r="N34" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O34" s="21">
+      <c r="N34" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O34" s="43">
         <v>1.5</v>
       </c>
-      <c r="P34" s="13">
+      <c r="P34" s="44">
         <v>2023</v>
       </c>
-      <c r="Q34" s="13">
+      <c r="Q34" s="44">
         <v>2028</v>
       </c>
-      <c r="R34" s="13">
+      <c r="R34" s="44">
         <v>2038</v>
       </c>
-      <c r="S34" s="4" t="s">
+      <c r="S34" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="T34" s="14">
+      <c r="T34" s="45">
         <v>122900000</v>
       </c>
-      <c r="U34" s="14" t="s">
+      <c r="U34" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V34" s="4">
+      <c r="V34" s="39">
         <v>43.151000000000003</v>
       </c>
-      <c r="W34" s="4">
+      <c r="W34" s="39">
         <v>-7.6859999999999999</v>
       </c>
-      <c r="X34" s="4" t="s">
+      <c r="X34" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="Y34" s="11" t="s">
+      <c r="Y34" s="41" t="s">
         <v>356</v>
       </c>
-      <c r="Z34" s="11" t="s">
+      <c r="Z34" s="41" t="s">
         <v>464</v>
       </c>
-      <c r="AA34" s="25" t="s">
+      <c r="AA34" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="AB34" s="11" t="s">
+      <c r="AB34" s="41" t="s">
         <v>357</v>
       </c>
-      <c r="AC34" s="11" t="s">
+      <c r="AC34" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="AD34" s="70" t="s">
+      <c r="AD34" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="50">
         <v>0.28144999999999998</v>
       </c>
-      <c r="I35" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J35" s="22">
+      <c r="I35" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J35" s="51">
         <v>0.4</v>
       </c>
-      <c r="K35" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L35" s="27">
+      <c r="K35" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L35" s="61">
         <v>2.8</v>
       </c>
-      <c r="M35" s="22">
+      <c r="M35" s="51">
         <v>4</v>
       </c>
-      <c r="N35" s="22">
+      <c r="N35" s="51">
         <v>4</v>
       </c>
-      <c r="O35" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P35" s="17">
+      <c r="O35" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P35" s="52">
         <v>2024</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="Q35" s="52">
         <v>2026</v>
       </c>
-      <c r="R35" s="17">
+      <c r="R35" s="52">
         <v>2034</v>
       </c>
-      <c r="S35" s="3" t="s">
+      <c r="S35" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T35" s="18">
+      <c r="T35" s="53">
         <v>41041661</v>
       </c>
-      <c r="U35" s="18">
+      <c r="U35" s="53">
         <v>150000000</v>
       </c>
-      <c r="V35" s="7">
+      <c r="V35" s="54">
         <v>55.482799999999997</v>
       </c>
-      <c r="W35" s="7">
+      <c r="W35" s="54">
         <v>8.4393999999999991</v>
       </c>
-      <c r="X35" s="3" t="s">
+      <c r="X35" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y35" s="15" t="s">
+      <c r="Y35" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="Z35" s="15" t="s">
+      <c r="Z35" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="AA35" s="25" t="s">
+      <c r="AA35" s="47" t="s">
         <v>359</v>
       </c>
-      <c r="AB35" s="15" t="s">
+      <c r="AB35" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="AC35" s="15" t="s">
+      <c r="AC35" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="AD35" s="45" t="s">
+      <c r="AD35" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="40" t="s">
         <v>459</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="50">
         <v>1.28</v>
       </c>
-      <c r="I36" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J36" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K36" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L36" s="22">
+      <c r="I36" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J36" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K36" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L36" s="51">
         <v>12.8</v>
       </c>
-      <c r="M36" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N36" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O36" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="P36" s="17">
+      <c r="M36" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N36" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O36" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P36" s="52">
         <v>2025</v>
       </c>
-      <c r="Q36" s="17">
+      <c r="Q36" s="52">
         <v>2029</v>
       </c>
-      <c r="R36" s="17">
+      <c r="R36" s="52">
         <v>2039</v>
       </c>
-      <c r="S36" s="3" t="s">
+      <c r="S36" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T36" s="18">
+      <c r="T36" s="53">
         <v>159000000</v>
       </c>
-      <c r="U36" s="14" t="s">
+      <c r="U36" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V36" s="7">
+      <c r="V36" s="54">
         <v>51.1339349</v>
       </c>
-      <c r="W36" s="7">
+      <c r="W36" s="54">
         <v>3.7766611000000001</v>
       </c>
-      <c r="X36" s="3" t="s">
+      <c r="X36" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y36" s="15" t="s">
+      <c r="Y36" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="Z36" s="15" t="s">
+      <c r="Z36" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA36" s="25" t="s">
+      <c r="AA36" s="47" t="s">
         <v>366</v>
       </c>
-      <c r="AB36" s="15" t="s">
+      <c r="AB36" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="AC36" s="15" t="s">
+      <c r="AC36" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="AD36" s="51" t="s">
+      <c r="AD36" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="42" t="s">
+      <c r="B37" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="H37" s="32">
+      <c r="H37" s="60">
         <v>5.0046999999999999E-3</v>
       </c>
-      <c r="I37" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J37" s="22">
+      <c r="I37" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J37" s="51">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="K37" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L37" s="27">
+      <c r="K37" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L37" s="61">
         <v>5.0047000000000001E-2</v>
       </c>
-      <c r="M37" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N37" s="32">
+      <c r="M37" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N37" s="60">
         <v>5.1711E-2</v>
       </c>
-      <c r="O37" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="P37" s="17">
+      <c r="O37" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="P37" s="52">
         <v>2026</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="Q37" s="52">
         <v>2028</v>
       </c>
-      <c r="R37" s="17">
+      <c r="R37" s="52">
         <v>2038</v>
       </c>
-      <c r="S37" s="3" t="s">
+      <c r="S37" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T37" s="18">
+      <c r="T37" s="53">
         <v>26498650</v>
       </c>
-      <c r="U37" s="14" t="s">
+      <c r="U37" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V37" s="7">
+      <c r="V37" s="54">
         <v>50.529000000000003</v>
       </c>
-      <c r="W37" s="7">
+      <c r="W37" s="54">
         <v>18.047000000000001</v>
       </c>
-      <c r="X37" s="3" t="s">
+      <c r="X37" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y37" s="15" t="s">
+      <c r="Y37" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="Z37" s="15" t="s">
+      <c r="Z37" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="AA37" s="25" t="s">
+      <c r="AA37" s="47" t="s">
         <v>365</v>
       </c>
-      <c r="AB37" s="15" t="s">
+      <c r="AB37" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="AC37" s="15" t="s">
+      <c r="AC37" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="AD37" s="51" t="s">
+      <c r="AD37" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="50">
         <v>0.68</v>
       </c>
-      <c r="I38" s="22">
+      <c r="I38" s="51">
         <v>1.9</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="51">
         <v>1.9</v>
       </c>
-      <c r="K38" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L38" s="22">
+      <c r="K38" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L38" s="51">
         <v>6.8</v>
       </c>
-      <c r="M38" s="22">
+      <c r="M38" s="51">
         <v>19</v>
       </c>
-      <c r="N38" s="22">
+      <c r="N38" s="51">
         <v>19</v>
       </c>
-      <c r="O38" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P38" s="17">
+      <c r="O38" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P38" s="52">
         <v>2025</v>
       </c>
-      <c r="Q38" s="17">
+      <c r="Q38" s="52">
         <v>2029</v>
       </c>
-      <c r="R38" s="17">
+      <c r="R38" s="52">
         <v>2039</v>
       </c>
-      <c r="S38" s="3" t="s">
+      <c r="S38" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="T38" s="18">
+      <c r="T38" s="53">
         <v>234000000</v>
       </c>
-      <c r="U38" s="18" t="s">
+      <c r="U38" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V38" s="7">
+      <c r="V38" s="54">
         <v>38.129899999999999</v>
       </c>
-      <c r="W38" s="7">
+      <c r="W38" s="54">
         <v>23.527000000000001</v>
       </c>
-      <c r="X38" s="3" t="s">
+      <c r="X38" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y38" s="15" t="s">
+      <c r="Y38" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="Z38" s="15" t="s">
+      <c r="Z38" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA38" s="25" t="s">
+      <c r="AA38" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="AB38" s="15" t="s">
+      <c r="AB38" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="AC38" s="15" t="s">
+      <c r="AC38" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="AD38" s="71" t="s">
+      <c r="AD38" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="40" t="s">
         <v>454</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="12">
+      <c r="G39" s="40"/>
+      <c r="H39" s="48">
         <v>0.2</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="43">
         <v>0.2</v>
       </c>
-      <c r="J39" s="21">
+      <c r="J39" s="43">
         <v>0.2</v>
       </c>
-      <c r="K39" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L39" s="21">
+      <c r="K39" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L39" s="43">
         <v>2</v>
       </c>
-      <c r="M39" s="21">
+      <c r="M39" s="43">
         <v>2</v>
       </c>
-      <c r="N39" s="21">
+      <c r="N39" s="43">
         <v>2</v>
       </c>
-      <c r="O39" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P39" s="13">
+      <c r="O39" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P39" s="44">
         <v>2025</v>
       </c>
-      <c r="Q39" s="13">
+      <c r="Q39" s="44">
         <v>2028</v>
       </c>
-      <c r="R39" s="13">
+      <c r="R39" s="44">
         <v>2038</v>
       </c>
-      <c r="S39" s="4" t="s">
+      <c r="S39" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T39" s="14">
+      <c r="T39" s="45">
         <v>54000000</v>
       </c>
-      <c r="U39" s="14">
+      <c r="U39" s="45">
         <v>265000000</v>
       </c>
-      <c r="V39" s="5">
+      <c r="V39" s="46">
         <v>56.069083041647602</v>
       </c>
-      <c r="W39" s="5">
+      <c r="W39" s="46">
         <v>12.7671053619066</v>
       </c>
-      <c r="X39" s="4" t="s">
+      <c r="X39" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="Y39" s="11" t="s">
+      <c r="Y39" s="41" t="s">
         <v>279</v>
       </c>
-      <c r="Z39" s="11" t="s">
+      <c r="Z39" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA39" s="25" t="s">
+      <c r="AA39" s="47" t="s">
         <v>367</v>
       </c>
-      <c r="AB39" s="11" t="s">
+      <c r="AB39" s="41" t="s">
         <v>475</v>
       </c>
-      <c r="AC39" s="11" t="s">
+      <c r="AC39" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="AD39" s="46" t="s">
+      <c r="AD39" s="13" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="48">
         <v>0.85799999999999998</v>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="43">
         <v>0.85</v>
       </c>
-      <c r="J40" s="21">
+      <c r="J40" s="43">
         <v>0.84</v>
       </c>
-      <c r="K40" s="21">
+      <c r="K40" s="43">
         <v>0.01</v>
       </c>
-      <c r="L40" s="21">
+      <c r="L40" s="43">
         <v>8.58</v>
       </c>
-      <c r="M40" s="21">
+      <c r="M40" s="43">
         <v>8.5</v>
       </c>
-      <c r="N40" s="21">
+      <c r="N40" s="43">
         <v>8.4</v>
       </c>
-      <c r="O40" s="21">
+      <c r="O40" s="43">
         <v>0.1</v>
       </c>
-      <c r="P40" s="13">
+      <c r="P40" s="44">
         <v>2024</v>
       </c>
-      <c r="Q40" s="13">
+      <c r="Q40" s="44">
         <v>2029</v>
       </c>
-      <c r="R40" s="13">
+      <c r="R40" s="44">
         <v>2039</v>
       </c>
-      <c r="S40" s="4" t="s">
+      <c r="S40" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="T40" s="14">
+      <c r="T40" s="45">
         <v>127000000</v>
       </c>
-      <c r="U40" s="18" t="s">
+      <c r="U40" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V40" s="5">
+      <c r="V40" s="46">
         <v>37.916800000000002</v>
       </c>
-      <c r="W40" s="5">
+      <c r="W40" s="46">
         <v>23.069400000000002</v>
       </c>
-      <c r="X40" s="4" t="s">
+      <c r="X40" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y40" s="11" t="s">
+      <c r="Y40" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="Z40" s="11" t="s">
+      <c r="Z40" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA40" s="25" t="s">
+      <c r="AA40" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="AB40" s="11" t="s">
+      <c r="AB40" s="41" t="s">
         <v>368</v>
       </c>
-      <c r="AC40" s="11" t="s">
+      <c r="AC40" s="41" t="s">
         <v>369</v>
       </c>
-      <c r="AD40" s="70" t="s">
+      <c r="AD40" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="H41" s="12">
+      <c r="H41" s="48">
         <v>1.4</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="43">
         <v>1.4</v>
       </c>
-      <c r="J41" s="21">
+      <c r="J41" s="43">
         <v>1.4</v>
       </c>
-      <c r="K41" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L41" s="21">
+      <c r="K41" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L41" s="43">
         <v>14</v>
       </c>
-      <c r="M41" s="21">
+      <c r="M41" s="43">
         <v>14</v>
       </c>
-      <c r="N41" s="21">
+      <c r="N41" s="43">
         <v>14</v>
       </c>
-      <c r="O41" s="21" t="s">
+      <c r="O41" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="P41" s="13">
+      <c r="P41" s="44">
         <v>2020</v>
       </c>
-      <c r="Q41" s="13">
+      <c r="Q41" s="44">
         <v>2029</v>
       </c>
-      <c r="R41" s="13">
+      <c r="R41" s="44">
         <v>2039</v>
       </c>
-      <c r="S41" s="4" t="s">
+      <c r="S41" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="T41" s="14">
+      <c r="T41" s="45">
         <v>356900000</v>
       </c>
-      <c r="U41" s="18" t="s">
+      <c r="U41" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V41" s="5">
+      <c r="V41" s="46">
         <v>51.368588000000003</v>
       </c>
-      <c r="W41" s="5">
+      <c r="W41" s="46">
         <v>4.2713660000000004</v>
       </c>
-      <c r="X41" s="4" t="s">
+      <c r="X41" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y41" s="11" t="s">
+      <c r="Y41" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="Z41" s="11" t="s">
+      <c r="Z41" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA41" s="25" t="s">
+      <c r="AA41" s="47" t="s">
         <v>372</v>
       </c>
-      <c r="AB41" s="11" t="s">
+      <c r="AB41" s="41" t="s">
         <v>370</v>
       </c>
-      <c r="AC41" s="11" t="s">
+      <c r="AC41" s="41" t="s">
         <v>371</v>
       </c>
-      <c r="AD41" s="50" t="s">
+      <c r="AD41" s="17" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="42" t="s">
+      <c r="B42" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="50">
         <v>0.36599999999999999</v>
       </c>
-      <c r="I42" s="22">
+      <c r="I42" s="51">
         <v>0.36599999999999999</v>
       </c>
-      <c r="J42" s="22">
+      <c r="J42" s="51">
         <v>0.36599999999999999</v>
       </c>
-      <c r="K42" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L42" s="22">
+      <c r="K42" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L42" s="51">
         <v>3.7</v>
       </c>
-      <c r="M42" s="22">
+      <c r="M42" s="51">
         <v>3.66</v>
       </c>
-      <c r="N42" s="22">
+      <c r="N42" s="51">
         <v>3.66</v>
       </c>
-      <c r="O42" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P42" s="17">
+      <c r="O42" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P42" s="52">
         <v>2023</v>
       </c>
-      <c r="Q42" s="17">
+      <c r="Q42" s="52">
         <v>2028</v>
       </c>
-      <c r="R42" s="17">
+      <c r="R42" s="52">
         <v>2038</v>
       </c>
-      <c r="S42" s="3" t="s">
+      <c r="S42" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="T42" s="18">
+      <c r="T42" s="53">
         <v>117000000</v>
       </c>
-      <c r="U42" s="18" t="s">
+      <c r="U42" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V42" s="7">
+      <c r="V42" s="54">
         <v>44.968299999999999</v>
       </c>
-      <c r="W42" s="7">
+      <c r="W42" s="54">
         <v>14.1221</v>
       </c>
-      <c r="X42" s="3" t="s">
+      <c r="X42" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y42" s="15" t="s">
+      <c r="Y42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="Z42" s="15" t="s">
+      <c r="Z42" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA42" s="25" t="s">
+      <c r="AA42" s="47" t="s">
         <v>281</v>
       </c>
-      <c r="AB42" s="15" t="s">
+      <c r="AB42" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="AC42" s="15" t="s">
+      <c r="AC42" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="AD42" s="51" t="s">
+      <c r="AD42" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="42" t="s">
+      <c r="B43" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="41" t="s">
         <v>457</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I43" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J43" s="22">
+      <c r="G43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="I43" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J43" s="51">
         <v>5</v>
       </c>
-      <c r="K43" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L43" s="28">
+      <c r="K43" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" s="55">
         <v>31.381101000000001</v>
       </c>
-      <c r="M43" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N43" s="22">
+      <c r="M43" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N43" s="51">
         <v>50</v>
       </c>
-      <c r="O43" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P43" s="17">
+      <c r="O43" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P43" s="52">
         <v>2025</v>
       </c>
-      <c r="Q43" s="17">
+      <c r="Q43" s="52">
         <v>2029</v>
       </c>
-      <c r="R43" s="17">
+      <c r="R43" s="52">
         <v>2039</v>
       </c>
-      <c r="S43" s="3" t="s">
+      <c r="S43" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="18">
+      <c r="T43" s="53">
         <v>118000000</v>
       </c>
-      <c r="U43" s="18" t="s">
+      <c r="U43" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V43" s="7">
+      <c r="V43" s="54">
         <v>51.976999999999997</v>
       </c>
-      <c r="W43" s="7">
+      <c r="W43" s="54">
         <v>4.05</v>
       </c>
-      <c r="X43" s="3" t="s">
+      <c r="X43" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y43" s="15" t="s">
+      <c r="Y43" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="Z43" s="15" t="s">
+      <c r="Z43" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="AA43" s="26" t="s">
+      <c r="AA43" s="63" t="s">
         <v>264</v>
       </c>
-      <c r="AB43" s="15" t="s">
+      <c r="AB43" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="AC43" s="15" t="s">
+      <c r="AC43" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="AD43" s="51" t="s">
+      <c r="AD43" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H44" s="50">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="51">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44" s="51">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K44" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L44" s="22">
+      <c r="K44" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L44" s="51">
         <v>0.7</v>
       </c>
-      <c r="M44" s="22">
+      <c r="M44" s="51">
         <v>0.7</v>
       </c>
-      <c r="N44" s="22">
+      <c r="N44" s="51">
         <v>0.7</v>
       </c>
-      <c r="O44" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P44" s="17">
+      <c r="O44" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P44" s="52">
         <v>2026</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="52">
         <v>2031</v>
       </c>
-      <c r="R44" s="17">
+      <c r="R44" s="52">
         <v>2041</v>
       </c>
-      <c r="S44" s="3" t="s">
+      <c r="S44" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="18">
+      <c r="T44" s="53">
         <v>36000000</v>
       </c>
-      <c r="U44" s="18" t="s">
+      <c r="U44" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V44" s="7">
+      <c r="V44" s="54">
         <v>50.406342306737002</v>
       </c>
-      <c r="W44" s="7">
+      <c r="W44" s="54">
         <v>4.6321740189769196</v>
       </c>
-      <c r="X44" s="3" t="s">
+      <c r="X44" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y44" s="15" t="s">
+      <c r="Y44" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="Z44" s="15" t="s">
+      <c r="Z44" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA44" s="25" t="s">
+      <c r="AA44" s="47" t="s">
         <v>380</v>
       </c>
-      <c r="AB44" s="15" t="s">
+      <c r="AB44" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="AC44" s="15" t="s">
+      <c r="AC44" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="AD44" s="51" t="s">
+      <c r="AD44" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="42" t="s">
+      <c r="B45" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H45" s="16">
+      <c r="G45" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="50">
         <v>0.04</v>
       </c>
-      <c r="I45" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J45" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L45" s="16">
+      <c r="I45" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J45" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K45" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L45" s="50">
         <v>0.41452</v>
       </c>
-      <c r="M45" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N45" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O45" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P45" s="17">
+      <c r="M45" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N45" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O45" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P45" s="52">
         <v>2025</v>
       </c>
-      <c r="Q45" s="17">
+      <c r="Q45" s="52">
         <v>2028</v>
       </c>
-      <c r="R45" s="17">
+      <c r="R45" s="52">
         <v>2038</v>
       </c>
-      <c r="S45" s="3" t="s">
+      <c r="S45" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T45" s="18">
+      <c r="T45" s="53">
         <v>13000000</v>
       </c>
-      <c r="U45" s="18" t="s">
+      <c r="U45" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="49">
         <v>59.2181</v>
       </c>
-      <c r="W45" s="3">
+      <c r="W45" s="49">
         <v>10.9298</v>
       </c>
-      <c r="X45" s="3" t="s">
+      <c r="X45" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="Y45" s="15" t="s">
+      <c r="Y45" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="Z45" s="15" t="s">
+      <c r="Z45" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="AA45" s="25" t="s">
+      <c r="AA45" s="47" t="s">
         <v>383</v>
       </c>
-      <c r="AB45" s="15" t="s">
+      <c r="AB45" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="AC45" s="15" t="s">
+      <c r="AC45" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="AD45" s="70" t="s">
+      <c r="AD45" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="46" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="43" t="s">
+      <c r="B46" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="H46" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I46" s="21">
+      <c r="H46" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I46" s="43">
         <v>1</v>
       </c>
-      <c r="J46" s="21">
+      <c r="J46" s="43">
         <v>1</v>
       </c>
-      <c r="K46" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L46" s="29">
+      <c r="K46" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L46" s="67">
         <v>6.8833489999999999</v>
       </c>
-      <c r="M46" s="21">
+      <c r="M46" s="43">
         <v>10</v>
       </c>
-      <c r="N46" s="21">
+      <c r="N46" s="43">
         <v>10</v>
       </c>
-      <c r="O46" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P46" s="13">
+      <c r="O46" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P46" s="44">
         <v>2024</v>
       </c>
-      <c r="Q46" s="13">
+      <c r="Q46" s="44">
         <v>2029</v>
       </c>
-      <c r="R46" s="13">
+      <c r="R46" s="44">
         <v>2039</v>
       </c>
-      <c r="S46" s="4" t="s">
+      <c r="S46" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="T46" s="14">
+      <c r="T46" s="45">
         <v>124268490</v>
       </c>
-      <c r="U46" s="14">
+      <c r="U46" s="45">
         <v>400000000</v>
       </c>
-      <c r="V46" s="5">
+      <c r="V46" s="46">
         <v>38.375</v>
       </c>
-      <c r="W46" s="5">
+      <c r="W46" s="46">
         <v>24.060400000000001</v>
       </c>
-      <c r="X46" s="4" t="s">
+      <c r="X46" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y46" s="11" t="s">
+      <c r="Y46" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="Z46" s="11" t="s">
+      <c r="Z46" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA46" s="25" t="s">
+      <c r="AA46" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="AB46" s="11" t="s">
+      <c r="AB46" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="AC46" s="11" t="s">
+      <c r="AC46" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="AD46" s="70" t="s">
+      <c r="AD46" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="47" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="40" t="s">
         <v>388</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="56">
         <v>1.55E-2</v>
       </c>
-      <c r="I47" s="21" t="s">
+      <c r="I47" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="J47" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K47" s="21" t="s">
+      <c r="J47" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K47" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="L47" s="21">
+      <c r="L47" s="43">
         <v>0.155</v>
       </c>
-      <c r="M47" s="21" t="s">
+      <c r="M47" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="N47" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O47" s="21" t="s">
+      <c r="N47" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O47" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="P47" s="13">
+      <c r="P47" s="44">
         <v>2026</v>
       </c>
-      <c r="Q47" s="13">
+      <c r="Q47" s="44">
         <v>2028</v>
       </c>
-      <c r="R47" s="13">
+      <c r="R47" s="44">
         <v>2038</v>
       </c>
-      <c r="S47" s="4" t="s">
+      <c r="S47" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T47" s="14">
+      <c r="T47" s="45">
         <v>8600000</v>
       </c>
-      <c r="U47" s="18" t="s">
+      <c r="U47" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V47" s="5">
+      <c r="V47" s="46">
         <v>58.418889999999998</v>
       </c>
-      <c r="W47" s="5">
+      <c r="W47" s="46">
         <v>24.47278</v>
       </c>
-      <c r="X47" s="4" t="s">
+      <c r="X47" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y47" s="11" t="s">
+      <c r="Y47" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="Z47" s="11" t="s">
+      <c r="Z47" s="41" t="s">
         <v>464</v>
       </c>
-      <c r="AA47" s="25" t="s">
+      <c r="AA47" s="47" t="s">
         <v>392</v>
       </c>
-      <c r="AB47" s="11" t="s">
+      <c r="AB47" s="41" t="s">
         <v>390</v>
       </c>
-      <c r="AC47" s="11" t="s">
+      <c r="AC47" s="41" t="s">
         <v>391</v>
       </c>
-      <c r="AD47" s="48" t="s">
+      <c r="AD47" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="42" t="s">
+      <c r="B48" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="H48" s="16">
+      <c r="H48" s="50">
         <v>0.40600000000000003</v>
       </c>
-      <c r="I48" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J48" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K48" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L48" s="22">
+      <c r="I48" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J48" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K48" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L48" s="51">
         <v>4.0599999999999996</v>
       </c>
-      <c r="M48" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N48" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O48" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P48" s="17">
+      <c r="M48" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N48" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O48" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P48" s="52">
         <v>2023</v>
       </c>
-      <c r="Q48" s="17">
+      <c r="Q48" s="52">
         <v>2027</v>
       </c>
-      <c r="R48" s="17">
+      <c r="R48" s="52">
         <v>2037</v>
       </c>
-      <c r="S48" s="3" t="s">
+      <c r="S48" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="T48" s="18">
+      <c r="T48" s="53">
         <v>97000000</v>
       </c>
-      <c r="U48" s="18" t="s">
+      <c r="U48" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="V48" s="3">
+      <c r="V48" s="49">
         <v>58.099057767351503</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W48" s="49">
         <v>11.861499508001399</v>
       </c>
-      <c r="X48" s="3" t="s">
+      <c r="X48" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="Y48" s="15" t="s">
+      <c r="Y48" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="Z48" s="15" t="s">
+      <c r="Z48" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA48" s="26" t="s">
+      <c r="AA48" s="63" t="s">
         <v>235</v>
       </c>
-      <c r="AB48" s="15" t="s">
+      <c r="AB48" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="AC48" s="15" t="s">
+      <c r="AC48" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="AD48" s="71" t="s">
+      <c r="AD48" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="49" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="H49" s="32">
+      <c r="H49" s="60">
         <v>6.7077999999999999E-2</v>
       </c>
-      <c r="I49" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J49" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K49" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L49" s="27">
+      <c r="I49" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J49" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K49" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L49" s="61">
         <v>0.67078000000000004</v>
       </c>
-      <c r="M49" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N49" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O49" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P49" s="17">
+      <c r="M49" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N49" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O49" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P49" s="52">
         <v>2026</v>
       </c>
-      <c r="Q49" s="17">
+      <c r="Q49" s="52">
         <v>2030</v>
       </c>
-      <c r="R49" s="17">
+      <c r="R49" s="52">
         <v>2040</v>
       </c>
-      <c r="S49" s="3" t="s">
+      <c r="S49" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T49" s="18">
+      <c r="T49" s="53">
         <v>40000000</v>
       </c>
-      <c r="U49" s="18" t="s">
+      <c r="U49" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V49" s="7">
+      <c r="V49" s="54">
         <v>56.787056035485499</v>
       </c>
-      <c r="W49" s="7">
+      <c r="W49" s="54">
         <v>9.3873420638001708</v>
       </c>
-      <c r="X49" s="3" t="s">
+      <c r="X49" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y49" s="15" t="s">
+      <c r="Y49" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Z49" s="15" t="s">
+      <c r="Z49" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA49" s="25" t="s">
+      <c r="AA49" s="47" t="s">
         <v>396</v>
       </c>
-      <c r="AB49" s="15" t="s">
+      <c r="AB49" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="AC49" s="15" t="s">
+      <c r="AC49" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="AD49" s="70" t="s">
+      <c r="AD49" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="H50" s="16">
+      <c r="H50" s="50">
         <v>0.24099999999999999</v>
       </c>
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="22"/>
-      <c r="L50" s="27">
+      <c r="I50" s="51"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="51"/>
+      <c r="L50" s="61">
         <v>2.4073790000000002</v>
       </c>
-      <c r="M50" s="22"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="22"/>
-      <c r="P50" s="17">
+      <c r="M50" s="51"/>
+      <c r="N50" s="51"/>
+      <c r="O50" s="51"/>
+      <c r="P50" s="52">
         <v>2024</v>
       </c>
-      <c r="Q50" s="17">
+      <c r="Q50" s="52">
         <v>2026</v>
       </c>
-      <c r="R50" s="17">
+      <c r="R50" s="52">
         <v>2036</v>
       </c>
-      <c r="S50" s="3" t="s">
+      <c r="S50" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="T50" s="18">
+      <c r="T50" s="53">
         <v>19458418</v>
       </c>
-      <c r="U50" s="18" t="s">
+      <c r="U50" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V50" s="7">
+      <c r="V50" s="54">
         <v>48.096166502584701</v>
       </c>
-      <c r="W50" s="7">
+      <c r="W50" s="54">
         <v>11.0247947737657</v>
       </c>
-      <c r="X50" s="3" t="s">
+      <c r="X50" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="Y50" s="15" t="s">
+      <c r="Y50" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="Z50" s="15" t="s">
+      <c r="Z50" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="AA50" s="25" t="s">
+      <c r="AA50" s="47" t="s">
         <v>400</v>
       </c>
-      <c r="AB50" s="15" t="s">
+      <c r="AB50" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="AC50" s="15" t="s">
+      <c r="AC50" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="AD50" s="48" t="s">
+      <c r="AD50" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="51" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B51" s="41" t="s">
+      <c r="B51" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="G51" s="41" t="s">
         <v>403</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H51" s="48">
         <v>0.27411429999999998</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="68">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J51" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K51" s="33">
+      <c r="J51" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K51" s="68">
         <v>0.33400000000000002</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="69">
         <v>2.7411430000000001</v>
       </c>
-      <c r="M51" s="21">
+      <c r="M51" s="43">
         <v>3.34</v>
       </c>
-      <c r="N51" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O51" s="21">
+      <c r="N51" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O51" s="43">
         <v>3.34</v>
       </c>
-      <c r="P51" s="13">
+      <c r="P51" s="44">
         <v>2026</v>
       </c>
-      <c r="Q51" s="13">
+      <c r="Q51" s="44">
         <v>2031</v>
       </c>
-      <c r="R51" s="13">
+      <c r="R51" s="44">
         <v>2041</v>
       </c>
-      <c r="S51" s="4" t="s">
+      <c r="S51" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T51" s="14">
+      <c r="T51" s="45">
         <v>31982730</v>
       </c>
-      <c r="U51" s="14">
+      <c r="U51" s="45">
         <v>1400000000</v>
       </c>
-      <c r="V51" s="5">
+      <c r="V51" s="46">
         <v>43.833424400937297</v>
       </c>
-      <c r="W51" s="5">
+      <c r="W51" s="46">
         <v>-0.82662848923265397</v>
       </c>
-      <c r="X51" s="4" t="s">
+      <c r="X51" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="Y51" s="11" t="s">
+      <c r="Y51" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="Z51" s="11" t="s">
+      <c r="Z51" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA51" s="25" t="s">
+      <c r="AA51" s="47" t="s">
         <v>404</v>
       </c>
-      <c r="AB51" s="11" t="s">
+      <c r="AB51" s="41" t="s">
         <v>405</v>
       </c>
-      <c r="AC51" s="11" t="s">
+      <c r="AC51" s="41" t="s">
         <v>406</v>
       </c>
-      <c r="AD51" s="48" t="s">
+      <c r="AD51" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:30" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H52" s="50">
         <v>0.4</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52" s="51">
         <v>0.4</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52" s="51">
         <v>0.4</v>
       </c>
-      <c r="K52" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L52" s="22">
+      <c r="K52" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L52" s="51">
         <v>4</v>
       </c>
-      <c r="M52" s="22">
+      <c r="M52" s="51">
         <v>4</v>
       </c>
-      <c r="N52" s="22">
+      <c r="N52" s="51">
         <v>4</v>
       </c>
-      <c r="O52" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P52" s="17">
+      <c r="O52" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P52" s="52">
         <v>2022</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="Q52" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="R52" s="17" t="s">
+      <c r="R52" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="S52" s="3" t="s">
+      <c r="S52" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="T52" s="18">
+      <c r="T52" s="53">
         <v>88286266</v>
       </c>
-      <c r="U52" s="18" t="s">
+      <c r="U52" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V52" s="7">
+      <c r="V52" s="54">
         <v>60.306100000000001</v>
       </c>
-      <c r="W52" s="7">
+      <c r="W52" s="54">
         <v>25.498100000000001</v>
       </c>
-      <c r="X52" s="3" t="s">
+      <c r="X52" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y52" s="15" t="s">
+      <c r="Y52" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="Z52" s="15" t="s">
+      <c r="Z52" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA52" s="25" t="s">
+      <c r="AA52" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="AB52" s="15" t="s">
+      <c r="AB52" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AC52" s="15" t="s">
+      <c r="AC52" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD52" s="50" t="s">
+      <c r="AD52" s="17" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="53" spans="1:30" ht="114" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B53" s="41" t="s">
+      <c r="B53" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="H53" s="12">
+      <c r="H53" s="48">
         <v>1.72E-2</v>
       </c>
-      <c r="I53" s="21">
+      <c r="I53" s="43">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="J53" s="21">
+      <c r="J53" s="43">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="K53" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L53" s="21">
+      <c r="K53" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L53" s="43">
         <v>0.17199999999999999</v>
       </c>
-      <c r="M53" s="21">
+      <c r="M53" s="43">
         <v>0.15</v>
       </c>
-      <c r="N53" s="21">
+      <c r="N53" s="43">
         <v>0.15</v>
       </c>
-      <c r="O53" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P53" s="13">
+      <c r="O53" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P53" s="44">
         <v>2021</v>
       </c>
-      <c r="Q53" s="13">
+      <c r="Q53" s="44">
         <v>2025</v>
       </c>
-      <c r="R53" s="13">
+      <c r="R53" s="44">
         <v>2035</v>
       </c>
-      <c r="S53" s="4" t="s">
+      <c r="S53" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="T53" s="14">
+      <c r="T53" s="45">
         <v>3867988</v>
       </c>
-      <c r="U53" s="14" t="s">
+      <c r="U53" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V53" s="5">
+      <c r="V53" s="46">
         <v>64.037112316635401</v>
       </c>
-      <c r="W53" s="5">
+      <c r="W53" s="46">
         <v>-21.4004875161618</v>
       </c>
-      <c r="X53" s="4" t="s">
+      <c r="X53" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y53" s="11" t="s">
+      <c r="Y53" s="41" t="s">
         <v>410</v>
       </c>
-      <c r="Z53" s="11" t="s">
+      <c r="Z53" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA53" s="25" t="s">
+      <c r="AA53" s="47" t="s">
         <v>411</v>
       </c>
-      <c r="AB53" s="11" t="s">
+      <c r="AB53" s="41" t="s">
         <v>413</v>
       </c>
-      <c r="AC53" s="11" t="s">
+      <c r="AC53" s="41" t="s">
         <v>414</v>
       </c>
-      <c r="AD53" s="44" t="s">
+      <c r="AD53" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="B54" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="40" t="s">
         <v>469</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="41" t="s">
         <v>416</v>
       </c>
-      <c r="H54" s="12">
+      <c r="H54" s="48">
         <v>0.16981750000000001</v>
       </c>
-      <c r="I54" s="21">
+      <c r="I54" s="43">
         <v>0.126</v>
       </c>
-      <c r="J54" s="21">
+      <c r="J54" s="43">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="K54" s="21">
+      <c r="K54" s="43">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="L54" s="21">
+      <c r="L54" s="43">
         <v>1.69</v>
       </c>
-      <c r="M54" s="21">
+      <c r="M54" s="43">
         <v>1.26</v>
       </c>
-      <c r="N54" s="21">
+      <c r="N54" s="43">
         <v>0.87</v>
       </c>
-      <c r="O54" s="21">
+      <c r="O54" s="43">
         <v>0.34</v>
       </c>
-      <c r="P54" s="13">
+      <c r="P54" s="44">
         <v>2026</v>
       </c>
-      <c r="Q54" s="13">
+      <c r="Q54" s="44">
         <v>2031</v>
       </c>
-      <c r="R54" s="13">
+      <c r="R54" s="44">
         <v>2041</v>
       </c>
-      <c r="S54" s="4" t="s">
+      <c r="S54" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T54" s="14">
+      <c r="T54" s="45">
         <v>40000000</v>
       </c>
-      <c r="U54" s="14" t="s">
+      <c r="U54" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V54" s="5">
+      <c r="V54" s="46">
         <v>59.127044152710397</v>
       </c>
-      <c r="W54" s="5">
+      <c r="W54" s="46">
         <v>9.6218923201747906</v>
       </c>
-      <c r="X54" s="4" t="s">
+      <c r="X54" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="Y54" s="11" t="s">
+      <c r="Y54" s="41" t="s">
         <v>420</v>
       </c>
-      <c r="Z54" s="11" t="s">
+      <c r="Z54" s="41" t="s">
         <v>461</v>
       </c>
-      <c r="AA54" s="25" t="s">
+      <c r="AA54" s="47" t="s">
         <v>417</v>
       </c>
-      <c r="AB54" s="11" t="s">
+      <c r="AB54" s="41" t="s">
         <v>418</v>
       </c>
-      <c r="AC54" s="11" t="s">
+      <c r="AC54" s="41" t="s">
         <v>419</v>
       </c>
-      <c r="AD54" s="48" t="s">
+      <c r="AD54" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="41" t="s">
+      <c r="B55" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="41" t="s">
         <v>457</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="H55" s="12">
+      <c r="H55" s="48">
         <v>4.2</v>
       </c>
-      <c r="I55" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="J55" s="21">
+      <c r="I55" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="J55" s="43">
         <v>4.2750000000000004</v>
       </c>
-      <c r="K55" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L55" s="21">
+      <c r="K55" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L55" s="43">
         <v>42.05</v>
       </c>
-      <c r="M55" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="N55" s="21">
+      <c r="M55" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="N55" s="43">
         <v>42.75</v>
       </c>
-      <c r="O55" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P55" s="13">
+      <c r="O55" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P55" s="44">
         <v>2025</v>
       </c>
-      <c r="Q55" s="13">
+      <c r="Q55" s="44">
         <v>2029</v>
       </c>
-      <c r="R55" s="13">
+      <c r="R55" s="44">
         <v>2039</v>
       </c>
-      <c r="S55" s="4" t="s">
+      <c r="S55" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T55" s="14">
+      <c r="T55" s="45">
         <v>225000000</v>
       </c>
-      <c r="U55" s="14" t="s">
+      <c r="U55" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V55" s="4">
+      <c r="V55" s="39">
         <v>57.788622470324199</v>
       </c>
-      <c r="W55" s="4">
+      <c r="W55" s="39">
         <v>4.4366416948962097</v>
       </c>
-      <c r="X55" s="4" t="s">
+      <c r="X55" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="Y55" s="11" t="s">
+      <c r="Y55" s="41" t="s">
         <v>422</v>
       </c>
-      <c r="Z55" s="11" t="s">
+      <c r="Z55" s="41" t="s">
         <v>465</v>
       </c>
-      <c r="AA55" s="25" t="s">
+      <c r="AA55" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="AB55" s="11" t="s">
+      <c r="AB55" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="AC55" s="11" t="s">
+      <c r="AC55" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="AD55" s="51" t="s">
+      <c r="AD55" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="56" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="41" t="s">
+      <c r="B56" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="40" t="s">
         <v>424</v>
       </c>
-      <c r="H56" s="12">
+      <c r="H56" s="48">
         <v>0.17</v>
       </c>
-      <c r="I56" s="21">
+      <c r="I56" s="43">
         <v>0.16</v>
       </c>
-      <c r="J56" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K56" s="21">
+      <c r="J56" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K56" s="43">
         <v>0.16</v>
       </c>
-      <c r="L56" s="21">
+      <c r="L56" s="43">
         <v>1.6419999999999999</v>
       </c>
-      <c r="M56" s="21">
+      <c r="M56" s="43">
         <v>1.6</v>
       </c>
-      <c r="N56" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O56" s="21">
+      <c r="N56" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O56" s="43">
         <v>1.6</v>
       </c>
-      <c r="P56" s="13">
+      <c r="P56" s="44">
         <v>2026</v>
       </c>
-      <c r="Q56" s="13">
+      <c r="Q56" s="44">
         <v>2032</v>
       </c>
-      <c r="R56" s="13">
+      <c r="R56" s="44">
         <v>2042</v>
       </c>
-      <c r="S56" s="4" t="s">
+      <c r="S56" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T56" s="14">
+      <c r="T56" s="45">
         <v>40000000</v>
       </c>
-      <c r="U56" s="14">
+      <c r="U56" s="45">
         <v>800000000</v>
       </c>
-      <c r="V56" s="5">
+      <c r="V56" s="46">
         <v>47.297292165106498</v>
       </c>
-      <c r="W56" s="5">
+      <c r="W56" s="46">
         <v>-2.1625372580756901</v>
       </c>
-      <c r="X56" s="4" t="s">
+      <c r="X56" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="Y56" s="11" t="s">
+      <c r="Y56" s="41" t="s">
         <v>425</v>
       </c>
-      <c r="Z56" s="11" t="s">
+      <c r="Z56" s="41" t="s">
         <v>462</v>
       </c>
-      <c r="AA56" s="25" t="s">
+      <c r="AA56" s="47" t="s">
         <v>426</v>
       </c>
-      <c r="AB56" s="11" t="s">
+      <c r="AB56" s="41" t="s">
         <v>427</v>
       </c>
-      <c r="AC56" s="11" t="s">
+      <c r="AC56" s="41" t="s">
         <v>428</v>
       </c>
-      <c r="AD56" s="70" t="s">
+      <c r="AD56" s="37" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="57" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B57" s="41" t="s">
+      <c r="B57" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="41" t="s">
         <v>457</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="40" t="s">
         <v>429</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="40" t="s">
         <v>429</v>
       </c>
-      <c r="H57" s="12">
+      <c r="H57" s="48">
         <v>2</v>
       </c>
-      <c r="I57" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="J57" s="21">
+      <c r="I57" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="J57" s="43">
         <v>2</v>
       </c>
-      <c r="K57" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L57" s="21">
+      <c r="K57" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L57" s="43">
         <v>20</v>
       </c>
-      <c r="M57" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="N57" s="21">
-        <v>54</v>
-      </c>
-      <c r="O57" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P57" s="13">
+      <c r="M57" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="N57" s="43">
+        <v>54</v>
+      </c>
+      <c r="O57" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P57" s="44">
         <v>2025</v>
       </c>
-      <c r="Q57" s="13">
+      <c r="Q57" s="44">
         <v>2031</v>
       </c>
-      <c r="R57" s="13">
+      <c r="R57" s="44">
         <v>2041</v>
       </c>
-      <c r="S57" s="4" t="s">
+      <c r="S57" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T57" s="14">
+      <c r="T57" s="45">
         <v>205061582</v>
       </c>
-      <c r="U57" s="14" t="s">
+      <c r="U57" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="V57" s="5">
+      <c r="V57" s="46">
         <v>40.8482802817337</v>
       </c>
-      <c r="W57" s="5">
+      <c r="W57" s="46">
         <v>1.6966936283218199</v>
       </c>
-      <c r="X57" s="4" t="s">
+      <c r="X57" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="Y57" s="11" t="s">
+      <c r="Y57" s="41" t="s">
         <v>430</v>
       </c>
-      <c r="Z57" s="11" t="s">
+      <c r="Z57" s="41" t="s">
         <v>465</v>
       </c>
-      <c r="AA57" s="6" t="s">
+      <c r="AA57" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="AB57" s="11" t="s">
+      <c r="AB57" s="41" t="s">
         <v>431</v>
       </c>
-      <c r="AC57" s="11" t="s">
+      <c r="AC57" s="41" t="s">
         <v>432</v>
       </c>
-      <c r="AD57" s="51" t="s">
+      <c r="AD57" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="58" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="41" t="s">
+      <c r="B58" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="H58" s="31">
+      <c r="H58" s="56">
         <v>7.8E-2</v>
       </c>
-      <c r="I58" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="J58" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K58" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L58" s="35">
+      <c r="I58" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="J58" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="K58" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L58" s="70">
         <v>0.784304</v>
       </c>
-      <c r="M58" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="N58" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="O58" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="P58" s="13">
+      <c r="M58" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="N58" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O58" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P58" s="44">
         <v>2025</v>
       </c>
-      <c r="Q58" s="13">
+      <c r="Q58" s="44">
         <v>2030</v>
       </c>
-      <c r="R58" s="13">
+      <c r="R58" s="44">
         <v>2040</v>
       </c>
-      <c r="S58" s="4" t="s">
+      <c r="S58" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="T58" s="14">
+      <c r="T58" s="45">
         <v>29401945</v>
       </c>
-      <c r="U58" s="14">
+      <c r="U58" s="45">
         <v>100000000</v>
       </c>
-      <c r="V58" s="5">
+      <c r="V58" s="46">
         <v>38.714642196750198</v>
       </c>
-      <c r="W58" s="5">
+      <c r="W58" s="46">
         <v>23.058033778902399</v>
       </c>
-      <c r="X58" s="4" t="s">
+      <c r="X58" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="Y58" s="11" t="s">
+      <c r="Y58" s="41" t="s">
         <v>443</v>
       </c>
-      <c r="Z58" s="11" t="s">
+      <c r="Z58" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="AA58" s="25" t="s">
+      <c r="AA58" s="47" t="s">
         <v>440</v>
       </c>
-      <c r="AB58" s="11" t="s">
+      <c r="AB58" s="41" t="s">
         <v>441</v>
       </c>
-      <c r="AC58" s="11" t="s">
+      <c r="AC58" s="41" t="s">
         <v>442</v>
       </c>
-      <c r="AD58" s="51" t="s">
+      <c r="AD58" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="59" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B59" s="42" t="s">
+      <c r="B59" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="60">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="I59" s="22">
+      <c r="I59" s="51">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="J59" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K59" s="22">
+      <c r="J59" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K59" s="51">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="L59" s="22">
+      <c r="L59" s="51">
         <v>0.86</v>
       </c>
-      <c r="M59" s="22">
+      <c r="M59" s="51">
         <v>0.56000000000000005</v>
       </c>
-      <c r="N59" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O59" s="22">
+      <c r="N59" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O59" s="51">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P59" s="17">
+      <c r="P59" s="52">
         <v>2024</v>
       </c>
-      <c r="Q59" s="17">
+      <c r="Q59" s="52">
         <v>2028</v>
       </c>
-      <c r="R59" s="17">
+      <c r="R59" s="52">
         <v>2038</v>
       </c>
-      <c r="S59" s="3" t="s">
+      <c r="S59" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="T59" s="18">
+      <c r="T59" s="53">
         <v>48846672</v>
       </c>
-      <c r="U59" s="18">
+      <c r="U59" s="53">
         <v>130000000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="49">
         <v>43.463112000000002</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="49">
         <v>-8.2351799999999997</v>
       </c>
-      <c r="X59" s="3" t="s">
+      <c r="X59" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="Y59" s="15" t="s">
+      <c r="Y59" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="Z59" s="15" t="s">
+      <c r="Z59" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="AA59" s="8" t="s">
+      <c r="AA59" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="AB59" s="15" t="s">
+      <c r="AB59" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="AC59" s="15" t="s">
+      <c r="AC59" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="AD59" s="71" t="s">
+      <c r="AD59" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="60" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B60" s="42" t="s">
+      <c r="B60" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="H60" s="16">
+      <c r="H60" s="50">
         <v>1.2</v>
       </c>
-      <c r="I60" s="22">
+      <c r="I60" s="51">
         <v>1.2</v>
       </c>
-      <c r="J60" s="22">
+      <c r="J60" s="51">
         <v>1.2</v>
       </c>
-      <c r="K60" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L60" s="22">
+      <c r="K60" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L60" s="51">
         <v>12</v>
       </c>
-      <c r="M60" s="22">
+      <c r="M60" s="51">
         <v>12</v>
       </c>
-      <c r="N60" s="22">
+      <c r="N60" s="51">
         <v>12</v>
       </c>
-      <c r="O60" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P60" s="17">
+      <c r="O60" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P60" s="52">
         <v>2026</v>
       </c>
-      <c r="Q60" s="17">
+      <c r="Q60" s="52">
         <v>2030</v>
       </c>
-      <c r="R60" s="17">
+      <c r="R60" s="52">
         <v>2040</v>
       </c>
-      <c r="S60" s="3" t="s">
+      <c r="S60" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T60" s="18">
+      <c r="T60" s="53">
         <v>149998000</v>
       </c>
-      <c r="U60" s="18">
+      <c r="U60" s="53">
         <v>1500000000</v>
       </c>
-      <c r="V60" s="7">
+      <c r="V60" s="54">
         <v>45.803797039587103</v>
       </c>
-      <c r="W60" s="7">
+      <c r="W60" s="54">
         <v>5.4216006729600599</v>
       </c>
-      <c r="X60" s="3" t="s">
+      <c r="X60" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="Y60" s="15" t="s">
+      <c r="Y60" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="Z60" s="15" t="s">
+      <c r="Z60" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="AA60" s="25" t="s">
+      <c r="AA60" s="47" t="s">
         <v>435</v>
       </c>
-      <c r="AB60" s="15" t="s">
+      <c r="AB60" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="AC60" s="15" t="s">
+      <c r="AC60" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="AD60" s="51" t="s">
+      <c r="AD60" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="61" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B61" s="42" t="s">
+      <c r="B61" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="D61" s="15" t="s">
+      <c r="D61" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H61" s="16">
+      <c r="H61" s="50">
         <v>0.1</v>
       </c>
-      <c r="I61" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J61" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K61" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L61" s="22">
+      <c r="I61" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J61" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="K61" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L61" s="51">
         <v>1</v>
       </c>
-      <c r="M61" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N61" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="O61" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="P61" s="17">
+      <c r="M61" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="N61" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O61" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="P61" s="52">
         <v>2026</v>
       </c>
-      <c r="Q61" s="17">
+      <c r="Q61" s="52">
         <v>2030</v>
       </c>
-      <c r="R61" s="17">
+      <c r="R61" s="52">
         <v>2040</v>
       </c>
-      <c r="S61" s="3" t="s">
+      <c r="S61" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="T61" s="18">
+      <c r="T61" s="53">
         <v>26200000</v>
       </c>
-      <c r="U61" s="18" t="s">
+      <c r="U61" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="V61" s="7">
+      <c r="V61" s="54">
         <v>59.242157075260003</v>
       </c>
-      <c r="W61" s="7">
+      <c r="W61" s="54">
         <v>11.046906259539099</v>
       </c>
-      <c r="X61" s="3" t="s">
+      <c r="X61" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="Y61" s="15" t="s">
+      <c r="Y61" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="Z61" s="15" t="s">
+      <c r="Z61" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="AA61" s="25" t="s">
+      <c r="AA61" s="47" t="s">
         <v>438</v>
       </c>
-      <c r="AB61" s="15" t="s">
+      <c r="AB61" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="AC61" s="15" t="s">
+      <c r="AC61" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="AD61" s="48" t="s">
+      <c r="AD61" s="15" t="s">
         <v>447</v>
       </c>
     </row>
@@ -8149,7 +8102,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId61"/>
-  <legacyDrawing r:id="rId62"/>
 </worksheet>
 </file>
 
@@ -8161,194 +8113,194 @@
   <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.21875" style="52" customWidth="1"/>
-    <col min="2" max="2" width="5" style="52" customWidth="1"/>
-    <col min="3" max="3" width="55" style="52" customWidth="1"/>
-    <col min="4" max="5" width="5" style="52" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="52"/>
+    <col min="1" max="1" width="36.21875" style="19" customWidth="1"/>
+    <col min="2" max="2" width="5" style="19" customWidth="1"/>
+    <col min="3" max="3" width="55" style="19" customWidth="1"/>
+    <col min="4" max="5" width="5" style="19" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="72"/>
+      <c r="B1" s="71"/>
     </row>
     <row r="2" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="62"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="3" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="56"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="23"/>
     </row>
     <row r="4" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="35" t="s">
         <v>446</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="22" t="s">
         <v>483</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="56"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="34" t="s">
         <v>445</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="22" t="s">
         <v>484</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="56"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="23"/>
     </row>
     <row r="6" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="36" t="s">
         <v>444</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="22" t="s">
         <v>485</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="56"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="22" t="s">
         <v>486</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="56"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="22" t="s">
         <v>487</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="56"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="23"/>
     </row>
     <row r="9" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="24" t="s">
         <v>488</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="59"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="53"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmeurope-my.sharepoint.com/personal/salman_muhammad_cmeurope_org/Documents/Technical/IF mapping tool/if-map/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1965" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EB866FB-CDF0-4B08-886C-B125D881B4FA}"/>
+  <xr:revisionPtr revIDLastSave="1966" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE30B954-1CC2-40C2-BC7D-7914E21575A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="492">
   <si>
     <t>Status</t>
   </si>
@@ -1524,6 +1524,9 @@
   </si>
   <si>
     <t>The project applies oxyfuel combustion and a CO₂ compression and purification unit (CPU) at the Holcim Lägerdorf cement plant to capture approximately 1.3 Mt CO₂ per year. Captured CO₂ is then processed through a thyssenkrupp/Linde CPU and utilised as a feedstock for the production of industrial chemicals, including methanol and plastic precursors, enabling CCU-based carbon conversion.</t>
+  </si>
+  <si>
+    <t>Vow Green Metals</t>
   </si>
 </sst>
 </file>
@@ -7961,7 +7964,7 @@
         <v>9</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>192</v>
+        <v>491</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>192</v>
@@ -8312,6 +8315,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100052CBA820BEBCD468114CF62615C95D9" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41d93ad2b4fecab14cfdaed9255371f8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ba695df1-2cef-45b3-b38e-525c8136ab22" xmlns:ns3="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a815193907c452009623866744c535" ns2:_="" ns3:_="">
     <xsd:import namespace="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
@@ -8552,27 +8575,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39E8DA8-D782-4F69-B46B-77021BF1B166}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82507086-9DCD-4197-A4F6-ECCED658E0D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8589,29 +8617,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39E8DA8-D782-4F69-B46B-77021BF1B166}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmeurope-my.sharepoint.com/personal/salman_muhammad_cmeurope_org/Documents/Technical/IF mapping tool/if-map/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1966" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE30B954-1CC2-40C2-BC7D-7914E21575A6}"/>
+  <xr:revisionPtr revIDLastSave="1973" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{164D9154-FC1A-46A4-A5AF-5583A80CF09C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -410,9 +410,6 @@
     <t>eM-Rhone</t>
   </si>
   <si>
-    <t>Elyse Energy</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101133147.pdf </t>
   </si>
   <si>
@@ -1076,12 +1073,6 @@
     <t>GIE OSIRIS</t>
   </si>
   <si>
-    <t>eM-Rhône is a French carbon capture and utilisation project led by Elyse Energy. It combines renewable hydrogen production on the Roches-Roussillon chemical platform in Salaise-sur-Sanne with carbon dioxide captured at Holcim/Lafarge’s cement plant in Le Teil, Ardèche, and transported by rail to the methanol site. The project is designed around 170 MW of PEM electrolysis, about 27 kt/year of hydrogen production, and about 195 kt/year of CO₂ use to produce large-scale e-methanol for chemical and maritime markets.</t>
-  </si>
-  <si>
-    <t>The project captures concentrated CO₂ from the Le Teil cement plant using a fully electric cryogenic capture scheme, liquefies and transports the CO₂ by rail to Salaise-sur-Sanne, then receives, stores, regasifies and purifies the CO₂ before reaction with hydrogen produced on site by 170 MW PEM electrolysis. The hydrogen is compressed and purified, then combined with the purified CO₂ in a methanol synthesis unit, followed by intermediate storage and final methanol storage via the adjacent TEPSA logistics system. The updated Innovation Fund factsheet gives 195 kt/year CO₂ input, 27 kt/year hydrogen production and 138 kt/year methanol output; Elyse’s project page still states 150 kt/year methanol.</t>
-  </si>
-  <si>
     <t>Usine Lafarge, 07220 Viviers, France</t>
   </si>
   <si>
@@ -1527,6 +1518,15 @@
   </si>
   <si>
     <t>Vow Green Metals</t>
+  </si>
+  <si>
+    <t>Elyse Energy, Lafarge (Holcim)</t>
+  </si>
+  <si>
+    <t>eM-Rhône is a joint venture of Elyse Energy and Lafarge Cement (Holcim). It combines renewable hydrogen production on the Roches-Roussillon chemical platform in Salaise-sur-Sanne with CO₂ captured at Holcim/Lafarge’s cement plant in Le Teil, Ardèche, and transported by rail to the methanol site. The project is designed around 170 MW of PEM electrolysis, about 27 kt/year of hydrogen production, and about 195 kt/year of CO₂ use to produce large-scale e-methanol for chemical and maritime markets.</t>
+  </si>
+  <si>
+    <t>The project captures concentrated CO₂ from the Le Teil cement plant using a fully electric cryogenic capture scheme, liquefies and transports the CO₂ by rail to Salaise-sur-Sanne, then receives, stores, regasifies and purifies the CO₂ before reaction with hydrogen produced on site by 170 MW PEM electrolysis. The hydrogen is compressed and purified, then combined with the purified CO₂ in a methanol synthesis unit, followed by intermediate storage and final methanol storage via the adjacent TEPSA logistics system. The updated Innovation Fund factsheet gives 195 kt/year CO₂ input, 27 kt/year hydrogen production and 138 kt/year methanol output.</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1883,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2097,6 +2097,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2493,10 +2496,10 @@
         <v>37</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>38</v>
@@ -2597,7 +2600,7 @@
         <v>220123498</v>
       </c>
       <c r="U2" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V2" s="46">
         <v>57.062100000000001</v>
@@ -2612,19 +2615,19 @@
         <v>95</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA2" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AB2" s="41" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AC2" s="41" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AD2" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -2632,10 +2635,10 @@
         <v>96</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>70</v>
@@ -2644,10 +2647,10 @@
         <v>19</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="48">
         <v>0.12330000000000001</v>
@@ -2689,7 +2692,7 @@
         <v>31238542</v>
       </c>
       <c r="U3" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V3" s="46">
         <v>44.464755134852901</v>
@@ -2701,22 +2704,22 @@
         <v>57</v>
       </c>
       <c r="Y3" s="41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Z3" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA3" s="47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AB3" s="41" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AC3" s="41" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AD3" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
@@ -2724,10 +2727,10 @@
         <v>59</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>103</v>
@@ -2736,10 +2739,10 @@
         <v>15</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H4" s="50" t="s">
         <v>54</v>
@@ -2781,7 +2784,7 @@
         <v>3168000</v>
       </c>
       <c r="U4" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V4" s="54">
         <v>43.327720234653299</v>
@@ -2793,19 +2796,19 @@
         <v>57</v>
       </c>
       <c r="Y4" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="AA4" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="Z4" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="AA4" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AC4" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="AD4" s="12" t="s">
         <v>2</v>
@@ -2816,13 +2819,13 @@
         <v>78</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C5" s="40" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E5" s="40" t="s">
         <v>5</v>
@@ -2858,7 +2861,7 @@
         <v>54</v>
       </c>
       <c r="P5" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q5" s="44">
         <v>2030</v>
@@ -2873,7 +2876,7 @@
         <v>145000000</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V5" s="46">
         <v>46.809800000000003</v>
@@ -2885,22 +2888,22 @@
         <v>57</v>
       </c>
       <c r="Y5" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Z5" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA5" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB5" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="AB5" s="41" t="s">
+      <c r="AC5" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="AC5" s="41" t="s">
-        <v>243</v>
-      </c>
       <c r="AD5" s="14" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
@@ -2908,10 +2911,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D6" s="41" t="s">
         <v>103</v>
@@ -2920,10 +2923,10 @@
         <v>8</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H6" s="48">
         <v>2.5999999999999999E-2</v>
@@ -2965,7 +2968,7 @@
         <v>7958244</v>
       </c>
       <c r="U6" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V6" s="39" t="s">
         <v>54</v>
@@ -2974,25 +2977,25 @@
         <v>54</v>
       </c>
       <c r="X6" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y6" s="41" t="s">
         <v>54</v>
       </c>
       <c r="Z6" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA6" s="47" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AB6" s="41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AC6" s="41" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AD6" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -3057,7 +3060,7 @@
         <v>189694949</v>
       </c>
       <c r="U7" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V7" s="46">
         <v>43.232830995956597</v>
@@ -3069,22 +3072,22 @@
         <v>89</v>
       </c>
       <c r="Y7" s="41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Z7" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA7" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB7" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="AC7" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="AB7" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="AC7" s="41" t="s">
-        <v>250</v>
-      </c>
       <c r="AD7" s="16" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3134,7 +3137,7 @@
         <v>54</v>
       </c>
       <c r="P8" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q8" s="44">
         <v>2029</v>
@@ -3149,7 +3152,7 @@
         <v>115000000</v>
       </c>
       <c r="U8" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V8" s="46">
         <v>50.575420999999999</v>
@@ -3164,19 +3167,19 @@
         <v>82</v>
       </c>
       <c r="Z8" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA8" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AB8" s="41" t="s">
         <v>83</v>
       </c>
       <c r="AC8" s="41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AD8" s="14" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -3184,22 +3187,22 @@
         <v>78</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H9" s="50">
         <v>2.5819174</v>
@@ -3241,7 +3244,7 @@
         <v>169300000</v>
       </c>
       <c r="U9" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V9" s="54">
         <v>37.960247145532399</v>
@@ -3253,22 +3256,22 @@
         <v>57</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AA9" s="47" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB9" s="7" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AC9" s="7" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AD9" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -3276,22 +3279,22 @@
         <v>49</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E10" s="40" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H10" s="48" t="s">
         <v>54</v>
@@ -3345,19 +3348,19 @@
         <v>57</v>
       </c>
       <c r="Y10" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z10" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA10" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AB10" s="41" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AD10" s="12" t="s">
         <v>2</v>
@@ -3368,10 +3371,10 @@
         <v>84</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D11" s="41" t="s">
         <v>103</v>
@@ -3380,10 +3383,10 @@
         <v>9</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>54</v>
@@ -3425,7 +3428,7 @@
         <v>10206000</v>
       </c>
       <c r="U11" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V11" s="46">
         <v>59.592303479664103</v>
@@ -3434,25 +3437,25 @@
         <v>5.8029778441568904</v>
       </c>
       <c r="X11" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y11" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z11" s="41" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA11" s="47" t="s">
+        <v>296</v>
+      </c>
+      <c r="AB11" s="41" t="s">
         <v>300</v>
       </c>
-      <c r="Z11" s="41" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA11" s="47" t="s">
-        <v>297</v>
-      </c>
-      <c r="AB11" s="41" t="s">
+      <c r="AC11" s="41" t="s">
         <v>301</v>
       </c>
-      <c r="AC11" s="41" t="s">
-        <v>302</v>
-      </c>
       <c r="AD11" s="14" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -3460,7 +3463,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>69</v>
@@ -3472,10 +3475,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H12" s="50">
         <v>1.3</v>
@@ -3529,22 +3532,22 @@
         <v>57</v>
       </c>
       <c r="Y12" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA12" s="47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AB12" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AC12" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AD12" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3621,22 +3624,22 @@
         <v>57</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA13" s="57" t="s">
         <v>117</v>
       </c>
       <c r="AB13" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="AC13" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="AC13" s="7" t="s">
-        <v>269</v>
-      </c>
       <c r="AD13" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -3644,10 +3647,10 @@
         <v>96</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>70</v>
@@ -3656,10 +3659,10 @@
         <v>19</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H14" s="50">
         <v>6.4000000000000001E-2</v>
@@ -3701,7 +3704,7 @@
         <v>23635998</v>
       </c>
       <c r="U14" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V14" s="54">
         <v>44.826999999999998</v>
@@ -3710,25 +3713,25 @@
         <v>11.614000000000001</v>
       </c>
       <c r="X14" s="49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA14" s="47" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AB14" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="AC14" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="AC14" s="7" t="s">
-        <v>293</v>
-      </c>
       <c r="AD14" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="148.19999999999999" x14ac:dyDescent="0.3">
@@ -3736,7 +3739,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>69</v>
@@ -3748,10 +3751,10 @@
         <v>5</v>
       </c>
       <c r="F15" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="H15" s="50">
         <v>0.7</v>
@@ -3793,7 +3796,7 @@
         <v>119682059</v>
       </c>
       <c r="U15" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V15" s="54">
         <v>43.186100000000003</v>
@@ -3805,22 +3808,22 @@
         <v>57</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA15" s="47" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AB15" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AC15" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AD15" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3828,7 +3831,7 @@
         <v>78</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>69</v>
@@ -3840,10 +3843,10 @@
         <v>22</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H16" s="48" t="s">
         <v>54</v>
@@ -3885,7 +3888,7 @@
         <v>146415990</v>
       </c>
       <c r="U16" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V16" s="46">
         <v>45.290985428950698</v>
@@ -3894,25 +3897,25 @@
         <v>25.1109549184484</v>
       </c>
       <c r="X16" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y16" s="41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Z16" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA16" s="47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AB16" s="41" t="s">
+        <v>306</v>
+      </c>
+      <c r="AC16" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="AC16" s="41" t="s">
-        <v>308</v>
-      </c>
       <c r="AD16" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3920,10 +3923,10 @@
         <v>59</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D17" s="41" t="s">
         <v>70</v>
@@ -3932,10 +3935,10 @@
         <v>6</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H17" s="58">
         <v>4.5999999999999999E-3</v>
@@ -3977,7 +3980,7 @@
         <v>30497000</v>
       </c>
       <c r="U17" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V17" s="39">
         <v>51.870851200822599</v>
@@ -3986,22 +3989,22 @@
         <v>4.30094696894741</v>
       </c>
       <c r="X17" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y17" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Z17" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA17" s="59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB17" s="41" t="s">
+        <v>310</v>
+      </c>
+      <c r="AC17" s="41" t="s">
         <v>311</v>
-      </c>
-      <c r="AC17" s="41" t="s">
-        <v>312</v>
       </c>
       <c r="AD17" s="12" t="s">
         <v>2</v>
@@ -4012,7 +4015,7 @@
         <v>49</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>69</v>
@@ -4024,10 +4027,10 @@
         <v>11</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" s="40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="43">
         <v>1.3</v>
@@ -4069,7 +4072,7 @@
         <v>157000000</v>
       </c>
       <c r="U18" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V18" s="46">
         <v>52.489100000000001</v>
@@ -4081,22 +4084,22 @@
         <v>57</v>
       </c>
       <c r="Y18" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z18" s="41" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA18" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="Z18" s="41" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA18" s="59" t="s">
-        <v>146</v>
-      </c>
       <c r="AB18" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="AC18" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="AC18" s="41" t="s">
-        <v>274</v>
-      </c>
       <c r="AD18" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="45.6" x14ac:dyDescent="0.3">
@@ -4161,7 +4164,7 @@
         <v>4265136</v>
       </c>
       <c r="U19" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V19" s="54">
         <v>50.569000000000003</v>
@@ -4176,10 +4179,10 @@
         <v>65</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA19" s="47" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AB19" s="7" t="s">
         <v>66</v>
@@ -4196,22 +4199,22 @@
         <v>49</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H20" s="50">
         <v>2.11</v>
@@ -4265,22 +4268,22 @@
         <v>57</v>
       </c>
       <c r="Y20" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z20" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="AA20" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="Z20" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="AA20" s="57" t="s">
-        <v>168</v>
-      </c>
       <c r="AB20" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="AC20" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="AC20" s="7" t="s">
-        <v>316</v>
-      </c>
       <c r="AD20" s="17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4288,13 +4291,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>15</v>
@@ -4303,7 +4306,7 @@
         <v>114</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H21" s="60">
         <v>0.63600000000000001</v>
@@ -4333,10 +4336,10 @@
         <v>2025</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R21" s="52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S21" s="49" t="s">
         <v>81</v>
@@ -4345,7 +4348,7 @@
         <v>25400000</v>
       </c>
       <c r="U21" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V21" s="54">
         <v>41.352637812781921</v>
@@ -4357,22 +4360,22 @@
         <v>89</v>
       </c>
       <c r="Y21" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="Z21" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="AA21" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB21" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="Z21" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="AA21" s="47" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB21" s="7" t="s">
-        <v>318</v>
-      </c>
       <c r="AC21" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4380,10 +4383,10 @@
         <v>59</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="40" t="s">
         <v>169</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>170</v>
       </c>
       <c r="D22" s="41" t="s">
         <v>103</v>
@@ -4392,10 +4395,10 @@
         <v>19</v>
       </c>
       <c r="F22" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G22" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H22" s="56">
         <v>1.7904E-2</v>
@@ -4446,25 +4449,25 @@
         <v>13.253440646806</v>
       </c>
       <c r="X22" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y22" s="62" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Z22" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA22" s="47" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB22" s="41" t="s">
         <v>320</v>
       </c>
-      <c r="AB22" s="41" t="s">
+      <c r="AC22" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="AC22" s="41" t="s">
-        <v>322</v>
-      </c>
       <c r="AD22" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="136.80000000000001" x14ac:dyDescent="0.3">
@@ -4472,22 +4475,22 @@
         <v>96</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>20</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H23" s="50">
         <v>0.56499999999999995</v>
@@ -4541,22 +4544,22 @@
         <v>57</v>
       </c>
       <c r="Y23" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA23" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB23" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="AB23" s="7" t="s">
+      <c r="AC23" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="AC23" s="7" t="s">
-        <v>327</v>
-      </c>
       <c r="AD23" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4564,10 +4567,10 @@
         <v>78</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>103</v>
@@ -4576,10 +4579,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>334</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>335</v>
       </c>
       <c r="H24" s="50">
         <v>0.2</v>
@@ -4630,25 +4633,25 @@
         <v>1.1835034670687401</v>
       </c>
       <c r="X24" s="49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y24" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z24" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA24" s="47" t="s">
         <v>338</v>
       </c>
-      <c r="Z24" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA24" s="47" t="s">
-        <v>339</v>
-      </c>
       <c r="AB24" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="AC24" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="AC24" s="7" t="s">
-        <v>337</v>
-      </c>
       <c r="AD24" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -4656,7 +4659,7 @@
         <v>78</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>69</v>
@@ -4668,10 +4671,10 @@
         <v>19</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H25" s="50">
         <v>1</v>
@@ -4713,7 +4716,7 @@
         <v>216000000</v>
       </c>
       <c r="U25" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V25" s="54">
         <v>45.515127894849797</v>
@@ -4722,25 +4725,25 @@
         <v>10.343124922954001</v>
       </c>
       <c r="X25" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA25" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB25" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="AB25" s="7" t="s">
+      <c r="AC25" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="AC25" s="7" t="s">
-        <v>332</v>
-      </c>
       <c r="AD25" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4748,10 +4751,10 @@
         <v>49</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>103</v>
@@ -4760,7 +4763,7 @@
         <v>9</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>55</v>
@@ -4805,7 +4808,7 @@
         <v>40000000</v>
       </c>
       <c r="U26" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V26" s="49">
         <v>59.121267699503399</v>
@@ -4814,28 +4817,28 @@
         <v>9.6300609243118291</v>
       </c>
       <c r="X26" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y26" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Z26" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="AA26" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB26" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="AC26" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="AA26" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB26" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="AC26" s="7" t="s">
-        <v>467</v>
-      </c>
       <c r="AD26" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>49</v>
       </c>
@@ -4851,11 +4854,11 @@
       <c r="E27" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="40" t="s">
-        <v>119</v>
+      <c r="F27" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="G27" s="40" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H27" s="48">
         <v>0.23252429999999999</v>
@@ -4909,22 +4912,22 @@
         <v>57</v>
       </c>
       <c r="Y27" s="41" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Z27" s="41" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA27" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB27" s="41" t="s">
-        <v>341</v>
+        <v>119</v>
+      </c>
+      <c r="AB27" s="72" t="s">
+        <v>490</v>
       </c>
       <c r="AC27" s="41" t="s">
-        <v>342</v>
+        <v>491</v>
       </c>
       <c r="AD27" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -4935,10 +4938,10 @@
         <v>100</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E28" s="40" t="s">
         <v>17</v>
@@ -4989,7 +4992,7 @@
         <v>54000000</v>
       </c>
       <c r="U28" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V28" s="46">
         <v>54.992185868676003</v>
@@ -5001,22 +5004,22 @@
         <v>89</v>
       </c>
       <c r="Y28" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z28" s="41" t="s">
+        <v>461</v>
+      </c>
+      <c r="AA28" s="47" t="s">
+        <v>342</v>
+      </c>
+      <c r="AB28" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="AC28" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="Z28" s="41" t="s">
-        <v>464</v>
-      </c>
-      <c r="AA28" s="47" t="s">
-        <v>345</v>
-      </c>
-      <c r="AB28" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="AC28" s="41" t="s">
-        <v>347</v>
-      </c>
       <c r="AD28" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -5024,7 +5027,7 @@
         <v>49</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>61</v>
@@ -5036,10 +5039,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G29" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H29" s="43">
         <v>1.5</v>
@@ -5081,7 +5084,7 @@
         <v>228721666</v>
       </c>
       <c r="U29" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V29" s="46">
         <v>51.297800000000002</v>
@@ -5090,25 +5093,25 @@
         <v>7.0148000000000001</v>
       </c>
       <c r="X29" s="39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y29" s="41" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Z29" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA29" s="59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB29" s="41" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AC29" s="41" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AD29" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5116,22 +5119,22 @@
         <v>113</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H30" s="60">
         <v>4.5999999999999999E-2</v>
@@ -5173,7 +5176,7 @@
         <v>29500000</v>
       </c>
       <c r="U30" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V30" s="49">
         <v>60.618241659279597</v>
@@ -5182,25 +5185,25 @@
         <v>16.891107915855802</v>
       </c>
       <c r="X30" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y30" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="Z30" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA30" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB30" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="Z30" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA30" s="63" t="s">
-        <v>376</v>
-      </c>
-      <c r="AB30" s="7" t="s">
-        <v>377</v>
-      </c>
       <c r="AC30" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AD30" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5208,7 +5211,7 @@
         <v>49</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>69</v>
@@ -5265,7 +5268,7 @@
         <v>191000000</v>
       </c>
       <c r="U31" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V31" s="54">
         <v>51.618000000000002</v>
@@ -5277,22 +5280,22 @@
         <v>57</v>
       </c>
       <c r="Y31" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z31" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA31" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="Z31" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA31" s="64" t="s">
-        <v>142</v>
-      </c>
       <c r="AB31" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="AC31" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="AC31" s="7" t="s">
-        <v>291</v>
-      </c>
       <c r="AD31" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5300,7 +5303,7 @@
         <v>49</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>69</v>
@@ -5312,10 +5315,10 @@
         <v>8</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H32" s="50">
         <v>1</v>
@@ -5369,22 +5372,22 @@
         <v>57</v>
       </c>
       <c r="Y32" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="Z32" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA32" s="47" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AB32" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AC32" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AD32" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5464,19 +5467,19 @@
         <v>73</v>
       </c>
       <c r="Z33" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA33" s="47" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AB33" s="41" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AC33" s="41" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AD33" s="17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5484,19 +5487,19 @@
         <v>49</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>15</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G34" s="40"/>
       <c r="H34" s="48">
@@ -5539,7 +5542,7 @@
         <v>122900000</v>
       </c>
       <c r="U34" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V34" s="39">
         <v>43.151000000000003</v>
@@ -5548,25 +5551,25 @@
         <v>-7.6859999999999999</v>
       </c>
       <c r="X34" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y34" s="41" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Z34" s="41" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA34" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB34" s="41" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AC34" s="41" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AD34" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -5577,10 +5580,10 @@
         <v>97</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>17</v>
@@ -5589,7 +5592,7 @@
         <v>98</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H35" s="50">
         <v>0.28144999999999998</v>
@@ -5646,16 +5649,16 @@
         <v>99</v>
       </c>
       <c r="Z35" s="7" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AA35" s="47" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AB35" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="AC35" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="AC35" s="7" t="s">
-        <v>260</v>
       </c>
       <c r="AD35" s="12" t="s">
         <v>2</v>
@@ -5669,7 +5672,7 @@
         <v>74</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>70</v>
@@ -5723,7 +5726,7 @@
         <v>159000000</v>
       </c>
       <c r="U36" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V36" s="54">
         <v>51.1339349</v>
@@ -5735,22 +5738,22 @@
         <v>57</v>
       </c>
       <c r="Y36" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Z36" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA36" s="47" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AB36" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AC36" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AD36" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5758,22 +5761,22 @@
         <v>113</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="H37" s="60">
         <v>5.0046999999999999E-3</v>
@@ -5815,7 +5818,7 @@
         <v>26498650</v>
       </c>
       <c r="U37" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V37" s="54">
         <v>50.529000000000003</v>
@@ -5827,22 +5830,22 @@
         <v>57</v>
       </c>
       <c r="Y37" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Z37" s="7" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AA37" s="47" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AB37" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AC37" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AD37" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5850,7 +5853,7 @@
         <v>49</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>69</v>
@@ -5862,10 +5865,10 @@
         <v>13</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H38" s="50">
         <v>0.68</v>
@@ -5907,7 +5910,7 @@
         <v>234000000</v>
       </c>
       <c r="U38" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V38" s="54">
         <v>38.129899999999999</v>
@@ -5919,22 +5922,22 @@
         <v>57</v>
       </c>
       <c r="Y38" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z38" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA38" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="Z38" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA38" s="47" t="s">
-        <v>289</v>
-      </c>
       <c r="AB38" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC38" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="AC38" s="7" t="s">
-        <v>287</v>
-      </c>
       <c r="AD38" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5942,10 +5945,10 @@
         <v>96</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>70</v>
@@ -5954,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G39" s="40"/>
       <c r="H39" s="48">
@@ -6006,22 +6009,22 @@
         <v>12.7671053619066</v>
       </c>
       <c r="X39" s="39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y39" s="41" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Z39" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA39" s="47" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AB39" s="41" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AC39" s="41" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AD39" s="13" t="s">
         <v>2</v>
@@ -6032,22 +6035,22 @@
         <v>49</v>
       </c>
       <c r="B40" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="C40" s="40" t="s">
-        <v>154</v>
-      </c>
       <c r="D40" s="41" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E40" s="40" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H40" s="48">
         <v>0.85799999999999998</v>
@@ -6089,7 +6092,7 @@
         <v>127000000</v>
       </c>
       <c r="U40" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V40" s="46">
         <v>37.916800000000002</v>
@@ -6101,22 +6104,22 @@
         <v>57</v>
       </c>
       <c r="Y40" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z40" s="41" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA40" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="Z40" s="41" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA40" s="47" t="s">
-        <v>157</v>
-      </c>
       <c r="AB40" s="41" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AC40" s="41" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AD40" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6181,7 +6184,7 @@
         <v>356900000</v>
       </c>
       <c r="U41" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V41" s="46">
         <v>51.368588000000003</v>
@@ -6196,19 +6199,19 @@
         <v>58</v>
       </c>
       <c r="Z41" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA41" s="47" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AB41" s="41" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AC41" s="41" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AD41" s="17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6273,7 +6276,7 @@
         <v>117000000</v>
       </c>
       <c r="U42" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V42" s="54">
         <v>44.968299999999999</v>
@@ -6288,19 +6291,19 @@
         <v>92</v>
       </c>
       <c r="Z42" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA42" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AB42" s="7" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AC42" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AD42" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -6308,19 +6311,19 @@
         <v>49</v>
       </c>
       <c r="B43" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D43" s="41" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>54</v>
@@ -6365,7 +6368,7 @@
         <v>118000000</v>
       </c>
       <c r="U43" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V43" s="54">
         <v>51.976999999999997</v>
@@ -6377,22 +6380,22 @@
         <v>57</v>
       </c>
       <c r="Y43" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z43" s="7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AA43" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB43" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="AB43" s="7" t="s">
+      <c r="AC43" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="AC43" s="7" t="s">
-        <v>266</v>
-      </c>
       <c r="AD43" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
@@ -6457,7 +6460,7 @@
         <v>36000000</v>
       </c>
       <c r="U44" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V44" s="54">
         <v>50.406342306737002</v>
@@ -6469,22 +6472,22 @@
         <v>57</v>
       </c>
       <c r="Y44" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="Z44" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA44" s="47" t="s">
+        <v>377</v>
+      </c>
+      <c r="AB44" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="AC44" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="Z44" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA44" s="47" t="s">
-        <v>380</v>
-      </c>
-      <c r="AB44" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="AC44" s="7" t="s">
-        <v>382</v>
-      </c>
       <c r="AD44" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6492,19 +6495,19 @@
         <v>113</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>54</v>
@@ -6549,7 +6552,7 @@
         <v>13000000</v>
       </c>
       <c r="U45" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V45" s="49">
         <v>59.2181</v>
@@ -6558,25 +6561,25 @@
         <v>10.9298</v>
       </c>
       <c r="X45" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y45" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="Z45" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA45" s="47" t="s">
+        <v>380</v>
+      </c>
+      <c r="AB45" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="AB45" s="7" t="s">
-        <v>386</v>
-      </c>
       <c r="AC45" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AD45" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="46" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -6584,7 +6587,7 @@
         <v>49</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C46" s="40" t="s">
         <v>69</v>
@@ -6596,10 +6599,10 @@
         <v>13</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G46" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H46" s="48" t="s">
         <v>54</v>
@@ -6653,22 +6656,22 @@
         <v>57</v>
       </c>
       <c r="Y46" s="41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z46" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA46" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AB46" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC46" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="AC46" s="41" t="s">
-        <v>284</v>
-      </c>
       <c r="AD46" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -6679,7 +6682,7 @@
         <v>105</v>
       </c>
       <c r="C47" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D47" s="41" t="s">
         <v>103</v>
@@ -6688,10 +6691,10 @@
         <v>18</v>
       </c>
       <c r="F47" s="40" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G47" s="40" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H47" s="56">
         <v>1.55E-2</v>
@@ -6733,7 +6736,7 @@
         <v>8600000</v>
       </c>
       <c r="U47" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V47" s="46">
         <v>58.418889999999998</v>
@@ -6748,19 +6751,19 @@
         <v>106</v>
       </c>
       <c r="Z47" s="41" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA47" s="47" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AB47" s="41" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AC47" s="41" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AD47" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -6768,7 +6771,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>51</v>
@@ -6780,10 +6783,10 @@
         <v>21</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H48" s="50">
         <v>0.40600000000000003</v>
@@ -6825,7 +6828,7 @@
         <v>97000000</v>
       </c>
       <c r="U48" s="53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="V48" s="49">
         <v>58.099057767351503</v>
@@ -6834,25 +6837,25 @@
         <v>11.861499508001399</v>
       </c>
       <c r="X48" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y48" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Z48" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA48" s="63" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB48" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AC48" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AD48" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6863,7 +6866,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>103</v>
@@ -6872,10 +6875,10 @@
         <v>17</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H49" s="60">
         <v>6.7077999999999999E-2</v>
@@ -6917,7 +6920,7 @@
         <v>40000000</v>
       </c>
       <c r="U49" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V49" s="54">
         <v>56.787056035485499</v>
@@ -6932,19 +6935,19 @@
         <v>104</v>
       </c>
       <c r="Z49" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA49" s="47" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AB49" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AC49" s="7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AD49" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -6952,22 +6955,22 @@
         <v>84</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H50" s="50">
         <v>0.24099999999999999</v>
@@ -6997,7 +7000,7 @@
         <v>19458418</v>
       </c>
       <c r="U50" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V50" s="54">
         <v>48.096166502584701</v>
@@ -7009,22 +7012,22 @@
         <v>89</v>
       </c>
       <c r="Y50" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z50" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA50" s="47" t="s">
+        <v>397</v>
+      </c>
+      <c r="AB50" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC50" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="Z50" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA50" s="47" t="s">
-        <v>400</v>
-      </c>
-      <c r="AB50" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC50" s="7" t="s">
-        <v>402</v>
-      </c>
       <c r="AD50" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -7032,10 +7035,10 @@
         <v>78</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D51" s="41" t="s">
         <v>103</v>
@@ -7044,10 +7047,10 @@
         <v>5</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G51" s="41" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H51" s="48">
         <v>0.27411429999999998</v>
@@ -7101,22 +7104,22 @@
         <v>89</v>
       </c>
       <c r="Y51" s="41" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Z51" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA51" s="47" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AB51" s="41" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AC51" s="41" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AD51" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52" spans="1:30" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7127,7 +7130,7 @@
         <v>107</v>
       </c>
       <c r="C52" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D52" s="40" t="s">
         <v>70</v>
@@ -7181,7 +7184,7 @@
         <v>88286266</v>
       </c>
       <c r="U52" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V52" s="54">
         <v>60.306100000000001</v>
@@ -7196,7 +7199,7 @@
         <v>109</v>
       </c>
       <c r="Z52" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA52" s="47" t="s">
         <v>110</v>
@@ -7208,7 +7211,7 @@
         <v>112</v>
       </c>
       <c r="AD52" s="17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="53" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -7216,10 +7219,10 @@
         <v>59</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D53" s="41" t="s">
         <v>70</v>
@@ -7228,10 +7231,10 @@
         <v>12</v>
       </c>
       <c r="F53" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H53" s="48">
         <v>1.72E-2</v>
@@ -7273,7 +7276,7 @@
         <v>3867988</v>
       </c>
       <c r="U53" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V53" s="46">
         <v>64.037112316635401</v>
@@ -7285,19 +7288,19 @@
         <v>57</v>
       </c>
       <c r="Y53" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="Z53" s="41" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA53" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB53" s="41" t="s">
         <v>410</v>
       </c>
-      <c r="Z53" s="41" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA53" s="47" t="s">
+      <c r="AC53" s="41" t="s">
         <v>411</v>
-      </c>
-      <c r="AB53" s="41" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC53" s="41" t="s">
-        <v>414</v>
       </c>
       <c r="AD53" s="11" t="s">
         <v>3</v>
@@ -7308,22 +7311,22 @@
         <v>113</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C54" s="40" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E54" s="40" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G54" s="41" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H54" s="48">
         <v>0.16981750000000001</v>
@@ -7365,7 +7368,7 @@
         <v>40000000</v>
       </c>
       <c r="U54" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V54" s="46">
         <v>59.127044152710397</v>
@@ -7377,22 +7380,22 @@
         <v>89</v>
       </c>
       <c r="Y54" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Z54" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA54" s="47" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB54" s="41" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AC54" s="41" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AD54" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
@@ -7400,22 +7403,22 @@
         <v>49</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>9</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G55" s="40" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H55" s="48">
         <v>4.2</v>
@@ -7457,7 +7460,7 @@
         <v>225000000</v>
       </c>
       <c r="U55" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V55" s="39">
         <v>57.788622470324199</v>
@@ -7469,22 +7472,22 @@
         <v>89</v>
       </c>
       <c r="Y55" s="41" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="Z55" s="41" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AA55" s="47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AB55" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="AC55" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="AC55" s="41" t="s">
-        <v>272</v>
-      </c>
       <c r="AD55" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="56" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -7492,7 +7495,7 @@
         <v>113</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C56" s="40" t="s">
         <v>69</v>
@@ -7504,10 +7507,10 @@
         <v>5</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H56" s="48">
         <v>0.17</v>
@@ -7561,22 +7564,22 @@
         <v>57</v>
       </c>
       <c r="Y56" s="41" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z56" s="41" t="s">
+        <v>459</v>
+      </c>
+      <c r="AA56" s="47" t="s">
+        <v>423</v>
+      </c>
+      <c r="AB56" s="41" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC56" s="41" t="s">
         <v>425</v>
       </c>
-      <c r="Z56" s="41" t="s">
-        <v>462</v>
-      </c>
-      <c r="AA56" s="47" t="s">
-        <v>426</v>
-      </c>
-      <c r="AB56" s="41" t="s">
-        <v>427</v>
-      </c>
-      <c r="AC56" s="41" t="s">
-        <v>428</v>
-      </c>
       <c r="AD56" s="37" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="57" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -7584,22 +7587,22 @@
         <v>49</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C57" s="40" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>15</v>
       </c>
       <c r="F57" s="40" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H57" s="48">
         <v>2</v>
@@ -7641,7 +7644,7 @@
         <v>205061582</v>
       </c>
       <c r="U57" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V57" s="46">
         <v>40.8482802817337</v>
@@ -7653,22 +7656,22 @@
         <v>89</v>
       </c>
       <c r="Y57" s="41" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="Z57" s="41" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AA57" s="59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB57" s="41" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AC57" s="41" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AD57" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="58" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -7676,22 +7679,22 @@
         <v>84</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E58" s="40" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H58" s="56">
         <v>7.8E-2</v>
@@ -7745,22 +7748,22 @@
         <v>89</v>
       </c>
       <c r="Y58" s="41" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="Z58" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA58" s="47" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AB58" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="AC58" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="AD58" s="18" t="s">
         <v>441</v>
-      </c>
-      <c r="AC58" s="41" t="s">
-        <v>442</v>
-      </c>
-      <c r="AD58" s="18" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="59" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
@@ -7768,10 +7771,10 @@
         <v>49</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>103</v>
@@ -7780,10 +7783,10 @@
         <v>15</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H59" s="60">
         <v>8.5999999999999993E-2</v>
@@ -7834,25 +7837,25 @@
         <v>-8.2351799999999997</v>
       </c>
       <c r="X59" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y59" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Z59" s="7" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA59" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB59" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="AC59" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="AB59" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="AC59" s="7" t="s">
-        <v>213</v>
-      </c>
       <c r="AD59" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="60" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -7860,7 +7863,7 @@
         <v>78</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>69</v>
@@ -7872,10 +7875,10 @@
         <v>5</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H60" s="50">
         <v>1.2</v>
@@ -7929,22 +7932,22 @@
         <v>57</v>
       </c>
       <c r="Y60" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z60" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AA60" s="47" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AB60" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AC60" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AD60" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="61" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -7952,22 +7955,22 @@
         <v>84</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C61" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H61" s="50">
         <v>0.1</v>
@@ -8009,7 +8012,7 @@
         <v>26200000</v>
       </c>
       <c r="U61" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V61" s="54">
         <v>59.242157075260003</v>
@@ -8018,25 +8021,25 @@
         <v>11.046906259539099</v>
       </c>
       <c r="X61" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y61" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="Z61" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA61" s="47" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB61" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AC61" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AD61" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -8125,7 +8128,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="71" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B1" s="71"/>
     </row>
@@ -8151,10 +8154,10 @@
     </row>
     <row r="3" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="20"/>
@@ -8171,10 +8174,10 @@
     </row>
     <row r="4" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="20"/>
@@ -8191,10 +8194,10 @@
     </row>
     <row r="5" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="20"/>
@@ -8211,10 +8214,10 @@
     </row>
     <row r="6" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="20"/>
@@ -8234,7 +8237,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="20"/>
@@ -8254,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="20"/>
@@ -8271,10 +8274,10 @@
     </row>
     <row r="9" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="25"/>
@@ -8315,17 +8318,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8334,7 +8326,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100052CBA820BEBCD468114CF62615C95D9" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41d93ad2b4fecab14cfdaed9255371f8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ba695df1-2cef-45b3-b38e-525c8136ab22" xmlns:ns3="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a815193907c452009623866744c535" ns2:_="" ns3:_="">
     <xsd:import namespace="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
@@ -8575,24 +8567,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39E8DA8-D782-4F69-B46B-77021BF1B166}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -8600,7 +8586,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82507086-9DCD-4197-A4F6-ECCED658E0D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8617,4 +8603,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 120626.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmeurope-my.sharepoint.com/personal/salman_muhammad_cmeurope_org/Documents/Technical/IF mapping tool/if-map/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1973" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{164D9154-FC1A-46A4-A5AF-5583A80CF09C}"/>
+  <xr:revisionPtr revIDLastSave="1976" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28563BF1-43D2-4918-9D9D-1DF834F86BD4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -800,9 +800,6 @@
     <t>https://climate.ec.europa.eu/document/download/7eb6d2d5-c109-4c33-ba50-c065beb654d7_en?filename=if_pf_2022_anrav_en.pdf</t>
   </si>
   <si>
-    <t>Hybrid staged CO₂ capture system combining oxyfuel combustion (OxyCal) and post-combustion amine scrubbing. Achieving up to ~99% capture efficiency; CO₂ is processed via a CO₂ Processing Unit (CPU), transported by pipeline, and permanently stored in the depleted Galata gas field under the Black Sea.</t>
-  </si>
-  <si>
     <t>https://www.anthemis-ccs.com/en/about-the-project</t>
   </si>
   <si>
@@ -1226,9 +1223,6 @@
     <t>erstorp Oxo AB (Stenungsund site)</t>
   </si>
   <si>
-    <t>Project Air is a large-scale Innovation Fund project led by Perstorp Oxo AB at Perstorp’s Stenungsund chemicals site in Sweden. The project integrates carbon capture and utilisation with renewable hydrogen production to manufacture 200,000 tonnes of sustainable methanol per year for use as a chemical feedstock, replacing fossil methanol in Perstorp’s European operations. The Innovation Fund factsheet reports 4.06 MtCO₂e of greenhouse-gas avoidance over ten years, and the project is planned to enter operation in 2027.</t>
-  </si>
-  <si>
     <t>BioCirc Group ApS.</t>
   </si>
   <si>
@@ -1526,7 +1520,13 @@
     <t>eM-Rhône is a joint venture of Elyse Energy and Lafarge Cement (Holcim). It combines renewable hydrogen production on the Roches-Roussillon chemical platform in Salaise-sur-Sanne with CO₂ captured at Holcim/Lafarge’s cement plant in Le Teil, Ardèche, and transported by rail to the methanol site. The project is designed around 170 MW of PEM electrolysis, about 27 kt/year of hydrogen production, and about 195 kt/year of CO₂ use to produce large-scale e-methanol for chemical and maritime markets.</t>
   </si>
   <si>
-    <t>The project captures concentrated CO₂ from the Le Teil cement plant using a fully electric cryogenic capture scheme, liquefies and transports the CO₂ by rail to Salaise-sur-Sanne, then receives, stores, regasifies and purifies the CO₂ before reaction with hydrogen produced on site by 170 MW PEM electrolysis. The hydrogen is compressed and purified, then combined with the purified CO₂ in a methanol synthesis unit, followed by intermediate storage and final methanol storage via the adjacent TEPSA logistics system. The updated Innovation Fund factsheet gives 195 kt/year CO₂ input, 27 kt/year hydrogen production and 138 kt/year methanol output.</t>
+    <t>The project captures concentrated CO₂ from the Le Teil cement plant using a fully electric cryogenic capture scheme, liquefies and transports the CO₂ by rail to Salaise-sur-Sanne, then receives, stores, regasifies and purifies the CO₂ before reaction with hydrogen produced on site by 170 MW PEM electrolysis. The hydrogen is compressed and purified, then combined with the purified CO₂ in a methanol synthesis unit, followed by intermediate storage and final methanol storage via the adjacent TEPSA logistics system. The project takes 195 kt/year of CO₂ input and results in 27 kt/year of hydrogen production and 138 kt/year of methanol output.</t>
+  </si>
+  <si>
+    <t>Hybrid staged CO₂ capture system combining oxyfuel combustion (OxyCal) and post-combustion amine scrubbing. Achieving up to ~99% capture efficiency; CO₂ will be processed via a CO₂ Processing Unit (CPU), transported by pipeline, and permanently stored in the depleted Galata gas field under the Black Sea.</t>
+  </si>
+  <si>
+    <t>Project Air is a large-scale Innovation Fund project led by Perstorp Oxo AB at Perstorp’s Stenungsund chemicals site in Sweden. The project integrates carbon capture and utilisation with renewable hydrogen production to manufacture 200,000 tonnes of sustainable methanol per year for use as a chemical feedstock, replacing fossil methanol in Perstorp’s European operations. The Innovation Fund project factsheet reports 4.06 MtCO₂e of greenhouse-gas avoidance over ten years, and the project is planned to enter operation in 2027.</t>
   </si>
 </sst>
 </file>
@@ -2095,11 +2095,11 @@
     <xf numFmtId="167" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2615,19 +2615,19 @@
         <v>95</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA2" s="47" t="s">
         <v>236</v>
       </c>
       <c r="AB2" s="41" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AC2" s="41" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AD2" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -2635,7 +2635,7 @@
         <v>96</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C3" s="40" t="s">
         <v>169</v>
@@ -2704,22 +2704,22 @@
         <v>57</v>
       </c>
       <c r="Y3" s="41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Z3" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA3" s="47" t="s">
         <v>176</v>
       </c>
       <c r="AB3" s="41" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AC3" s="41" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AD3" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
@@ -2799,7 +2799,7 @@
         <v>226</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AA4" s="47" t="s">
         <v>235</v>
@@ -2825,7 +2825,7 @@
         <v>69</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E5" s="40" t="s">
         <v>5</v>
@@ -2891,7 +2891,7 @@
         <v>124</v>
       </c>
       <c r="Z5" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA5" s="47" t="s">
         <v>240</v>
@@ -2903,7 +2903,7 @@
         <v>242</v>
       </c>
       <c r="AD5" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
@@ -2983,7 +2983,7 @@
         <v>54</v>
       </c>
       <c r="Z6" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA6" s="47" t="s">
         <v>246</v>
@@ -2992,10 +2992,10 @@
         <v>245</v>
       </c>
       <c r="AC6" s="41" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AD6" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -3075,7 +3075,7 @@
         <v>223</v>
       </c>
       <c r="Z7" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA7" s="47" t="s">
         <v>248</v>
@@ -3084,10 +3084,10 @@
         <v>247</v>
       </c>
       <c r="AC7" s="41" t="s">
-        <v>249</v>
+        <v>490</v>
       </c>
       <c r="AD7" s="16" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3167,19 +3167,19 @@
         <v>82</v>
       </c>
       <c r="Z8" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA8" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AB8" s="41" t="s">
         <v>83</v>
       </c>
       <c r="AC8" s="41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AD8" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -3190,19 +3190,19 @@
         <v>157</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H9" s="50">
         <v>2.5819174</v>
@@ -3256,22 +3256,22 @@
         <v>57</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AA9" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB9" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AC9" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AD9" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -3279,13 +3279,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" s="40" t="s">
         <v>244</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E10" s="40" t="s">
         <v>21</v>
@@ -3351,16 +3351,16 @@
         <v>218</v>
       </c>
       <c r="Z10" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA10" s="47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AB10" s="41" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AD10" s="12" t="s">
         <v>2</v>
@@ -3383,10 +3383,10 @@
         <v>9</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>54</v>
@@ -3440,22 +3440,22 @@
         <v>171</v>
       </c>
       <c r="Y11" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="Z11" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA11" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="AB11" s="41" t="s">
         <v>299</v>
       </c>
-      <c r="Z11" s="41" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA11" s="47" t="s">
-        <v>296</v>
-      </c>
-      <c r="AB11" s="41" t="s">
+      <c r="AC11" s="41" t="s">
         <v>300</v>
       </c>
-      <c r="AC11" s="41" t="s">
-        <v>301</v>
-      </c>
       <c r="AD11" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -3535,19 +3535,19 @@
         <v>134</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA12" s="47" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AB12" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AC12" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AD12" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3624,22 +3624,22 @@
         <v>57</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA13" s="57" t="s">
         <v>117</v>
       </c>
       <c r="AB13" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="AC13" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="AC13" s="7" t="s">
-        <v>268</v>
-      </c>
       <c r="AD13" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -3650,7 +3650,7 @@
         <v>172</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>70</v>
@@ -3719,19 +3719,19 @@
         <v>174</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA14" s="47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AB14" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="AC14" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="AC14" s="7" t="s">
-        <v>292</v>
-      </c>
       <c r="AD14" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="148.19999999999999" x14ac:dyDescent="0.3">
@@ -3811,19 +3811,19 @@
         <v>123</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA15" s="47" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AB15" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AC15" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AD15" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3846,7 +3846,7 @@
         <v>195</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H16" s="48" t="s">
         <v>54</v>
@@ -3900,22 +3900,22 @@
         <v>171</v>
       </c>
       <c r="Y16" s="41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Z16" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA16" s="47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AB16" s="41" t="s">
+        <v>305</v>
+      </c>
+      <c r="AC16" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="AC16" s="41" t="s">
-        <v>307</v>
-      </c>
       <c r="AD16" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -3938,7 +3938,7 @@
         <v>179</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H17" s="58">
         <v>4.5999999999999999E-3</v>
@@ -3992,19 +3992,19 @@
         <v>171</v>
       </c>
       <c r="Y17" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Z17" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA17" s="59" t="s">
         <v>180</v>
       </c>
       <c r="AB17" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="AC17" s="41" t="s">
         <v>310</v>
-      </c>
-      <c r="AC17" s="41" t="s">
-        <v>311</v>
       </c>
       <c r="AD17" s="12" t="s">
         <v>2</v>
@@ -4087,19 +4087,19 @@
         <v>144</v>
       </c>
       <c r="Z18" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA18" s="59" t="s">
         <v>145</v>
       </c>
       <c r="AB18" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC18" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="AC18" s="41" t="s">
-        <v>273</v>
-      </c>
       <c r="AD18" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="45.6" x14ac:dyDescent="0.3">
@@ -4179,10 +4179,10 @@
         <v>65</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA19" s="47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AB19" s="7" t="s">
         <v>66</v>
@@ -4202,10 +4202,10 @@
         <v>165</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>12</v>
@@ -4214,7 +4214,7 @@
         <v>164</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H20" s="50">
         <v>2.11</v>
@@ -4271,19 +4271,19 @@
         <v>166</v>
       </c>
       <c r="Z20" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AA20" s="57" t="s">
         <v>167</v>
       </c>
       <c r="AB20" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="AC20" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="AC20" s="7" t="s">
-        <v>315</v>
-      </c>
       <c r="AD20" s="17" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4294,10 +4294,10 @@
         <v>215</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>15</v>
@@ -4360,22 +4360,22 @@
         <v>89</v>
       </c>
       <c r="Y21" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z21" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA21" s="47" t="s">
+        <v>317</v>
+      </c>
+      <c r="AB21" s="7" t="s">
         <v>316</v>
-      </c>
-      <c r="Z21" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="AA21" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="AB21" s="7" t="s">
-        <v>317</v>
       </c>
       <c r="AC21" s="7" t="s">
         <v>216</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4452,22 +4452,22 @@
         <v>171</v>
       </c>
       <c r="Y22" s="62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Z22" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA22" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB22" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="AB22" s="41" t="s">
+      <c r="AC22" s="41" t="s">
         <v>320</v>
       </c>
-      <c r="AC22" s="41" t="s">
-        <v>321</v>
-      </c>
       <c r="AD22" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="136.80000000000001" x14ac:dyDescent="0.3">
@@ -4487,10 +4487,10 @@
         <v>20</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H23" s="50">
         <v>0.56499999999999995</v>
@@ -4544,22 +4544,22 @@
         <v>57</v>
       </c>
       <c r="Y23" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA23" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB23" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="AB23" s="7" t="s">
+      <c r="AC23" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="AC23" s="7" t="s">
-        <v>326</v>
-      </c>
       <c r="AD23" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4579,10 +4579,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>334</v>
       </c>
       <c r="H24" s="50">
         <v>0.2</v>
@@ -4636,22 +4636,22 @@
         <v>126</v>
       </c>
       <c r="Y24" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z24" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA24" s="47" t="s">
         <v>337</v>
       </c>
-      <c r="Z24" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA24" s="47" t="s">
-        <v>338</v>
-      </c>
       <c r="AB24" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="AC24" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="AC24" s="7" t="s">
-        <v>336</v>
-      </c>
       <c r="AD24" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -4671,10 +4671,10 @@
         <v>19</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H25" s="50">
         <v>1</v>
@@ -4728,22 +4728,22 @@
         <v>171</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA25" s="47" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB25" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="AB25" s="7" t="s">
+      <c r="AC25" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="AC25" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="AD25" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -4754,7 +4754,7 @@
         <v>183</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>103</v>
@@ -4820,22 +4820,22 @@
         <v>171</v>
       </c>
       <c r="Y26" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Z26" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA26" s="57" t="s">
         <v>185</v>
       </c>
       <c r="AB26" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AC26" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AD26" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="129.6" x14ac:dyDescent="0.3">
@@ -4855,10 +4855,10 @@
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G27" s="40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H27" s="48">
         <v>0.23252429999999999</v>
@@ -4912,22 +4912,22 @@
         <v>57</v>
       </c>
       <c r="Y27" s="41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Z27" s="41" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA27" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="AB27" s="72" t="s">
-        <v>490</v>
+      <c r="AB27" s="71" t="s">
+        <v>488</v>
       </c>
       <c r="AC27" s="41" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AD27" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -4941,7 +4941,7 @@
         <v>158</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E28" s="40" t="s">
         <v>17</v>
@@ -5004,22 +5004,22 @@
         <v>89</v>
       </c>
       <c r="Y28" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="Z28" s="41" t="s">
+        <v>459</v>
+      </c>
+      <c r="AA28" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="Z28" s="41" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA28" s="47" t="s">
+      <c r="AB28" s="41" t="s">
         <v>342</v>
       </c>
-      <c r="AB28" s="41" t="s">
+      <c r="AC28" s="41" t="s">
         <v>343</v>
       </c>
-      <c r="AC28" s="41" t="s">
-        <v>344</v>
-      </c>
       <c r="AD28" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -5096,22 +5096,22 @@
         <v>126</v>
       </c>
       <c r="Y29" s="41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Z29" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA29" s="59" t="s">
         <v>138</v>
       </c>
       <c r="AB29" s="41" t="s">
+        <v>345</v>
+      </c>
+      <c r="AC29" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="AC29" s="41" t="s">
-        <v>347</v>
-      </c>
       <c r="AD29" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5119,19 +5119,19 @@
         <v>113</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>221</v>
@@ -5188,22 +5188,22 @@
         <v>171</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Z30" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA30" s="63" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB30" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="AB30" s="7" t="s">
+      <c r="AC30" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="AC30" s="7" t="s">
-        <v>375</v>
-      </c>
       <c r="AD30" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5283,19 +5283,19 @@
         <v>140</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA31" s="64" t="s">
         <v>141</v>
       </c>
       <c r="AB31" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AC31" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="AC31" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="AD31" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5315,10 +5315,10 @@
         <v>8</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H32" s="50">
         <v>1</v>
@@ -5372,22 +5372,22 @@
         <v>57</v>
       </c>
       <c r="Y32" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z32" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA32" s="47" t="s">
         <v>348</v>
       </c>
-      <c r="Z32" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA32" s="47" t="s">
-        <v>349</v>
-      </c>
       <c r="AB32" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AC32" s="7" t="s">
         <v>196</v>
       </c>
       <c r="AD32" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5467,19 +5467,19 @@
         <v>73</v>
       </c>
       <c r="Z33" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA33" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AB33" s="41" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC33" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="AC33" s="41" t="s">
-        <v>351</v>
-      </c>
       <c r="AD33" s="17" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5493,7 +5493,7 @@
         <v>158</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>15</v>
@@ -5554,22 +5554,22 @@
         <v>171</v>
       </c>
       <c r="Y34" s="41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Z34" s="41" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA34" s="47" t="s">
         <v>208</v>
       </c>
       <c r="AB34" s="41" t="s">
+        <v>353</v>
+      </c>
+      <c r="AC34" s="41" t="s">
         <v>354</v>
       </c>
-      <c r="AC34" s="41" t="s">
-        <v>355</v>
-      </c>
       <c r="AD34" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -5580,10 +5580,10 @@
         <v>97</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>17</v>
@@ -5592,7 +5592,7 @@
         <v>98</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H35" s="50">
         <v>0.28144999999999998</v>
@@ -5649,16 +5649,16 @@
         <v>99</v>
       </c>
       <c r="Z35" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AA35" s="47" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AB35" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC35" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="AC35" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="AD35" s="12" t="s">
         <v>2</v>
@@ -5672,7 +5672,7 @@
         <v>74</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>70</v>
@@ -5738,22 +5738,22 @@
         <v>57</v>
       </c>
       <c r="Y36" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="Z36" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA36" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="AB36" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="Z36" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA36" s="47" t="s">
-        <v>363</v>
-      </c>
-      <c r="AB36" s="7" t="s">
+      <c r="AC36" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="AC36" s="7" t="s">
-        <v>359</v>
-      </c>
       <c r="AD36" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5764,10 +5764,10 @@
         <v>199</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>8</v>
@@ -5833,19 +5833,19 @@
         <v>202</v>
       </c>
       <c r="Z37" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AA37" s="47" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AB37" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="AC37" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="AC37" s="7" t="s">
-        <v>361</v>
-      </c>
       <c r="AD37" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -5922,22 +5922,22 @@
         <v>57</v>
       </c>
       <c r="Y38" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z38" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA38" s="47" t="s">
         <v>287</v>
       </c>
-      <c r="Z38" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA38" s="47" t="s">
-        <v>288</v>
-      </c>
       <c r="AB38" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="AC38" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="AC38" s="7" t="s">
-        <v>286</v>
-      </c>
       <c r="AD38" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -5948,7 +5948,7 @@
         <v>219</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>70</v>
@@ -6012,19 +6012,19 @@
         <v>126</v>
       </c>
       <c r="Y39" s="41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Z39" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA39" s="47" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AB39" s="41" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AC39" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AD39" s="13" t="s">
         <v>2</v>
@@ -6041,7 +6041,7 @@
         <v>153</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E40" s="40" t="s">
         <v>13</v>
@@ -6107,19 +6107,19 @@
         <v>155</v>
       </c>
       <c r="Z40" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA40" s="47" t="s">
         <v>156</v>
       </c>
       <c r="AB40" s="41" t="s">
+        <v>364</v>
+      </c>
+      <c r="AC40" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="AC40" s="41" t="s">
-        <v>366</v>
-      </c>
       <c r="AD40" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6199,19 +6199,19 @@
         <v>58</v>
       </c>
       <c r="Z41" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA41" s="47" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AB41" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="AC41" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="AC41" s="41" t="s">
-        <v>368</v>
-      </c>
       <c r="AD41" s="17" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6291,19 +6291,19 @@
         <v>92</v>
       </c>
       <c r="Z42" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA42" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AB42" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AC42" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AD42" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -6311,13 +6311,13 @@
         <v>49</v>
       </c>
       <c r="B43" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>262</v>
-      </c>
       <c r="D43" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
@@ -6383,19 +6383,19 @@
         <v>182</v>
       </c>
       <c r="Z43" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA43" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB43" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="AB43" s="7" t="s">
+      <c r="AC43" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="AC43" s="7" t="s">
-        <v>265</v>
-      </c>
       <c r="AD43" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
@@ -6472,22 +6472,22 @@
         <v>57</v>
       </c>
       <c r="Y44" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z44" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA44" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="Z44" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA44" s="47" t="s">
+      <c r="AB44" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="AB44" s="7" t="s">
+      <c r="AC44" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="AC44" s="7" t="s">
-        <v>379</v>
-      </c>
       <c r="AD44" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6501,13 +6501,13 @@
         <v>244</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>54</v>
@@ -6564,22 +6564,22 @@
         <v>171</v>
       </c>
       <c r="Y45" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Z45" s="7" t="s">
         <v>158</v>
       </c>
       <c r="AA45" s="47" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AB45" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="AC45" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="AC45" s="7" t="s">
-        <v>384</v>
-      </c>
       <c r="AD45" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="46" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -6659,19 +6659,19 @@
         <v>150</v>
       </c>
       <c r="Z46" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA46" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AB46" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="AC46" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="AC46" s="41" t="s">
-        <v>283</v>
-      </c>
       <c r="AD46" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -6691,10 +6691,10 @@
         <v>18</v>
       </c>
       <c r="F47" s="40" t="s">
+        <v>384</v>
+      </c>
+      <c r="G47" s="40" t="s">
         <v>385</v>
-      </c>
-      <c r="G47" s="40" t="s">
-        <v>386</v>
       </c>
       <c r="H47" s="56">
         <v>1.55E-2</v>
@@ -6751,22 +6751,22 @@
         <v>106</v>
       </c>
       <c r="Z47" s="41" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA47" s="47" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AB47" s="41" t="s">
+        <v>386</v>
+      </c>
+      <c r="AC47" s="41" t="s">
         <v>387</v>
       </c>
-      <c r="AC47" s="41" t="s">
-        <v>388</v>
-      </c>
       <c r="AD47" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A48" s="49" t="s">
         <v>49</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>231</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H48" s="50">
         <v>0.40600000000000003</v>
@@ -6843,19 +6843,19 @@
         <v>237</v>
       </c>
       <c r="Z48" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA48" s="63" t="s">
         <v>234</v>
       </c>
       <c r="AB48" s="7" t="s">
-        <v>391</v>
+        <v>491</v>
       </c>
       <c r="AC48" s="7" t="s">
         <v>233</v>
       </c>
       <c r="AD48" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -6875,10 +6875,10 @@
         <v>17</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H49" s="60">
         <v>6.7077999999999999E-2</v>
@@ -6935,19 +6935,19 @@
         <v>104</v>
       </c>
       <c r="Z49" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA49" s="47" t="s">
+        <v>391</v>
+      </c>
+      <c r="AB49" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC49" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="AB49" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC49" s="7" t="s">
-        <v>395</v>
-      </c>
       <c r="AD49" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -6961,7 +6961,7 @@
         <v>158</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>11</v>
@@ -7012,22 +7012,22 @@
         <v>89</v>
       </c>
       <c r="Y50" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Z50" s="7" t="s">
         <v>158</v>
       </c>
       <c r="AA50" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="AB50" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC50" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="AB50" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="AC50" s="7" t="s">
-        <v>399</v>
-      </c>
       <c r="AD50" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -7047,10 +7047,10 @@
         <v>5</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G51" s="41" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H51" s="48">
         <v>0.27411429999999998</v>
@@ -7104,22 +7104,22 @@
         <v>89</v>
       </c>
       <c r="Y51" s="41" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Z51" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA51" s="47" t="s">
+        <v>399</v>
+      </c>
+      <c r="AB51" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="AC51" s="41" t="s">
         <v>401</v>
       </c>
-      <c r="AB51" s="41" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC51" s="41" t="s">
-        <v>403</v>
-      </c>
       <c r="AD51" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="52" spans="1:30" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7199,7 +7199,7 @@
         <v>109</v>
       </c>
       <c r="Z52" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA52" s="47" t="s">
         <v>110</v>
@@ -7211,7 +7211,7 @@
         <v>112</v>
       </c>
       <c r="AD52" s="17" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" spans="1:30" ht="114" x14ac:dyDescent="0.3">
@@ -7222,7 +7222,7 @@
         <v>163</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D53" s="41" t="s">
         <v>70</v>
@@ -7234,7 +7234,7 @@
         <v>164</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H53" s="48">
         <v>1.72E-2</v>
@@ -7288,19 +7288,19 @@
         <v>57</v>
       </c>
       <c r="Y53" s="41" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Z53" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA53" s="47" t="s">
+        <v>406</v>
+      </c>
+      <c r="AB53" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="AB53" s="41" t="s">
-        <v>410</v>
-      </c>
       <c r="AC53" s="41" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AD53" s="11" t="s">
         <v>3</v>
@@ -7314,19 +7314,19 @@
         <v>193</v>
       </c>
       <c r="C54" s="40" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E54" s="40" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G54" s="41" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H54" s="48">
         <v>0.16981750000000001</v>
@@ -7380,22 +7380,22 @@
         <v>89</v>
       </c>
       <c r="Y54" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z54" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA54" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB54" s="41" t="s">
+        <v>413</v>
+      </c>
+      <c r="AC54" s="41" t="s">
         <v>414</v>
       </c>
-      <c r="AB54" s="41" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC54" s="41" t="s">
-        <v>416</v>
-      </c>
       <c r="AD54" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="55" spans="1:30" ht="125.4" x14ac:dyDescent="0.3">
@@ -7406,19 +7406,19 @@
         <v>186</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>9</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G55" s="40" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H55" s="48">
         <v>4.2</v>
@@ -7472,22 +7472,22 @@
         <v>89</v>
       </c>
       <c r="Y55" s="41" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Z55" s="41" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA55" s="47" t="s">
         <v>187</v>
       </c>
       <c r="AB55" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="AC55" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="AC55" s="41" t="s">
-        <v>271</v>
-      </c>
       <c r="AD55" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="56" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -7507,10 +7507,10 @@
         <v>5</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H56" s="48">
         <v>0.17</v>
@@ -7564,22 +7564,22 @@
         <v>57</v>
       </c>
       <c r="Y56" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z56" s="41" t="s">
+        <v>457</v>
+      </c>
+      <c r="AA56" s="47" t="s">
+        <v>421</v>
+      </c>
+      <c r="AB56" s="41" t="s">
         <v>422</v>
       </c>
-      <c r="Z56" s="41" t="s">
-        <v>459</v>
-      </c>
-      <c r="AA56" s="47" t="s">
+      <c r="AC56" s="41" t="s">
         <v>423</v>
       </c>
-      <c r="AB56" s="41" t="s">
-        <v>424</v>
-      </c>
-      <c r="AC56" s="41" t="s">
-        <v>425</v>
-      </c>
       <c r="AD56" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -7590,19 +7590,19 @@
         <v>213</v>
       </c>
       <c r="C57" s="40" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>15</v>
       </c>
       <c r="F57" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H57" s="48">
         <v>2</v>
@@ -7656,22 +7656,22 @@
         <v>89</v>
       </c>
       <c r="Y57" s="41" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Z57" s="41" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA57" s="59" t="s">
         <v>214</v>
       </c>
       <c r="AB57" s="41" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AC57" s="41" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AD57" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="58" spans="1:30" ht="102.6" x14ac:dyDescent="0.3">
@@ -7685,7 +7685,7 @@
         <v>158</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E58" s="40" t="s">
         <v>13</v>
@@ -7748,22 +7748,22 @@
         <v>89</v>
       </c>
       <c r="Y58" s="41" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Z58" s="41" t="s">
         <v>158</v>
       </c>
       <c r="AA58" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="AB58" s="41" t="s">
+        <v>436</v>
+      </c>
+      <c r="AC58" s="41" t="s">
         <v>437</v>
       </c>
-      <c r="AB58" s="41" t="s">
-        <v>438</v>
-      </c>
-      <c r="AC58" s="41" t="s">
+      <c r="AD58" s="18" t="s">
         <v>439</v>
-      </c>
-      <c r="AD58" s="18" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="59" spans="1:30" ht="68.400000000000006" x14ac:dyDescent="0.3">
@@ -7840,22 +7840,22 @@
         <v>171</v>
       </c>
       <c r="Y59" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Z59" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA59" s="57" t="s">
         <v>211</v>
       </c>
       <c r="AB59" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AC59" s="7" t="s">
         <v>212</v>
       </c>
       <c r="AD59" s="38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="60" spans="1:30" ht="79.8" x14ac:dyDescent="0.3">
@@ -7932,22 +7932,22 @@
         <v>57</v>
       </c>
       <c r="Y60" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Z60" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA60" s="47" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AB60" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AC60" s="7" t="s">
         <v>131</v>
       </c>
       <c r="AD60" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="61" spans="1:30" ht="91.2" x14ac:dyDescent="0.3">
@@ -7961,13 +7961,13 @@
         <v>169</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>191</v>
@@ -8024,22 +8024,22 @@
         <v>171</v>
       </c>
       <c r="Y61" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Z61" s="7" t="s">
         <v>158</v>
       </c>
       <c r="AA61" s="47" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AB61" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AC61" s="7" t="s">
         <v>192</v>
       </c>
       <c r="AD61" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -8127,10 +8127,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
-        <v>486</v>
-      </c>
-      <c r="B1" s="71"/>
+      <c r="A1" s="72" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="72"/>
     </row>
     <row r="2" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -8154,10 +8154,10 @@
     </row>
     <row r="3" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="20"/>
@@ -8174,10 +8174,10 @@
     </row>
     <row r="4" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="20"/>
@@ -8194,10 +8194,10 @@
     </row>
     <row r="5" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="20"/>
@@ -8214,10 +8214,10 @@
     </row>
     <row r="6" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="20"/>
@@ -8237,7 +8237,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="20"/>
@@ -8257,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="20"/>
@@ -8274,10 +8274,10 @@
     </row>
     <row r="9" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="25"/>
